--- a/12626731.xlsx
+++ b/12626731.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHIVEN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C4F2BF3-A7D0-426D-96E6-8C6E6598A8BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57D6BFD9-F7A8-410D-8910-5DF3CB087B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -269,6 +269,9 @@
   </si>
   <si>
     <t>Today, I worked on Coding.</t>
+  </si>
+  <si>
+    <t>Today, I worked on Coding Hackathon.</t>
   </si>
 </sst>
 </file>
@@ -2475,93 +2478,189 @@
         <v>77</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="8"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="11"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="12"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="8"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="11"/>
-      <c r="L38" s="11"/>
-      <c r="M38" s="11"/>
-      <c r="N38" s="12"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="8"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="11"/>
-      <c r="L39" s="11"/>
-      <c r="M39" s="11"/>
-      <c r="N39" s="12"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="8"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="11"/>
-      <c r="L40" s="11"/>
-      <c r="M40" s="11"/>
-      <c r="N40" s="12"/>
+    <row r="37" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B37" s="14">
+        <v>60</v>
+      </c>
+      <c r="C37" s="14">
+        <v>0</v>
+      </c>
+      <c r="D37" s="14">
+        <v>0</v>
+      </c>
+      <c r="E37" s="14">
+        <v>300</v>
+      </c>
+      <c r="F37" s="14">
+        <v>0</v>
+      </c>
+      <c r="G37" s="14">
+        <v>0</v>
+      </c>
+      <c r="H37" s="14">
+        <v>270</v>
+      </c>
+      <c r="I37" s="15">
+        <f t="shared" ref="I37:I39" si="50">IF(SUM(B37:F37,H37)=0,"",SUM(B37:F37,H37))</f>
+        <v>630</v>
+      </c>
+      <c r="J37" s="15">
+        <f t="shared" ref="J37:J39" si="51">IF(I37="","",1440-I37)</f>
+        <v>810</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B38" s="14">
+        <v>600</v>
+      </c>
+      <c r="C38" s="14">
+        <v>0</v>
+      </c>
+      <c r="D38" s="14">
+        <v>0</v>
+      </c>
+      <c r="E38" s="14">
+        <v>420</v>
+      </c>
+      <c r="F38" s="14">
+        <v>0</v>
+      </c>
+      <c r="G38" s="14">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14">
+        <v>270</v>
+      </c>
+      <c r="I38" s="15">
+        <f t="shared" si="50"/>
+        <v>1290</v>
+      </c>
+      <c r="J38" s="15">
+        <f t="shared" si="51"/>
+        <v>150</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B39" s="14">
+        <v>540</v>
+      </c>
+      <c r="C39" s="14">
+        <v>0</v>
+      </c>
+      <c r="D39" s="14">
+        <v>300</v>
+      </c>
+      <c r="E39" s="14">
+        <v>30</v>
+      </c>
+      <c r="F39" s="14">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14">
+        <v>270</v>
+      </c>
+      <c r="I39" s="15">
+        <f t="shared" si="50"/>
+        <v>1140</v>
+      </c>
+      <c r="J39" s="15">
+        <f t="shared" si="51"/>
+        <v>300</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B40" s="14">
+        <v>400</v>
+      </c>
+      <c r="C40" s="14">
+        <v>0</v>
+      </c>
+      <c r="D40" s="14">
+        <v>120</v>
+      </c>
+      <c r="E40" s="14">
+        <v>30</v>
+      </c>
+      <c r="F40" s="14">
+        <v>350</v>
+      </c>
+      <c r="G40" s="14">
+        <v>7</v>
+      </c>
+      <c r="H40" s="14">
+        <v>270</v>
+      </c>
+      <c r="I40" s="15">
+        <f t="shared" ref="I40" si="52">IF(SUM(B40:F40,H40)=0,"",SUM(B40:F40,H40))</f>
+        <v>1170</v>
+      </c>
+      <c r="J40" s="15">
+        <f t="shared" ref="J40" si="53">IF(I40="","",1440-I40)</f>
+        <v>270</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="8"/>
@@ -3211,11 +3310,11 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
       <c r="I70" s="10" t="str">
-        <f t="shared" ref="I70:I133" si="50">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="54">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="10" t="str">
-        <f t="shared" ref="J70:J133" si="51">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="55">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="11"/>
@@ -3233,11 +3332,11 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
       <c r="I71" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J71" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K71" s="11"/>
@@ -3255,11 +3354,11 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
       <c r="I72" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J72" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K72" s="11"/>
@@ -3277,11 +3376,11 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
       <c r="I73" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J73" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K73" s="11"/>
@@ -3299,11 +3398,11 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
       <c r="I74" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J74" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K74" s="11"/>
@@ -3321,11 +3420,11 @@
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="I75" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J75" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K75" s="11"/>
@@ -3343,11 +3442,11 @@
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="I76" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J76" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K76" s="11"/>
@@ -3365,11 +3464,11 @@
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J77" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K77" s="11"/>
@@ -3387,11 +3486,11 @@
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J78" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K78" s="11"/>
@@ -3409,11 +3508,11 @@
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J79" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K79" s="11"/>
@@ -3431,11 +3530,11 @@
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J80" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K80" s="11"/>
@@ -3453,11 +3552,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J81" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -3475,11 +3574,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J82" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -3497,11 +3596,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J83" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -3519,11 +3618,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J84" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -3541,11 +3640,11 @@
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
       <c r="I85" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J85" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K85" s="11"/>
@@ -3563,11 +3662,11 @@
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J86" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K86" s="11"/>
@@ -3585,11 +3684,11 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
       <c r="I87" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J87" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K87" s="11"/>
@@ -3607,11 +3706,11 @@
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
       <c r="I88" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J88" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K88" s="11"/>
@@ -3629,11 +3728,11 @@
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
       <c r="I89" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J89" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K89" s="11"/>
@@ -3651,11 +3750,11 @@
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
       <c r="I90" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J90" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K90" s="11"/>
@@ -3673,11 +3772,11 @@
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
       <c r="I91" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J91" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K91" s="11"/>
@@ -3695,11 +3794,11 @@
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
       <c r="I92" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J92" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K92" s="11"/>
@@ -3717,11 +3816,11 @@
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
       <c r="I93" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J93" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K93" s="11"/>
@@ -3739,11 +3838,11 @@
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
       <c r="I94" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J94" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K94" s="11"/>
@@ -3761,11 +3860,11 @@
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
       <c r="I95" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J95" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K95" s="11"/>
@@ -3783,11 +3882,11 @@
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
       <c r="I96" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J96" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K96" s="11"/>
@@ -3805,11 +3904,11 @@
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J97" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K97" s="11"/>
@@ -3827,11 +3926,11 @@
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
       <c r="I98" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J98" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K98" s="11"/>
@@ -3849,11 +3948,11 @@
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
       <c r="I99" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J99" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K99" s="11"/>
@@ -3871,11 +3970,11 @@
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
       <c r="I100" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J100" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K100" s="11"/>
@@ -3893,11 +3992,11 @@
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
       <c r="I101" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J101" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K101" s="11"/>
@@ -3915,11 +4014,11 @@
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
       <c r="I102" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J102" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K102" s="11"/>
@@ -3937,11 +4036,11 @@
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J103" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K103" s="11"/>
@@ -3959,11 +4058,11 @@
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
       <c r="I104" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J104" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K104" s="11"/>
@@ -3981,11 +4080,11 @@
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
       <c r="I105" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J105" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K105" s="11"/>
@@ -4003,11 +4102,11 @@
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
       <c r="I106" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J106" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K106" s="11"/>
@@ -4025,11 +4124,11 @@
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J107" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K107" s="11"/>
@@ -4047,11 +4146,11 @@
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
       <c r="I108" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J108" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K108" s="11"/>
@@ -4069,11 +4168,11 @@
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J109" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K109" s="11"/>
@@ -4091,11 +4190,11 @@
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J110" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K110" s="11"/>
@@ -4113,11 +4212,11 @@
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J111" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K111" s="11"/>
@@ -4135,11 +4234,11 @@
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J112" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K112" s="11"/>
@@ -4157,11 +4256,11 @@
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J113" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K113" s="11"/>
@@ -4179,11 +4278,11 @@
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
       <c r="I114" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J114" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K114" s="11"/>
@@ -4201,11 +4300,11 @@
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
       <c r="I115" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J115" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K115" s="11"/>
@@ -4223,11 +4322,11 @@
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
       <c r="I116" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J116" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K116" s="11"/>
@@ -4245,11 +4344,11 @@
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
       <c r="I117" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J117" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K117" s="11"/>
@@ -4267,11 +4366,11 @@
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J118" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K118" s="11"/>
@@ -4289,11 +4388,11 @@
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
       <c r="I119" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J119" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K119" s="11"/>
@@ -4311,11 +4410,11 @@
       <c r="G120" s="9"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J120" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K120" s="11"/>
@@ -4333,11 +4432,11 @@
       <c r="G121" s="9"/>
       <c r="H121" s="9"/>
       <c r="I121" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J121" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K121" s="11"/>
@@ -4355,11 +4454,11 @@
       <c r="G122" s="9"/>
       <c r="H122" s="9"/>
       <c r="I122" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J122" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K122" s="11"/>
@@ -4377,11 +4476,11 @@
       <c r="G123" s="9"/>
       <c r="H123" s="9"/>
       <c r="I123" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J123" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K123" s="11"/>
@@ -4399,11 +4498,11 @@
       <c r="G124" s="9"/>
       <c r="H124" s="9"/>
       <c r="I124" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J124" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K124" s="11"/>
@@ -4421,11 +4520,11 @@
       <c r="G125" s="9"/>
       <c r="H125" s="9"/>
       <c r="I125" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J125" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K125" s="11"/>
@@ -4443,11 +4542,11 @@
       <c r="G126" s="9"/>
       <c r="H126" s="9"/>
       <c r="I126" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J126" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K126" s="11"/>
@@ -4465,11 +4564,11 @@
       <c r="G127" s="9"/>
       <c r="H127" s="9"/>
       <c r="I127" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J127" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K127" s="11"/>
@@ -4487,11 +4586,11 @@
       <c r="G128" s="9"/>
       <c r="H128" s="9"/>
       <c r="I128" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J128" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K128" s="11"/>
@@ -4509,11 +4608,11 @@
       <c r="G129" s="9"/>
       <c r="H129" s="9"/>
       <c r="I129" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J129" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K129" s="11"/>
@@ -4531,11 +4630,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -4553,11 +4652,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -4575,11 +4674,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -4597,11 +4696,11 @@
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
       <c r="I133" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J133" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K133" s="11"/>
@@ -4619,11 +4718,11 @@
       <c r="G134" s="9"/>
       <c r="H134" s="9"/>
       <c r="I134" s="10" t="str">
-        <f t="shared" ref="I134:I197" si="52">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="56">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="10" t="str">
-        <f t="shared" ref="J134:J197" si="53">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="57">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="11"/>
@@ -4641,11 +4740,11 @@
       <c r="G135" s="9"/>
       <c r="H135" s="9"/>
       <c r="I135" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J135" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K135" s="11"/>
@@ -4663,11 +4762,11 @@
       <c r="G136" s="9"/>
       <c r="H136" s="9"/>
       <c r="I136" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J136" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K136" s="11"/>
@@ -4685,11 +4784,11 @@
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
       <c r="I137" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J137" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K137" s="11"/>
@@ -4707,11 +4806,11 @@
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J138" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K138" s="11"/>
@@ -4729,11 +4828,11 @@
       <c r="G139" s="9"/>
       <c r="H139" s="9"/>
       <c r="I139" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J139" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K139" s="11"/>
@@ -4751,11 +4850,11 @@
       <c r="G140" s="9"/>
       <c r="H140" s="9"/>
       <c r="I140" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J140" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K140" s="11"/>
@@ -4773,11 +4872,11 @@
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
       <c r="I141" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J141" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K141" s="11"/>
@@ -4795,11 +4894,11 @@
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J142" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K142" s="11"/>
@@ -4817,11 +4916,11 @@
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
       <c r="I143" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J143" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K143" s="11"/>
@@ -4839,11 +4938,11 @@
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
       <c r="I144" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J144" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K144" s="11"/>
@@ -4861,11 +4960,11 @@
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J145" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K145" s="11"/>
@@ -4883,11 +4982,11 @@
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J146" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K146" s="11"/>
@@ -4905,11 +5004,11 @@
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
       <c r="I147" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J147" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K147" s="11"/>
@@ -4927,11 +5026,11 @@
       <c r="G148" s="9"/>
       <c r="H148" s="9"/>
       <c r="I148" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J148" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K148" s="11"/>
@@ -4949,11 +5048,11 @@
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
       <c r="I149" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J149" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K149" s="11"/>
@@ -4971,11 +5070,11 @@
       <c r="G150" s="9"/>
       <c r="H150" s="9"/>
       <c r="I150" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J150" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K150" s="11"/>
@@ -4993,11 +5092,11 @@
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
       <c r="I151" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J151" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K151" s="11"/>
@@ -5015,11 +5114,11 @@
       <c r="G152" s="9"/>
       <c r="H152" s="9"/>
       <c r="I152" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J152" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K152" s="11"/>
@@ -5037,11 +5136,11 @@
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
       <c r="I153" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J153" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K153" s="11"/>
@@ -5059,11 +5158,11 @@
       <c r="G154" s="9"/>
       <c r="H154" s="9"/>
       <c r="I154" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J154" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K154" s="11"/>
@@ -5081,11 +5180,11 @@
       <c r="G155" s="9"/>
       <c r="H155" s="9"/>
       <c r="I155" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J155" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K155" s="11"/>
@@ -5103,11 +5202,11 @@
       <c r="G156" s="9"/>
       <c r="H156" s="9"/>
       <c r="I156" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J156" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K156" s="11"/>
@@ -5125,11 +5224,11 @@
       <c r="G157" s="9"/>
       <c r="H157" s="9"/>
       <c r="I157" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J157" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K157" s="11"/>
@@ -5147,11 +5246,11 @@
       <c r="G158" s="9"/>
       <c r="H158" s="9"/>
       <c r="I158" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J158" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K158" s="11"/>
@@ -5169,11 +5268,11 @@
       <c r="G159" s="9"/>
       <c r="H159" s="9"/>
       <c r="I159" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J159" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K159" s="11"/>
@@ -5191,11 +5290,11 @@
       <c r="G160" s="9"/>
       <c r="H160" s="9"/>
       <c r="I160" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J160" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K160" s="11"/>
@@ -5213,11 +5312,11 @@
       <c r="G161" s="9"/>
       <c r="H161" s="9"/>
       <c r="I161" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J161" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K161" s="11"/>
@@ -5235,11 +5334,11 @@
       <c r="G162" s="9"/>
       <c r="H162" s="9"/>
       <c r="I162" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J162" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K162" s="11"/>
@@ -5257,11 +5356,11 @@
       <c r="G163" s="9"/>
       <c r="H163" s="9"/>
       <c r="I163" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J163" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K163" s="11"/>
@@ -5279,11 +5378,11 @@
       <c r="G164" s="9"/>
       <c r="H164" s="9"/>
       <c r="I164" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J164" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K164" s="11"/>
@@ -5301,11 +5400,11 @@
       <c r="G165" s="9"/>
       <c r="H165" s="9"/>
       <c r="I165" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J165" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K165" s="11"/>
@@ -5323,11 +5422,11 @@
       <c r="G166" s="9"/>
       <c r="H166" s="9"/>
       <c r="I166" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J166" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K166" s="11"/>
@@ -5345,11 +5444,11 @@
       <c r="G167" s="9"/>
       <c r="H167" s="9"/>
       <c r="I167" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J167" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K167" s="11"/>
@@ -5367,11 +5466,11 @@
       <c r="G168" s="9"/>
       <c r="H168" s="9"/>
       <c r="I168" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J168" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K168" s="11"/>
@@ -5389,11 +5488,11 @@
       <c r="G169" s="9"/>
       <c r="H169" s="9"/>
       <c r="I169" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J169" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K169" s="11"/>
@@ -5411,11 +5510,11 @@
       <c r="G170" s="9"/>
       <c r="H170" s="9"/>
       <c r="I170" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J170" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K170" s="11"/>
@@ -5433,11 +5532,11 @@
       <c r="G171" s="9"/>
       <c r="H171" s="9"/>
       <c r="I171" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J171" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K171" s="11"/>
@@ -5455,11 +5554,11 @@
       <c r="G172" s="9"/>
       <c r="H172" s="9"/>
       <c r="I172" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J172" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K172" s="11"/>
@@ -5477,11 +5576,11 @@
       <c r="G173" s="9"/>
       <c r="H173" s="9"/>
       <c r="I173" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J173" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K173" s="11"/>
@@ -5499,11 +5598,11 @@
       <c r="G174" s="9"/>
       <c r="H174" s="9"/>
       <c r="I174" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J174" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K174" s="11"/>
@@ -5521,11 +5620,11 @@
       <c r="G175" s="9"/>
       <c r="H175" s="9"/>
       <c r="I175" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J175" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K175" s="11"/>
@@ -5543,11 +5642,11 @@
       <c r="G176" s="9"/>
       <c r="H176" s="9"/>
       <c r="I176" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J176" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K176" s="11"/>
@@ -5565,11 +5664,11 @@
       <c r="G177" s="9"/>
       <c r="H177" s="9"/>
       <c r="I177" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J177" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K177" s="11"/>
@@ -5587,11 +5686,11 @@
       <c r="G178" s="9"/>
       <c r="H178" s="9"/>
       <c r="I178" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J178" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K178" s="11"/>
@@ -5609,11 +5708,11 @@
       <c r="G179" s="9"/>
       <c r="H179" s="9"/>
       <c r="I179" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J179" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K179" s="11"/>
@@ -5631,11 +5730,11 @@
       <c r="G180" s="9"/>
       <c r="H180" s="9"/>
       <c r="I180" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J180" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K180" s="11"/>
@@ -5653,11 +5752,11 @@
       <c r="G181" s="9"/>
       <c r="H181" s="9"/>
       <c r="I181" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J181" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K181" s="11"/>
@@ -5675,11 +5774,11 @@
       <c r="G182" s="9"/>
       <c r="H182" s="9"/>
       <c r="I182" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J182" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K182" s="11"/>
@@ -5697,11 +5796,11 @@
       <c r="G183" s="9"/>
       <c r="H183" s="9"/>
       <c r="I183" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J183" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K183" s="11"/>
@@ -5719,11 +5818,11 @@
       <c r="G184" s="9"/>
       <c r="H184" s="9"/>
       <c r="I184" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J184" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K184" s="11"/>
@@ -5741,11 +5840,11 @@
       <c r="G185" s="9"/>
       <c r="H185" s="9"/>
       <c r="I185" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J185" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K185" s="11"/>
@@ -5763,11 +5862,11 @@
       <c r="G186" s="9"/>
       <c r="H186" s="9"/>
       <c r="I186" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J186" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K186" s="11"/>
@@ -5785,11 +5884,11 @@
       <c r="G187" s="9"/>
       <c r="H187" s="9"/>
       <c r="I187" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J187" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K187" s="11"/>
@@ -5807,11 +5906,11 @@
       <c r="G188" s="9"/>
       <c r="H188" s="9"/>
       <c r="I188" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J188" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K188" s="11"/>
@@ -5829,11 +5928,11 @@
       <c r="G189" s="9"/>
       <c r="H189" s="9"/>
       <c r="I189" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J189" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K189" s="11"/>
@@ -5851,11 +5950,11 @@
       <c r="G190" s="9"/>
       <c r="H190" s="9"/>
       <c r="I190" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J190" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K190" s="11"/>
@@ -5873,11 +5972,11 @@
       <c r="G191" s="9"/>
       <c r="H191" s="9"/>
       <c r="I191" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J191" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K191" s="11"/>
@@ -5895,11 +5994,11 @@
       <c r="G192" s="9"/>
       <c r="H192" s="9"/>
       <c r="I192" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J192" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K192" s="11"/>
@@ -5917,11 +6016,11 @@
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J193" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K193" s="11"/>
@@ -5939,11 +6038,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -5961,11 +6060,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -5983,11 +6082,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -6005,11 +6104,11 @@
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J197" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K197" s="11"/>
@@ -6027,11 +6126,11 @@
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
       <c r="I198" s="10" t="str">
-        <f t="shared" ref="I198:I261" si="54">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="58">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="10" t="str">
-        <f t="shared" ref="J198:J261" si="55">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="59">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="11"/>
@@ -6049,11 +6148,11 @@
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
       <c r="I199" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J199" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K199" s="11"/>
@@ -6071,11 +6170,11 @@
       <c r="G200" s="9"/>
       <c r="H200" s="9"/>
       <c r="I200" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J200" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K200" s="11"/>
@@ -6093,11 +6192,11 @@
       <c r="G201" s="9"/>
       <c r="H201" s="9"/>
       <c r="I201" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J201" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K201" s="11"/>
@@ -6115,11 +6214,11 @@
       <c r="G202" s="9"/>
       <c r="H202" s="9"/>
       <c r="I202" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J202" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K202" s="11"/>
@@ -6137,11 +6236,11 @@
       <c r="G203" s="9"/>
       <c r="H203" s="9"/>
       <c r="I203" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J203" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K203" s="11"/>
@@ -6159,11 +6258,11 @@
       <c r="G204" s="9"/>
       <c r="H204" s="9"/>
       <c r="I204" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J204" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K204" s="11"/>
@@ -6181,11 +6280,11 @@
       <c r="G205" s="9"/>
       <c r="H205" s="9"/>
       <c r="I205" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J205" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K205" s="11"/>
@@ -6203,11 +6302,11 @@
       <c r="G206" s="9"/>
       <c r="H206" s="9"/>
       <c r="I206" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J206" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K206" s="11"/>
@@ -6225,11 +6324,11 @@
       <c r="G207" s="9"/>
       <c r="H207" s="9"/>
       <c r="I207" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J207" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K207" s="11"/>
@@ -6247,11 +6346,11 @@
       <c r="G208" s="9"/>
       <c r="H208" s="9"/>
       <c r="I208" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J208" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K208" s="11"/>
@@ -6269,11 +6368,11 @@
       <c r="G209" s="9"/>
       <c r="H209" s="9"/>
       <c r="I209" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J209" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K209" s="11"/>
@@ -6291,11 +6390,11 @@
       <c r="G210" s="9"/>
       <c r="H210" s="9"/>
       <c r="I210" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J210" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K210" s="11"/>
@@ -6313,11 +6412,11 @@
       <c r="G211" s="9"/>
       <c r="H211" s="9"/>
       <c r="I211" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J211" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K211" s="11"/>
@@ -6335,11 +6434,11 @@
       <c r="G212" s="9"/>
       <c r="H212" s="9"/>
       <c r="I212" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J212" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K212" s="11"/>
@@ -6357,11 +6456,11 @@
       <c r="G213" s="9"/>
       <c r="H213" s="9"/>
       <c r="I213" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J213" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K213" s="11"/>
@@ -6379,11 +6478,11 @@
       <c r="G214" s="9"/>
       <c r="H214" s="9"/>
       <c r="I214" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J214" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K214" s="11"/>
@@ -6401,11 +6500,11 @@
       <c r="G215" s="9"/>
       <c r="H215" s="9"/>
       <c r="I215" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J215" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K215" s="11"/>
@@ -6423,11 +6522,11 @@
       <c r="G216" s="9"/>
       <c r="H216" s="9"/>
       <c r="I216" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J216" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K216" s="11"/>
@@ -6445,11 +6544,11 @@
       <c r="G217" s="9"/>
       <c r="H217" s="9"/>
       <c r="I217" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J217" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K217" s="11"/>
@@ -6467,11 +6566,11 @@
       <c r="G218" s="9"/>
       <c r="H218" s="9"/>
       <c r="I218" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J218" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K218" s="11"/>
@@ -6489,11 +6588,11 @@
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
       <c r="I219" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J219" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K219" s="11"/>
@@ -6511,11 +6610,11 @@
       <c r="G220" s="9"/>
       <c r="H220" s="9"/>
       <c r="I220" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J220" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K220" s="11"/>
@@ -6533,11 +6632,11 @@
       <c r="G221" s="9"/>
       <c r="H221" s="9"/>
       <c r="I221" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J221" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K221" s="11"/>
@@ -6555,11 +6654,11 @@
       <c r="G222" s="9"/>
       <c r="H222" s="9"/>
       <c r="I222" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J222" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K222" s="11"/>
@@ -6577,11 +6676,11 @@
       <c r="G223" s="9"/>
       <c r="H223" s="9"/>
       <c r="I223" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J223" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K223" s="11"/>
@@ -6599,11 +6698,11 @@
       <c r="G224" s="9"/>
       <c r="H224" s="9"/>
       <c r="I224" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J224" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K224" s="11"/>
@@ -6621,11 +6720,11 @@
       <c r="G225" s="9"/>
       <c r="H225" s="9"/>
       <c r="I225" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J225" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K225" s="11"/>
@@ -6643,11 +6742,11 @@
       <c r="G226" s="9"/>
       <c r="H226" s="9"/>
       <c r="I226" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J226" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K226" s="11"/>
@@ -6665,11 +6764,11 @@
       <c r="G227" s="9"/>
       <c r="H227" s="9"/>
       <c r="I227" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J227" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K227" s="11"/>
@@ -6687,11 +6786,11 @@
       <c r="G228" s="9"/>
       <c r="H228" s="9"/>
       <c r="I228" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J228" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K228" s="11"/>
@@ -6709,11 +6808,11 @@
       <c r="G229" s="9"/>
       <c r="H229" s="9"/>
       <c r="I229" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J229" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K229" s="11"/>
@@ -6731,11 +6830,11 @@
       <c r="G230" s="9"/>
       <c r="H230" s="9"/>
       <c r="I230" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J230" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K230" s="11"/>
@@ -6753,11 +6852,11 @@
       <c r="G231" s="9"/>
       <c r="H231" s="9"/>
       <c r="I231" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J231" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K231" s="11"/>
@@ -6775,11 +6874,11 @@
       <c r="G232" s="9"/>
       <c r="H232" s="9"/>
       <c r="I232" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J232" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K232" s="11"/>
@@ -6797,11 +6896,11 @@
       <c r="G233" s="9"/>
       <c r="H233" s="9"/>
       <c r="I233" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J233" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K233" s="11"/>
@@ -6819,11 +6918,11 @@
       <c r="G234" s="9"/>
       <c r="H234" s="9"/>
       <c r="I234" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J234" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K234" s="11"/>
@@ -6841,11 +6940,11 @@
       <c r="G235" s="9"/>
       <c r="H235" s="9"/>
       <c r="I235" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J235" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K235" s="11"/>
@@ -6863,11 +6962,11 @@
       <c r="G236" s="9"/>
       <c r="H236" s="9"/>
       <c r="I236" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J236" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K236" s="11"/>
@@ -6885,11 +6984,11 @@
       <c r="G237" s="9"/>
       <c r="H237" s="9"/>
       <c r="I237" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J237" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K237" s="11"/>
@@ -6907,11 +7006,11 @@
       <c r="G238" s="9"/>
       <c r="H238" s="9"/>
       <c r="I238" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J238" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K238" s="11"/>
@@ -6929,11 +7028,11 @@
       <c r="G239" s="9"/>
       <c r="H239" s="9"/>
       <c r="I239" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J239" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K239" s="11"/>
@@ -6951,11 +7050,11 @@
       <c r="G240" s="9"/>
       <c r="H240" s="9"/>
       <c r="I240" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J240" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K240" s="11"/>
@@ -6973,11 +7072,11 @@
       <c r="G241" s="9"/>
       <c r="H241" s="9"/>
       <c r="I241" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J241" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K241" s="11"/>
@@ -6995,11 +7094,11 @@
       <c r="G242" s="9"/>
       <c r="H242" s="9"/>
       <c r="I242" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J242" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K242" s="11"/>
@@ -7017,11 +7116,11 @@
       <c r="G243" s="9"/>
       <c r="H243" s="9"/>
       <c r="I243" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J243" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K243" s="11"/>
@@ -7039,11 +7138,11 @@
       <c r="G244" s="9"/>
       <c r="H244" s="9"/>
       <c r="I244" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J244" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K244" s="11"/>
@@ -7061,11 +7160,11 @@
       <c r="G245" s="9"/>
       <c r="H245" s="9"/>
       <c r="I245" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J245" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K245" s="11"/>
@@ -7083,11 +7182,11 @@
       <c r="G246" s="9"/>
       <c r="H246" s="9"/>
       <c r="I246" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J246" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K246" s="11"/>
@@ -7105,11 +7204,11 @@
       <c r="G247" s="9"/>
       <c r="H247" s="9"/>
       <c r="I247" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J247" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K247" s="11"/>
@@ -7127,11 +7226,11 @@
       <c r="G248" s="9"/>
       <c r="H248" s="9"/>
       <c r="I248" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J248" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K248" s="11"/>
@@ -7149,11 +7248,11 @@
       <c r="G249" s="9"/>
       <c r="H249" s="9"/>
       <c r="I249" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J249" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K249" s="11"/>
@@ -7171,11 +7270,11 @@
       <c r="G250" s="9"/>
       <c r="H250" s="9"/>
       <c r="I250" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J250" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K250" s="11"/>
@@ -7193,11 +7292,11 @@
       <c r="G251" s="9"/>
       <c r="H251" s="9"/>
       <c r="I251" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J251" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K251" s="11"/>
@@ -7215,11 +7314,11 @@
       <c r="G252" s="9"/>
       <c r="H252" s="9"/>
       <c r="I252" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J252" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K252" s="11"/>
@@ -7237,11 +7336,11 @@
       <c r="G253" s="9"/>
       <c r="H253" s="9"/>
       <c r="I253" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J253" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K253" s="11"/>
@@ -7259,11 +7358,11 @@
       <c r="G254" s="9"/>
       <c r="H254" s="9"/>
       <c r="I254" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J254" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K254" s="11"/>
@@ -7281,11 +7380,11 @@
       <c r="G255" s="9"/>
       <c r="H255" s="9"/>
       <c r="I255" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J255" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K255" s="11"/>
@@ -7303,11 +7402,11 @@
       <c r="G256" s="9"/>
       <c r="H256" s="9"/>
       <c r="I256" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J256" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K256" s="11"/>
@@ -7325,11 +7424,11 @@
       <c r="G257" s="9"/>
       <c r="H257" s="9"/>
       <c r="I257" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J257" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K257" s="11"/>
@@ -7347,11 +7446,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -7369,11 +7468,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -7391,11 +7490,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -7413,11 +7512,11 @@
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
       <c r="I261" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J261" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K261" s="11"/>
@@ -7435,11 +7534,11 @@
       <c r="G262" s="9"/>
       <c r="H262" s="9"/>
       <c r="I262" s="10" t="str">
-        <f t="shared" ref="I262:I325" si="56">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="60">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="10" t="str">
-        <f t="shared" ref="J262:J325" si="57">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="61">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="11"/>
@@ -7457,11 +7556,11 @@
       <c r="G263" s="9"/>
       <c r="H263" s="9"/>
       <c r="I263" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J263" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K263" s="11"/>
@@ -7479,11 +7578,11 @@
       <c r="G264" s="9"/>
       <c r="H264" s="9"/>
       <c r="I264" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J264" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K264" s="11"/>
@@ -7501,11 +7600,11 @@
       <c r="G265" s="9"/>
       <c r="H265" s="9"/>
       <c r="I265" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J265" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K265" s="11"/>
@@ -7523,11 +7622,11 @@
       <c r="G266" s="9"/>
       <c r="H266" s="9"/>
       <c r="I266" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J266" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K266" s="11"/>
@@ -7545,11 +7644,11 @@
       <c r="G267" s="9"/>
       <c r="H267" s="9"/>
       <c r="I267" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J267" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K267" s="11"/>
@@ -7567,11 +7666,11 @@
       <c r="G268" s="9"/>
       <c r="H268" s="9"/>
       <c r="I268" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J268" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K268" s="11"/>
@@ -7589,11 +7688,11 @@
       <c r="G269" s="9"/>
       <c r="H269" s="9"/>
       <c r="I269" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J269" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K269" s="11"/>
@@ -7611,11 +7710,11 @@
       <c r="G270" s="9"/>
       <c r="H270" s="9"/>
       <c r="I270" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J270" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K270" s="11"/>
@@ -7633,11 +7732,11 @@
       <c r="G271" s="9"/>
       <c r="H271" s="9"/>
       <c r="I271" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J271" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K271" s="11"/>
@@ -7655,11 +7754,11 @@
       <c r="G272" s="9"/>
       <c r="H272" s="9"/>
       <c r="I272" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J272" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K272" s="11"/>
@@ -7677,11 +7776,11 @@
       <c r="G273" s="9"/>
       <c r="H273" s="9"/>
       <c r="I273" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J273" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K273" s="11"/>
@@ -7699,11 +7798,11 @@
       <c r="G274" s="9"/>
       <c r="H274" s="9"/>
       <c r="I274" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J274" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K274" s="11"/>
@@ -7721,11 +7820,11 @@
       <c r="G275" s="9"/>
       <c r="H275" s="9"/>
       <c r="I275" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J275" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K275" s="11"/>
@@ -7743,11 +7842,11 @@
       <c r="G276" s="9"/>
       <c r="H276" s="9"/>
       <c r="I276" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J276" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K276" s="11"/>
@@ -7765,11 +7864,11 @@
       <c r="G277" s="9"/>
       <c r="H277" s="9"/>
       <c r="I277" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J277" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K277" s="11"/>
@@ -7787,11 +7886,11 @@
       <c r="G278" s="9"/>
       <c r="H278" s="9"/>
       <c r="I278" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J278" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K278" s="11"/>
@@ -7809,11 +7908,11 @@
       <c r="G279" s="9"/>
       <c r="H279" s="9"/>
       <c r="I279" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J279" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K279" s="11"/>
@@ -7831,11 +7930,11 @@
       <c r="G280" s="9"/>
       <c r="H280" s="9"/>
       <c r="I280" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J280" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K280" s="11"/>
@@ -7853,11 +7952,11 @@
       <c r="G281" s="9"/>
       <c r="H281" s="9"/>
       <c r="I281" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J281" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K281" s="11"/>
@@ -7875,11 +7974,11 @@
       <c r="G282" s="9"/>
       <c r="H282" s="9"/>
       <c r="I282" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J282" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K282" s="11"/>
@@ -7897,11 +7996,11 @@
       <c r="G283" s="9"/>
       <c r="H283" s="9"/>
       <c r="I283" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J283" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K283" s="11"/>
@@ -7919,11 +8018,11 @@
       <c r="G284" s="9"/>
       <c r="H284" s="9"/>
       <c r="I284" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J284" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K284" s="11"/>
@@ -7941,11 +8040,11 @@
       <c r="G285" s="9"/>
       <c r="H285" s="9"/>
       <c r="I285" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J285" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K285" s="11"/>
@@ -7963,11 +8062,11 @@
       <c r="G286" s="9"/>
       <c r="H286" s="9"/>
       <c r="I286" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J286" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K286" s="11"/>
@@ -7985,11 +8084,11 @@
       <c r="G287" s="9"/>
       <c r="H287" s="9"/>
       <c r="I287" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J287" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K287" s="11"/>
@@ -8007,11 +8106,11 @@
       <c r="G288" s="9"/>
       <c r="H288" s="9"/>
       <c r="I288" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J288" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K288" s="11"/>
@@ -8029,11 +8128,11 @@
       <c r="G289" s="9"/>
       <c r="H289" s="9"/>
       <c r="I289" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J289" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K289" s="11"/>
@@ -8051,11 +8150,11 @@
       <c r="G290" s="9"/>
       <c r="H290" s="9"/>
       <c r="I290" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J290" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K290" s="11"/>
@@ -8073,11 +8172,11 @@
       <c r="G291" s="9"/>
       <c r="H291" s="9"/>
       <c r="I291" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J291" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K291" s="11"/>
@@ -8095,11 +8194,11 @@
       <c r="G292" s="9"/>
       <c r="H292" s="9"/>
       <c r="I292" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J292" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K292" s="11"/>
@@ -8117,11 +8216,11 @@
       <c r="G293" s="9"/>
       <c r="H293" s="9"/>
       <c r="I293" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J293" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K293" s="11"/>
@@ -8139,11 +8238,11 @@
       <c r="G294" s="9"/>
       <c r="H294" s="9"/>
       <c r="I294" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J294" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K294" s="11"/>
@@ -8161,11 +8260,11 @@
       <c r="G295" s="9"/>
       <c r="H295" s="9"/>
       <c r="I295" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J295" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K295" s="11"/>
@@ -8183,11 +8282,11 @@
       <c r="G296" s="9"/>
       <c r="H296" s="9"/>
       <c r="I296" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J296" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K296" s="11"/>
@@ -8205,11 +8304,11 @@
       <c r="G297" s="9"/>
       <c r="H297" s="9"/>
       <c r="I297" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J297" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K297" s="11"/>
@@ -8227,11 +8326,11 @@
       <c r="G298" s="9"/>
       <c r="H298" s="9"/>
       <c r="I298" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J298" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K298" s="11"/>
@@ -8249,11 +8348,11 @@
       <c r="G299" s="9"/>
       <c r="H299" s="9"/>
       <c r="I299" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J299" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K299" s="11"/>
@@ -8271,11 +8370,11 @@
       <c r="G300" s="9"/>
       <c r="H300" s="9"/>
       <c r="I300" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J300" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K300" s="11"/>
@@ -8293,11 +8392,11 @@
       <c r="G301" s="9"/>
       <c r="H301" s="9"/>
       <c r="I301" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J301" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K301" s="11"/>
@@ -8315,11 +8414,11 @@
       <c r="G302" s="9"/>
       <c r="H302" s="9"/>
       <c r="I302" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J302" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K302" s="11"/>
@@ -8337,11 +8436,11 @@
       <c r="G303" s="9"/>
       <c r="H303" s="9"/>
       <c r="I303" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J303" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K303" s="11"/>
@@ -8359,11 +8458,11 @@
       <c r="G304" s="9"/>
       <c r="H304" s="9"/>
       <c r="I304" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J304" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K304" s="11"/>
@@ -8381,11 +8480,11 @@
       <c r="G305" s="9"/>
       <c r="H305" s="9"/>
       <c r="I305" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J305" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K305" s="11"/>
@@ -8403,11 +8502,11 @@
       <c r="G306" s="9"/>
       <c r="H306" s="9"/>
       <c r="I306" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J306" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K306" s="11"/>
@@ -8425,11 +8524,11 @@
       <c r="G307" s="9"/>
       <c r="H307" s="9"/>
       <c r="I307" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J307" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K307" s="11"/>
@@ -8447,11 +8546,11 @@
       <c r="G308" s="9"/>
       <c r="H308" s="9"/>
       <c r="I308" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J308" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K308" s="11"/>
@@ -8469,11 +8568,11 @@
       <c r="G309" s="9"/>
       <c r="H309" s="9"/>
       <c r="I309" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J309" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K309" s="11"/>
@@ -8491,11 +8590,11 @@
       <c r="G310" s="9"/>
       <c r="H310" s="9"/>
       <c r="I310" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J310" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K310" s="11"/>
@@ -8513,11 +8612,11 @@
       <c r="G311" s="9"/>
       <c r="H311" s="9"/>
       <c r="I311" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J311" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K311" s="11"/>
@@ -8535,11 +8634,11 @@
       <c r="G312" s="9"/>
       <c r="H312" s="9"/>
       <c r="I312" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J312" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K312" s="11"/>
@@ -8557,11 +8656,11 @@
       <c r="G313" s="9"/>
       <c r="H313" s="9"/>
       <c r="I313" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J313" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K313" s="11"/>
@@ -8579,11 +8678,11 @@
       <c r="G314" s="9"/>
       <c r="H314" s="9"/>
       <c r="I314" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J314" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K314" s="11"/>
@@ -8601,11 +8700,11 @@
       <c r="G315" s="9"/>
       <c r="H315" s="9"/>
       <c r="I315" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J315" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K315" s="11"/>
@@ -8623,11 +8722,11 @@
       <c r="G316" s="9"/>
       <c r="H316" s="9"/>
       <c r="I316" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J316" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K316" s="11"/>
@@ -8645,11 +8744,11 @@
       <c r="G317" s="9"/>
       <c r="H317" s="9"/>
       <c r="I317" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J317" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K317" s="11"/>
@@ -8667,11 +8766,11 @@
       <c r="G318" s="9"/>
       <c r="H318" s="9"/>
       <c r="I318" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J318" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K318" s="11"/>
@@ -8689,11 +8788,11 @@
       <c r="G319" s="9"/>
       <c r="H319" s="9"/>
       <c r="I319" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J319" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K319" s="11"/>
@@ -8711,11 +8810,11 @@
       <c r="G320" s="9"/>
       <c r="H320" s="9"/>
       <c r="I320" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J320" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K320" s="11"/>
@@ -8733,11 +8832,11 @@
       <c r="G321" s="9"/>
       <c r="H321" s="9"/>
       <c r="I321" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J321" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K321" s="11"/>
@@ -8755,11 +8854,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -8777,11 +8876,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -8799,11 +8898,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -8821,11 +8920,11 @@
       <c r="G325" s="9"/>
       <c r="H325" s="9"/>
       <c r="I325" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J325" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K325" s="11"/>
@@ -8843,11 +8942,11 @@
       <c r="G326" s="9"/>
       <c r="H326" s="9"/>
       <c r="I326" s="10" t="str">
-        <f t="shared" ref="I326:I389" si="58">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="62">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="10" t="str">
-        <f t="shared" ref="J326:J389" si="59">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="63">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="11"/>
@@ -8865,11 +8964,11 @@
       <c r="G327" s="9"/>
       <c r="H327" s="9"/>
       <c r="I327" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J327" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K327" s="11"/>
@@ -8887,11 +8986,11 @@
       <c r="G328" s="9"/>
       <c r="H328" s="9"/>
       <c r="I328" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J328" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K328" s="11"/>
@@ -8909,11 +9008,11 @@
       <c r="G329" s="9"/>
       <c r="H329" s="9"/>
       <c r="I329" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J329" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K329" s="11"/>
@@ -8931,11 +9030,11 @@
       <c r="G330" s="9"/>
       <c r="H330" s="9"/>
       <c r="I330" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J330" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K330" s="11"/>
@@ -8953,11 +9052,11 @@
       <c r="G331" s="9"/>
       <c r="H331" s="9"/>
       <c r="I331" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J331" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K331" s="11"/>
@@ -8975,11 +9074,11 @@
       <c r="G332" s="9"/>
       <c r="H332" s="9"/>
       <c r="I332" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J332" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K332" s="11"/>
@@ -8997,11 +9096,11 @@
       <c r="G333" s="9"/>
       <c r="H333" s="9"/>
       <c r="I333" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J333" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K333" s="11"/>
@@ -9019,11 +9118,11 @@
       <c r="G334" s="9"/>
       <c r="H334" s="9"/>
       <c r="I334" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J334" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K334" s="11"/>
@@ -9041,11 +9140,11 @@
       <c r="G335" s="9"/>
       <c r="H335" s="9"/>
       <c r="I335" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J335" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K335" s="11"/>
@@ -9063,11 +9162,11 @@
       <c r="G336" s="9"/>
       <c r="H336" s="9"/>
       <c r="I336" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J336" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K336" s="11"/>
@@ -9085,11 +9184,11 @@
       <c r="G337" s="9"/>
       <c r="H337" s="9"/>
       <c r="I337" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J337" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K337" s="11"/>
@@ -9107,11 +9206,11 @@
       <c r="G338" s="9"/>
       <c r="H338" s="9"/>
       <c r="I338" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J338" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K338" s="11"/>
@@ -9129,11 +9228,11 @@
       <c r="G339" s="9"/>
       <c r="H339" s="9"/>
       <c r="I339" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J339" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K339" s="11"/>
@@ -9151,11 +9250,11 @@
       <c r="G340" s="9"/>
       <c r="H340" s="9"/>
       <c r="I340" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J340" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K340" s="11"/>
@@ -9173,11 +9272,11 @@
       <c r="G341" s="9"/>
       <c r="H341" s="9"/>
       <c r="I341" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J341" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K341" s="11"/>
@@ -9195,11 +9294,11 @@
       <c r="G342" s="9"/>
       <c r="H342" s="9"/>
       <c r="I342" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J342" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K342" s="11"/>
@@ -9217,11 +9316,11 @@
       <c r="G343" s="9"/>
       <c r="H343" s="9"/>
       <c r="I343" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J343" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K343" s="11"/>
@@ -9239,11 +9338,11 @@
       <c r="G344" s="9"/>
       <c r="H344" s="9"/>
       <c r="I344" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J344" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K344" s="11"/>
@@ -9261,11 +9360,11 @@
       <c r="G345" s="9"/>
       <c r="H345" s="9"/>
       <c r="I345" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J345" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K345" s="11"/>
@@ -9283,11 +9382,11 @@
       <c r="G346" s="9"/>
       <c r="H346" s="9"/>
       <c r="I346" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J346" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K346" s="11"/>
@@ -9305,11 +9404,11 @@
       <c r="G347" s="9"/>
       <c r="H347" s="9"/>
       <c r="I347" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J347" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K347" s="11"/>
@@ -9327,11 +9426,11 @@
       <c r="G348" s="9"/>
       <c r="H348" s="9"/>
       <c r="I348" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J348" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K348" s="11"/>
@@ -9349,11 +9448,11 @@
       <c r="G349" s="9"/>
       <c r="H349" s="9"/>
       <c r="I349" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J349" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K349" s="11"/>
@@ -9371,11 +9470,11 @@
       <c r="G350" s="9"/>
       <c r="H350" s="9"/>
       <c r="I350" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J350" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K350" s="11"/>
@@ -9393,11 +9492,11 @@
       <c r="G351" s="9"/>
       <c r="H351" s="9"/>
       <c r="I351" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J351" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K351" s="11"/>
@@ -9415,11 +9514,11 @@
       <c r="G352" s="9"/>
       <c r="H352" s="9"/>
       <c r="I352" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J352" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K352" s="11"/>
@@ -9437,11 +9536,11 @@
       <c r="G353" s="9"/>
       <c r="H353" s="9"/>
       <c r="I353" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J353" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K353" s="11"/>
@@ -9459,11 +9558,11 @@
       <c r="G354" s="9"/>
       <c r="H354" s="9"/>
       <c r="I354" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J354" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K354" s="11"/>
@@ -9481,11 +9580,11 @@
       <c r="G355" s="9"/>
       <c r="H355" s="9"/>
       <c r="I355" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J355" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K355" s="11"/>
@@ -9503,11 +9602,11 @@
       <c r="G356" s="9"/>
       <c r="H356" s="9"/>
       <c r="I356" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J356" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K356" s="11"/>
@@ -9525,11 +9624,11 @@
       <c r="G357" s="9"/>
       <c r="H357" s="9"/>
       <c r="I357" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J357" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K357" s="11"/>
@@ -9547,11 +9646,11 @@
       <c r="G358" s="9"/>
       <c r="H358" s="9"/>
       <c r="I358" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J358" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K358" s="11"/>
@@ -9569,11 +9668,11 @@
       <c r="G359" s="9"/>
       <c r="H359" s="9"/>
       <c r="I359" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J359" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K359" s="11"/>
@@ -9591,11 +9690,11 @@
       <c r="G360" s="9"/>
       <c r="H360" s="9"/>
       <c r="I360" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J360" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K360" s="11"/>
@@ -9613,11 +9712,11 @@
       <c r="G361" s="9"/>
       <c r="H361" s="9"/>
       <c r="I361" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J361" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K361" s="11"/>
@@ -9635,11 +9734,11 @@
       <c r="G362" s="9"/>
       <c r="H362" s="9"/>
       <c r="I362" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J362" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K362" s="11"/>
@@ -9657,11 +9756,11 @@
       <c r="G363" s="9"/>
       <c r="H363" s="9"/>
       <c r="I363" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J363" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K363" s="11"/>
@@ -9679,11 +9778,11 @@
       <c r="G364" s="9"/>
       <c r="H364" s="9"/>
       <c r="I364" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J364" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K364" s="11"/>
@@ -9701,11 +9800,11 @@
       <c r="G365" s="9"/>
       <c r="H365" s="9"/>
       <c r="I365" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J365" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K365" s="11"/>
@@ -9723,11 +9822,11 @@
       <c r="G366" s="9"/>
       <c r="H366" s="9"/>
       <c r="I366" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J366" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K366" s="11"/>
@@ -9745,11 +9844,11 @@
       <c r="G367" s="9"/>
       <c r="H367" s="9"/>
       <c r="I367" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J367" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K367" s="11"/>
@@ -9767,11 +9866,11 @@
       <c r="G368" s="9"/>
       <c r="H368" s="9"/>
       <c r="I368" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J368" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K368" s="11"/>
@@ -9789,11 +9888,11 @@
       <c r="G369" s="9"/>
       <c r="H369" s="9"/>
       <c r="I369" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J369" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K369" s="11"/>
@@ -9811,11 +9910,11 @@
       <c r="G370" s="9"/>
       <c r="H370" s="9"/>
       <c r="I370" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J370" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K370" s="11"/>
@@ -9833,11 +9932,11 @@
       <c r="G371" s="9"/>
       <c r="H371" s="9"/>
       <c r="I371" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J371" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K371" s="11"/>
@@ -9855,11 +9954,11 @@
       <c r="G372" s="9"/>
       <c r="H372" s="9"/>
       <c r="I372" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J372" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K372" s="11"/>
@@ -9877,11 +9976,11 @@
       <c r="G373" s="9"/>
       <c r="H373" s="9"/>
       <c r="I373" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J373" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K373" s="11"/>
@@ -9899,11 +9998,11 @@
       <c r="G374" s="9"/>
       <c r="H374" s="9"/>
       <c r="I374" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J374" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K374" s="11"/>
@@ -9921,11 +10020,11 @@
       <c r="G375" s="9"/>
       <c r="H375" s="9"/>
       <c r="I375" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J375" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K375" s="11"/>
@@ -9943,11 +10042,11 @@
       <c r="G376" s="9"/>
       <c r="H376" s="9"/>
       <c r="I376" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J376" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K376" s="11"/>
@@ -9965,11 +10064,11 @@
       <c r="G377" s="9"/>
       <c r="H377" s="9"/>
       <c r="I377" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J377" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K377" s="11"/>
@@ -9987,11 +10086,11 @@
       <c r="G378" s="9"/>
       <c r="H378" s="9"/>
       <c r="I378" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J378" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K378" s="11"/>
@@ -10009,11 +10108,11 @@
       <c r="G379" s="9"/>
       <c r="H379" s="9"/>
       <c r="I379" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J379" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K379" s="11"/>
@@ -10031,11 +10130,11 @@
       <c r="G380" s="9"/>
       <c r="H380" s="9"/>
       <c r="I380" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J380" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K380" s="11"/>
@@ -10053,11 +10152,11 @@
       <c r="G381" s="9"/>
       <c r="H381" s="9"/>
       <c r="I381" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J381" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K381" s="11"/>
@@ -10075,11 +10174,11 @@
       <c r="G382" s="9"/>
       <c r="H382" s="9"/>
       <c r="I382" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J382" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K382" s="11"/>
@@ -10097,11 +10196,11 @@
       <c r="G383" s="9"/>
       <c r="H383" s="9"/>
       <c r="I383" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J383" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K383" s="11"/>
@@ -10119,11 +10218,11 @@
       <c r="G384" s="9"/>
       <c r="H384" s="9"/>
       <c r="I384" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J384" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K384" s="11"/>
@@ -10141,11 +10240,11 @@
       <c r="G385" s="9"/>
       <c r="H385" s="9"/>
       <c r="I385" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J385" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K385" s="11"/>
@@ -10163,11 +10262,11 @@
       <c r="G386" s="9"/>
       <c r="H386" s="9"/>
       <c r="I386" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J386" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K386" s="11"/>
@@ -10185,11 +10284,11 @@
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J387" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K387" s="11"/>
@@ -10207,11 +10306,11 @@
       <c r="G388" s="9"/>
       <c r="H388" s="9"/>
       <c r="I388" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J388" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K388" s="11"/>
@@ -10229,11 +10328,11 @@
       <c r="G389" s="9"/>
       <c r="H389" s="9"/>
       <c r="I389" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J389" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K389" s="11"/>
@@ -10251,11 +10350,11 @@
       <c r="G390" s="9"/>
       <c r="H390" s="9"/>
       <c r="I390" s="10" t="str">
-        <f t="shared" ref="I390:I401" si="60">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="64">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="10" t="str">
-        <f t="shared" ref="J390:J401" si="61">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="65">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="11"/>
@@ -10273,11 +10372,11 @@
       <c r="G391" s="9"/>
       <c r="H391" s="9"/>
       <c r="I391" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J391" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K391" s="11"/>
@@ -10295,11 +10394,11 @@
       <c r="G392" s="9"/>
       <c r="H392" s="9"/>
       <c r="I392" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J392" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K392" s="11"/>
@@ -10317,11 +10416,11 @@
       <c r="G393" s="9"/>
       <c r="H393" s="9"/>
       <c r="I393" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J393" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K393" s="11"/>
@@ -10339,11 +10438,11 @@
       <c r="G394" s="9"/>
       <c r="H394" s="9"/>
       <c r="I394" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J394" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K394" s="11"/>
@@ -10361,11 +10460,11 @@
       <c r="G395" s="9"/>
       <c r="H395" s="9"/>
       <c r="I395" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J395" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K395" s="11"/>
@@ -10383,11 +10482,11 @@
       <c r="G396" s="9"/>
       <c r="H396" s="9"/>
       <c r="I396" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J396" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K396" s="11"/>
@@ -10405,11 +10504,11 @@
       <c r="G397" s="9"/>
       <c r="H397" s="9"/>
       <c r="I397" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J397" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K397" s="11"/>
@@ -10427,11 +10526,11 @@
       <c r="G398" s="9"/>
       <c r="H398" s="9"/>
       <c r="I398" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J398" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K398" s="11"/>
@@ -10449,11 +10548,11 @@
       <c r="G399" s="9"/>
       <c r="H399" s="9"/>
       <c r="I399" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J399" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K399" s="11"/>
@@ -10471,11 +10570,11 @@
       <c r="G400" s="9"/>
       <c r="H400" s="9"/>
       <c r="I400" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J400" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K400" s="11"/>
@@ -10493,11 +10592,11 @@
       <c r="G401" s="9"/>
       <c r="H401" s="9"/>
       <c r="I401" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J401" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K401" s="11"/>

--- a/12626731.xlsx
+++ b/12626731.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHIVEN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57D6BFD9-F7A8-410D-8910-5DF3CB087B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA5829E7-E615-4049-8A22-6FB29237E6C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2662,27 +2662,51 @@
         <v>73</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="8"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="11"/>
-      <c r="L41" s="11"/>
-      <c r="M41" s="11"/>
-      <c r="N41" s="12"/>
+    <row r="41" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B41" s="14">
+        <v>400</v>
+      </c>
+      <c r="C41" s="14">
+        <v>0</v>
+      </c>
+      <c r="D41" s="14">
+        <v>60</v>
+      </c>
+      <c r="E41" s="14">
+        <v>20</v>
+      </c>
+      <c r="F41" s="14">
+        <v>300</v>
+      </c>
+      <c r="G41" s="14">
+        <v>6</v>
+      </c>
+      <c r="H41" s="14">
+        <v>270</v>
+      </c>
+      <c r="I41" s="15">
+        <f t="shared" ref="I41" si="54">IF(SUM(B41:F41,H41)=0,"",SUM(B41:F41,H41))</f>
+        <v>1050</v>
+      </c>
+      <c r="J41" s="15">
+        <f t="shared" ref="J41" si="55">IF(I41="","",1440-I41)</f>
+        <v>390</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="8"/>
@@ -3310,11 +3334,11 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
       <c r="I70" s="10" t="str">
-        <f t="shared" ref="I70:I133" si="54">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="56">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="10" t="str">
-        <f t="shared" ref="J70:J133" si="55">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="57">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="11"/>
@@ -3332,11 +3356,11 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
       <c r="I71" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J71" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K71" s="11"/>
@@ -3354,11 +3378,11 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
       <c r="I72" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J72" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K72" s="11"/>
@@ -3376,11 +3400,11 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
       <c r="I73" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J73" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K73" s="11"/>
@@ -3398,11 +3422,11 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
       <c r="I74" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J74" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K74" s="11"/>
@@ -3420,11 +3444,11 @@
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="I75" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J75" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K75" s="11"/>
@@ -3442,11 +3466,11 @@
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="I76" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J76" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K76" s="11"/>
@@ -3464,11 +3488,11 @@
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J77" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K77" s="11"/>
@@ -3486,11 +3510,11 @@
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J78" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K78" s="11"/>
@@ -3508,11 +3532,11 @@
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J79" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K79" s="11"/>
@@ -3530,11 +3554,11 @@
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J80" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K80" s="11"/>
@@ -3552,11 +3576,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J81" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -3574,11 +3598,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J82" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -3596,11 +3620,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J83" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -3618,11 +3642,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J84" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -3640,11 +3664,11 @@
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
       <c r="I85" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J85" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K85" s="11"/>
@@ -3662,11 +3686,11 @@
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J86" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K86" s="11"/>
@@ -3684,11 +3708,11 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
       <c r="I87" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J87" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K87" s="11"/>
@@ -3706,11 +3730,11 @@
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
       <c r="I88" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J88" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K88" s="11"/>
@@ -3728,11 +3752,11 @@
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
       <c r="I89" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J89" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K89" s="11"/>
@@ -3750,11 +3774,11 @@
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
       <c r="I90" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J90" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K90" s="11"/>
@@ -3772,11 +3796,11 @@
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
       <c r="I91" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J91" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K91" s="11"/>
@@ -3794,11 +3818,11 @@
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
       <c r="I92" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J92" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K92" s="11"/>
@@ -3816,11 +3840,11 @@
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
       <c r="I93" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J93" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K93" s="11"/>
@@ -3838,11 +3862,11 @@
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
       <c r="I94" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J94" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K94" s="11"/>
@@ -3860,11 +3884,11 @@
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
       <c r="I95" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J95" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K95" s="11"/>
@@ -3882,11 +3906,11 @@
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
       <c r="I96" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J96" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K96" s="11"/>
@@ -3904,11 +3928,11 @@
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J97" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K97" s="11"/>
@@ -3926,11 +3950,11 @@
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
       <c r="I98" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J98" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K98" s="11"/>
@@ -3948,11 +3972,11 @@
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
       <c r="I99" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J99" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K99" s="11"/>
@@ -3970,11 +3994,11 @@
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
       <c r="I100" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J100" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K100" s="11"/>
@@ -3992,11 +4016,11 @@
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
       <c r="I101" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J101" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K101" s="11"/>
@@ -4014,11 +4038,11 @@
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
       <c r="I102" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J102" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K102" s="11"/>
@@ -4036,11 +4060,11 @@
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J103" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K103" s="11"/>
@@ -4058,11 +4082,11 @@
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
       <c r="I104" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J104" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K104" s="11"/>
@@ -4080,11 +4104,11 @@
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
       <c r="I105" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J105" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K105" s="11"/>
@@ -4102,11 +4126,11 @@
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
       <c r="I106" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J106" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K106" s="11"/>
@@ -4124,11 +4148,11 @@
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J107" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K107" s="11"/>
@@ -4146,11 +4170,11 @@
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
       <c r="I108" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J108" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K108" s="11"/>
@@ -4168,11 +4192,11 @@
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J109" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K109" s="11"/>
@@ -4190,11 +4214,11 @@
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J110" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K110" s="11"/>
@@ -4212,11 +4236,11 @@
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J111" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K111" s="11"/>
@@ -4234,11 +4258,11 @@
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J112" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K112" s="11"/>
@@ -4256,11 +4280,11 @@
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J113" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K113" s="11"/>
@@ -4278,11 +4302,11 @@
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
       <c r="I114" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J114" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K114" s="11"/>
@@ -4300,11 +4324,11 @@
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
       <c r="I115" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J115" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K115" s="11"/>
@@ -4322,11 +4346,11 @@
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
       <c r="I116" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J116" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K116" s="11"/>
@@ -4344,11 +4368,11 @@
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
       <c r="I117" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J117" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K117" s="11"/>
@@ -4366,11 +4390,11 @@
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J118" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K118" s="11"/>
@@ -4388,11 +4412,11 @@
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
       <c r="I119" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J119" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K119" s="11"/>
@@ -4410,11 +4434,11 @@
       <c r="G120" s="9"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J120" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K120" s="11"/>
@@ -4432,11 +4456,11 @@
       <c r="G121" s="9"/>
       <c r="H121" s="9"/>
       <c r="I121" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J121" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K121" s="11"/>
@@ -4454,11 +4478,11 @@
       <c r="G122" s="9"/>
       <c r="H122" s="9"/>
       <c r="I122" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J122" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K122" s="11"/>
@@ -4476,11 +4500,11 @@
       <c r="G123" s="9"/>
       <c r="H123" s="9"/>
       <c r="I123" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J123" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K123" s="11"/>
@@ -4498,11 +4522,11 @@
       <c r="G124" s="9"/>
       <c r="H124" s="9"/>
       <c r="I124" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J124" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K124" s="11"/>
@@ -4520,11 +4544,11 @@
       <c r="G125" s="9"/>
       <c r="H125" s="9"/>
       <c r="I125" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J125" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K125" s="11"/>
@@ -4542,11 +4566,11 @@
       <c r="G126" s="9"/>
       <c r="H126" s="9"/>
       <c r="I126" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J126" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K126" s="11"/>
@@ -4564,11 +4588,11 @@
       <c r="G127" s="9"/>
       <c r="H127" s="9"/>
       <c r="I127" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J127" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K127" s="11"/>
@@ -4586,11 +4610,11 @@
       <c r="G128" s="9"/>
       <c r="H128" s="9"/>
       <c r="I128" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J128" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K128" s="11"/>
@@ -4608,11 +4632,11 @@
       <c r="G129" s="9"/>
       <c r="H129" s="9"/>
       <c r="I129" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J129" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K129" s="11"/>
@@ -4630,11 +4654,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -4652,11 +4676,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -4674,11 +4698,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -4696,11 +4720,11 @@
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
       <c r="I133" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J133" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K133" s="11"/>
@@ -4718,11 +4742,11 @@
       <c r="G134" s="9"/>
       <c r="H134" s="9"/>
       <c r="I134" s="10" t="str">
-        <f t="shared" ref="I134:I197" si="56">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="58">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="10" t="str">
-        <f t="shared" ref="J134:J197" si="57">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="59">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="11"/>
@@ -4740,11 +4764,11 @@
       <c r="G135" s="9"/>
       <c r="H135" s="9"/>
       <c r="I135" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J135" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K135" s="11"/>
@@ -4762,11 +4786,11 @@
       <c r="G136" s="9"/>
       <c r="H136" s="9"/>
       <c r="I136" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J136" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K136" s="11"/>
@@ -4784,11 +4808,11 @@
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
       <c r="I137" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J137" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K137" s="11"/>
@@ -4806,11 +4830,11 @@
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J138" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K138" s="11"/>
@@ -4828,11 +4852,11 @@
       <c r="G139" s="9"/>
       <c r="H139" s="9"/>
       <c r="I139" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J139" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K139" s="11"/>
@@ -4850,11 +4874,11 @@
       <c r="G140" s="9"/>
       <c r="H140" s="9"/>
       <c r="I140" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J140" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K140" s="11"/>
@@ -4872,11 +4896,11 @@
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
       <c r="I141" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J141" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K141" s="11"/>
@@ -4894,11 +4918,11 @@
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J142" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K142" s="11"/>
@@ -4916,11 +4940,11 @@
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
       <c r="I143" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J143" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K143" s="11"/>
@@ -4938,11 +4962,11 @@
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
       <c r="I144" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J144" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K144" s="11"/>
@@ -4960,11 +4984,11 @@
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J145" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K145" s="11"/>
@@ -4982,11 +5006,11 @@
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J146" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K146" s="11"/>
@@ -5004,11 +5028,11 @@
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
       <c r="I147" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J147" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K147" s="11"/>
@@ -5026,11 +5050,11 @@
       <c r="G148" s="9"/>
       <c r="H148" s="9"/>
       <c r="I148" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J148" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K148" s="11"/>
@@ -5048,11 +5072,11 @@
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
       <c r="I149" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J149" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K149" s="11"/>
@@ -5070,11 +5094,11 @@
       <c r="G150" s="9"/>
       <c r="H150" s="9"/>
       <c r="I150" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J150" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K150" s="11"/>
@@ -5092,11 +5116,11 @@
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
       <c r="I151" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J151" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K151" s="11"/>
@@ -5114,11 +5138,11 @@
       <c r="G152" s="9"/>
       <c r="H152" s="9"/>
       <c r="I152" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J152" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K152" s="11"/>
@@ -5136,11 +5160,11 @@
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
       <c r="I153" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J153" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K153" s="11"/>
@@ -5158,11 +5182,11 @@
       <c r="G154" s="9"/>
       <c r="H154" s="9"/>
       <c r="I154" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J154" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K154" s="11"/>
@@ -5180,11 +5204,11 @@
       <c r="G155" s="9"/>
       <c r="H155" s="9"/>
       <c r="I155" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J155" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K155" s="11"/>
@@ -5202,11 +5226,11 @@
       <c r="G156" s="9"/>
       <c r="H156" s="9"/>
       <c r="I156" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J156" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K156" s="11"/>
@@ -5224,11 +5248,11 @@
       <c r="G157" s="9"/>
       <c r="H157" s="9"/>
       <c r="I157" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J157" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K157" s="11"/>
@@ -5246,11 +5270,11 @@
       <c r="G158" s="9"/>
       <c r="H158" s="9"/>
       <c r="I158" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J158" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K158" s="11"/>
@@ -5268,11 +5292,11 @@
       <c r="G159" s="9"/>
       <c r="H159" s="9"/>
       <c r="I159" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J159" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K159" s="11"/>
@@ -5290,11 +5314,11 @@
       <c r="G160" s="9"/>
       <c r="H160" s="9"/>
       <c r="I160" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J160" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K160" s="11"/>
@@ -5312,11 +5336,11 @@
       <c r="G161" s="9"/>
       <c r="H161" s="9"/>
       <c r="I161" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J161" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K161" s="11"/>
@@ -5334,11 +5358,11 @@
       <c r="G162" s="9"/>
       <c r="H162" s="9"/>
       <c r="I162" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J162" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K162" s="11"/>
@@ -5356,11 +5380,11 @@
       <c r="G163" s="9"/>
       <c r="H163" s="9"/>
       <c r="I163" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J163" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K163" s="11"/>
@@ -5378,11 +5402,11 @@
       <c r="G164" s="9"/>
       <c r="H164" s="9"/>
       <c r="I164" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J164" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K164" s="11"/>
@@ -5400,11 +5424,11 @@
       <c r="G165" s="9"/>
       <c r="H165" s="9"/>
       <c r="I165" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J165" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K165" s="11"/>
@@ -5422,11 +5446,11 @@
       <c r="G166" s="9"/>
       <c r="H166" s="9"/>
       <c r="I166" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J166" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K166" s="11"/>
@@ -5444,11 +5468,11 @@
       <c r="G167" s="9"/>
       <c r="H167" s="9"/>
       <c r="I167" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J167" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K167" s="11"/>
@@ -5466,11 +5490,11 @@
       <c r="G168" s="9"/>
       <c r="H168" s="9"/>
       <c r="I168" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J168" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K168" s="11"/>
@@ -5488,11 +5512,11 @@
       <c r="G169" s="9"/>
       <c r="H169" s="9"/>
       <c r="I169" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J169" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K169" s="11"/>
@@ -5510,11 +5534,11 @@
       <c r="G170" s="9"/>
       <c r="H170" s="9"/>
       <c r="I170" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J170" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K170" s="11"/>
@@ -5532,11 +5556,11 @@
       <c r="G171" s="9"/>
       <c r="H171" s="9"/>
       <c r="I171" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J171" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K171" s="11"/>
@@ -5554,11 +5578,11 @@
       <c r="G172" s="9"/>
       <c r="H172" s="9"/>
       <c r="I172" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J172" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K172" s="11"/>
@@ -5576,11 +5600,11 @@
       <c r="G173" s="9"/>
       <c r="H173" s="9"/>
       <c r="I173" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J173" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K173" s="11"/>
@@ -5598,11 +5622,11 @@
       <c r="G174" s="9"/>
       <c r="H174" s="9"/>
       <c r="I174" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J174" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K174" s="11"/>
@@ -5620,11 +5644,11 @@
       <c r="G175" s="9"/>
       <c r="H175" s="9"/>
       <c r="I175" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J175" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K175" s="11"/>
@@ -5642,11 +5666,11 @@
       <c r="G176" s="9"/>
       <c r="H176" s="9"/>
       <c r="I176" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J176" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K176" s="11"/>
@@ -5664,11 +5688,11 @@
       <c r="G177" s="9"/>
       <c r="H177" s="9"/>
       <c r="I177" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J177" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K177" s="11"/>
@@ -5686,11 +5710,11 @@
       <c r="G178" s="9"/>
       <c r="H178" s="9"/>
       <c r="I178" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J178" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K178" s="11"/>
@@ -5708,11 +5732,11 @@
       <c r="G179" s="9"/>
       <c r="H179" s="9"/>
       <c r="I179" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J179" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K179" s="11"/>
@@ -5730,11 +5754,11 @@
       <c r="G180" s="9"/>
       <c r="H180" s="9"/>
       <c r="I180" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J180" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K180" s="11"/>
@@ -5752,11 +5776,11 @@
       <c r="G181" s="9"/>
       <c r="H181" s="9"/>
       <c r="I181" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J181" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K181" s="11"/>
@@ -5774,11 +5798,11 @@
       <c r="G182" s="9"/>
       <c r="H182" s="9"/>
       <c r="I182" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J182" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K182" s="11"/>
@@ -5796,11 +5820,11 @@
       <c r="G183" s="9"/>
       <c r="H183" s="9"/>
       <c r="I183" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J183" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K183" s="11"/>
@@ -5818,11 +5842,11 @@
       <c r="G184" s="9"/>
       <c r="H184" s="9"/>
       <c r="I184" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J184" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K184" s="11"/>
@@ -5840,11 +5864,11 @@
       <c r="G185" s="9"/>
       <c r="H185" s="9"/>
       <c r="I185" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J185" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K185" s="11"/>
@@ -5862,11 +5886,11 @@
       <c r="G186" s="9"/>
       <c r="H186" s="9"/>
       <c r="I186" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J186" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K186" s="11"/>
@@ -5884,11 +5908,11 @@
       <c r="G187" s="9"/>
       <c r="H187" s="9"/>
       <c r="I187" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J187" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K187" s="11"/>
@@ -5906,11 +5930,11 @@
       <c r="G188" s="9"/>
       <c r="H188" s="9"/>
       <c r="I188" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J188" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K188" s="11"/>
@@ -5928,11 +5952,11 @@
       <c r="G189" s="9"/>
       <c r="H189" s="9"/>
       <c r="I189" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J189" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K189" s="11"/>
@@ -5950,11 +5974,11 @@
       <c r="G190" s="9"/>
       <c r="H190" s="9"/>
       <c r="I190" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J190" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K190" s="11"/>
@@ -5972,11 +5996,11 @@
       <c r="G191" s="9"/>
       <c r="H191" s="9"/>
       <c r="I191" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J191" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K191" s="11"/>
@@ -5994,11 +6018,11 @@
       <c r="G192" s="9"/>
       <c r="H192" s="9"/>
       <c r="I192" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J192" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K192" s="11"/>
@@ -6016,11 +6040,11 @@
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J193" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K193" s="11"/>
@@ -6038,11 +6062,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -6060,11 +6084,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -6082,11 +6106,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -6104,11 +6128,11 @@
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J197" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K197" s="11"/>
@@ -6126,11 +6150,11 @@
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
       <c r="I198" s="10" t="str">
-        <f t="shared" ref="I198:I261" si="58">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="60">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="10" t="str">
-        <f t="shared" ref="J198:J261" si="59">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="61">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="11"/>
@@ -6148,11 +6172,11 @@
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
       <c r="I199" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J199" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K199" s="11"/>
@@ -6170,11 +6194,11 @@
       <c r="G200" s="9"/>
       <c r="H200" s="9"/>
       <c r="I200" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J200" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K200" s="11"/>
@@ -6192,11 +6216,11 @@
       <c r="G201" s="9"/>
       <c r="H201" s="9"/>
       <c r="I201" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J201" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K201" s="11"/>
@@ -6214,11 +6238,11 @@
       <c r="G202" s="9"/>
       <c r="H202" s="9"/>
       <c r="I202" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J202" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K202" s="11"/>
@@ -6236,11 +6260,11 @@
       <c r="G203" s="9"/>
       <c r="H203" s="9"/>
       <c r="I203" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J203" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K203" s="11"/>
@@ -6258,11 +6282,11 @@
       <c r="G204" s="9"/>
       <c r="H204" s="9"/>
       <c r="I204" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J204" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K204" s="11"/>
@@ -6280,11 +6304,11 @@
       <c r="G205" s="9"/>
       <c r="H205" s="9"/>
       <c r="I205" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J205" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K205" s="11"/>
@@ -6302,11 +6326,11 @@
       <c r="G206" s="9"/>
       <c r="H206" s="9"/>
       <c r="I206" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J206" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K206" s="11"/>
@@ -6324,11 +6348,11 @@
       <c r="G207" s="9"/>
       <c r="H207" s="9"/>
       <c r="I207" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J207" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K207" s="11"/>
@@ -6346,11 +6370,11 @@
       <c r="G208" s="9"/>
       <c r="H208" s="9"/>
       <c r="I208" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J208" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K208" s="11"/>
@@ -6368,11 +6392,11 @@
       <c r="G209" s="9"/>
       <c r="H209" s="9"/>
       <c r="I209" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J209" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K209" s="11"/>
@@ -6390,11 +6414,11 @@
       <c r="G210" s="9"/>
       <c r="H210" s="9"/>
       <c r="I210" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J210" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K210" s="11"/>
@@ -6412,11 +6436,11 @@
       <c r="G211" s="9"/>
       <c r="H211" s="9"/>
       <c r="I211" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J211" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K211" s="11"/>
@@ -6434,11 +6458,11 @@
       <c r="G212" s="9"/>
       <c r="H212" s="9"/>
       <c r="I212" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J212" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K212" s="11"/>
@@ -6456,11 +6480,11 @@
       <c r="G213" s="9"/>
       <c r="H213" s="9"/>
       <c r="I213" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J213" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K213" s="11"/>
@@ -6478,11 +6502,11 @@
       <c r="G214" s="9"/>
       <c r="H214" s="9"/>
       <c r="I214" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J214" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K214" s="11"/>
@@ -6500,11 +6524,11 @@
       <c r="G215" s="9"/>
       <c r="H215" s="9"/>
       <c r="I215" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J215" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K215" s="11"/>
@@ -6522,11 +6546,11 @@
       <c r="G216" s="9"/>
       <c r="H216" s="9"/>
       <c r="I216" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J216" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K216" s="11"/>
@@ -6544,11 +6568,11 @@
       <c r="G217" s="9"/>
       <c r="H217" s="9"/>
       <c r="I217" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J217" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K217" s="11"/>
@@ -6566,11 +6590,11 @@
       <c r="G218" s="9"/>
       <c r="H218" s="9"/>
       <c r="I218" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J218" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K218" s="11"/>
@@ -6588,11 +6612,11 @@
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
       <c r="I219" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J219" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K219" s="11"/>
@@ -6610,11 +6634,11 @@
       <c r="G220" s="9"/>
       <c r="H220" s="9"/>
       <c r="I220" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J220" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K220" s="11"/>
@@ -6632,11 +6656,11 @@
       <c r="G221" s="9"/>
       <c r="H221" s="9"/>
       <c r="I221" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J221" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K221" s="11"/>
@@ -6654,11 +6678,11 @@
       <c r="G222" s="9"/>
       <c r="H222" s="9"/>
       <c r="I222" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J222" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K222" s="11"/>
@@ -6676,11 +6700,11 @@
       <c r="G223" s="9"/>
       <c r="H223" s="9"/>
       <c r="I223" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J223" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K223" s="11"/>
@@ -6698,11 +6722,11 @@
       <c r="G224" s="9"/>
       <c r="H224" s="9"/>
       <c r="I224" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J224" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K224" s="11"/>
@@ -6720,11 +6744,11 @@
       <c r="G225" s="9"/>
       <c r="H225" s="9"/>
       <c r="I225" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J225" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K225" s="11"/>
@@ -6742,11 +6766,11 @@
       <c r="G226" s="9"/>
       <c r="H226" s="9"/>
       <c r="I226" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J226" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K226" s="11"/>
@@ -6764,11 +6788,11 @@
       <c r="G227" s="9"/>
       <c r="H227" s="9"/>
       <c r="I227" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J227" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K227" s="11"/>
@@ -6786,11 +6810,11 @@
       <c r="G228" s="9"/>
       <c r="H228" s="9"/>
       <c r="I228" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J228" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K228" s="11"/>
@@ -6808,11 +6832,11 @@
       <c r="G229" s="9"/>
       <c r="H229" s="9"/>
       <c r="I229" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J229" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K229" s="11"/>
@@ -6830,11 +6854,11 @@
       <c r="G230" s="9"/>
       <c r="H230" s="9"/>
       <c r="I230" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J230" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K230" s="11"/>
@@ -6852,11 +6876,11 @@
       <c r="G231" s="9"/>
       <c r="H231" s="9"/>
       <c r="I231" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J231" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K231" s="11"/>
@@ -6874,11 +6898,11 @@
       <c r="G232" s="9"/>
       <c r="H232" s="9"/>
       <c r="I232" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J232" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K232" s="11"/>
@@ -6896,11 +6920,11 @@
       <c r="G233" s="9"/>
       <c r="H233" s="9"/>
       <c r="I233" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J233" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K233" s="11"/>
@@ -6918,11 +6942,11 @@
       <c r="G234" s="9"/>
       <c r="H234" s="9"/>
       <c r="I234" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J234" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K234" s="11"/>
@@ -6940,11 +6964,11 @@
       <c r="G235" s="9"/>
       <c r="H235" s="9"/>
       <c r="I235" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J235" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K235" s="11"/>
@@ -6962,11 +6986,11 @@
       <c r="G236" s="9"/>
       <c r="H236" s="9"/>
       <c r="I236" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J236" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K236" s="11"/>
@@ -6984,11 +7008,11 @@
       <c r="G237" s="9"/>
       <c r="H237" s="9"/>
       <c r="I237" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J237" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K237" s="11"/>
@@ -7006,11 +7030,11 @@
       <c r="G238" s="9"/>
       <c r="H238" s="9"/>
       <c r="I238" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J238" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K238" s="11"/>
@@ -7028,11 +7052,11 @@
       <c r="G239" s="9"/>
       <c r="H239" s="9"/>
       <c r="I239" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J239" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K239" s="11"/>
@@ -7050,11 +7074,11 @@
       <c r="G240" s="9"/>
       <c r="H240" s="9"/>
       <c r="I240" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J240" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K240" s="11"/>
@@ -7072,11 +7096,11 @@
       <c r="G241" s="9"/>
       <c r="H241" s="9"/>
       <c r="I241" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J241" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K241" s="11"/>
@@ -7094,11 +7118,11 @@
       <c r="G242" s="9"/>
       <c r="H242" s="9"/>
       <c r="I242" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J242" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K242" s="11"/>
@@ -7116,11 +7140,11 @@
       <c r="G243" s="9"/>
       <c r="H243" s="9"/>
       <c r="I243" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J243" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K243" s="11"/>
@@ -7138,11 +7162,11 @@
       <c r="G244" s="9"/>
       <c r="H244" s="9"/>
       <c r="I244" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J244" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K244" s="11"/>
@@ -7160,11 +7184,11 @@
       <c r="G245" s="9"/>
       <c r="H245" s="9"/>
       <c r="I245" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J245" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K245" s="11"/>
@@ -7182,11 +7206,11 @@
       <c r="G246" s="9"/>
       <c r="H246" s="9"/>
       <c r="I246" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J246" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K246" s="11"/>
@@ -7204,11 +7228,11 @@
       <c r="G247" s="9"/>
       <c r="H247" s="9"/>
       <c r="I247" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J247" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K247" s="11"/>
@@ -7226,11 +7250,11 @@
       <c r="G248" s="9"/>
       <c r="H248" s="9"/>
       <c r="I248" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J248" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K248" s="11"/>
@@ -7248,11 +7272,11 @@
       <c r="G249" s="9"/>
       <c r="H249" s="9"/>
       <c r="I249" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J249" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K249" s="11"/>
@@ -7270,11 +7294,11 @@
       <c r="G250" s="9"/>
       <c r="H250" s="9"/>
       <c r="I250" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J250" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K250" s="11"/>
@@ -7292,11 +7316,11 @@
       <c r="G251" s="9"/>
       <c r="H251" s="9"/>
       <c r="I251" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J251" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K251" s="11"/>
@@ -7314,11 +7338,11 @@
       <c r="G252" s="9"/>
       <c r="H252" s="9"/>
       <c r="I252" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J252" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K252" s="11"/>
@@ -7336,11 +7360,11 @@
       <c r="G253" s="9"/>
       <c r="H253" s="9"/>
       <c r="I253" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J253" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K253" s="11"/>
@@ -7358,11 +7382,11 @@
       <c r="G254" s="9"/>
       <c r="H254" s="9"/>
       <c r="I254" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J254" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K254" s="11"/>
@@ -7380,11 +7404,11 @@
       <c r="G255" s="9"/>
       <c r="H255" s="9"/>
       <c r="I255" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J255" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K255" s="11"/>
@@ -7402,11 +7426,11 @@
       <c r="G256" s="9"/>
       <c r="H256" s="9"/>
       <c r="I256" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J256" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K256" s="11"/>
@@ -7424,11 +7448,11 @@
       <c r="G257" s="9"/>
       <c r="H257" s="9"/>
       <c r="I257" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J257" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K257" s="11"/>
@@ -7446,11 +7470,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -7468,11 +7492,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -7490,11 +7514,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -7512,11 +7536,11 @@
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
       <c r="I261" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J261" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K261" s="11"/>
@@ -7534,11 +7558,11 @@
       <c r="G262" s="9"/>
       <c r="H262" s="9"/>
       <c r="I262" s="10" t="str">
-        <f t="shared" ref="I262:I325" si="60">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="62">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="10" t="str">
-        <f t="shared" ref="J262:J325" si="61">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="63">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="11"/>
@@ -7556,11 +7580,11 @@
       <c r="G263" s="9"/>
       <c r="H263" s="9"/>
       <c r="I263" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J263" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K263" s="11"/>
@@ -7578,11 +7602,11 @@
       <c r="G264" s="9"/>
       <c r="H264" s="9"/>
       <c r="I264" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J264" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K264" s="11"/>
@@ -7600,11 +7624,11 @@
       <c r="G265" s="9"/>
       <c r="H265" s="9"/>
       <c r="I265" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J265" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K265" s="11"/>
@@ -7622,11 +7646,11 @@
       <c r="G266" s="9"/>
       <c r="H266" s="9"/>
       <c r="I266" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J266" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K266" s="11"/>
@@ -7644,11 +7668,11 @@
       <c r="G267" s="9"/>
       <c r="H267" s="9"/>
       <c r="I267" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J267" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K267" s="11"/>
@@ -7666,11 +7690,11 @@
       <c r="G268" s="9"/>
       <c r="H268" s="9"/>
       <c r="I268" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J268" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K268" s="11"/>
@@ -7688,11 +7712,11 @@
       <c r="G269" s="9"/>
       <c r="H269" s="9"/>
       <c r="I269" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J269" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K269" s="11"/>
@@ -7710,11 +7734,11 @@
       <c r="G270" s="9"/>
       <c r="H270" s="9"/>
       <c r="I270" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J270" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K270" s="11"/>
@@ -7732,11 +7756,11 @@
       <c r="G271" s="9"/>
       <c r="H271" s="9"/>
       <c r="I271" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J271" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K271" s="11"/>
@@ -7754,11 +7778,11 @@
       <c r="G272" s="9"/>
       <c r="H272" s="9"/>
       <c r="I272" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J272" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K272" s="11"/>
@@ -7776,11 +7800,11 @@
       <c r="G273" s="9"/>
       <c r="H273" s="9"/>
       <c r="I273" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J273" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K273" s="11"/>
@@ -7798,11 +7822,11 @@
       <c r="G274" s="9"/>
       <c r="H274" s="9"/>
       <c r="I274" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J274" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K274" s="11"/>
@@ -7820,11 +7844,11 @@
       <c r="G275" s="9"/>
       <c r="H275" s="9"/>
       <c r="I275" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J275" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K275" s="11"/>
@@ -7842,11 +7866,11 @@
       <c r="G276" s="9"/>
       <c r="H276" s="9"/>
       <c r="I276" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J276" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K276" s="11"/>
@@ -7864,11 +7888,11 @@
       <c r="G277" s="9"/>
       <c r="H277" s="9"/>
       <c r="I277" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J277" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K277" s="11"/>
@@ -7886,11 +7910,11 @@
       <c r="G278" s="9"/>
       <c r="H278" s="9"/>
       <c r="I278" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J278" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K278" s="11"/>
@@ -7908,11 +7932,11 @@
       <c r="G279" s="9"/>
       <c r="H279" s="9"/>
       <c r="I279" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J279" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K279" s="11"/>
@@ -7930,11 +7954,11 @@
       <c r="G280" s="9"/>
       <c r="H280" s="9"/>
       <c r="I280" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J280" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K280" s="11"/>
@@ -7952,11 +7976,11 @@
       <c r="G281" s="9"/>
       <c r="H281" s="9"/>
       <c r="I281" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J281" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K281" s="11"/>
@@ -7974,11 +7998,11 @@
       <c r="G282" s="9"/>
       <c r="H282" s="9"/>
       <c r="I282" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J282" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K282" s="11"/>
@@ -7996,11 +8020,11 @@
       <c r="G283" s="9"/>
       <c r="H283" s="9"/>
       <c r="I283" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J283" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K283" s="11"/>
@@ -8018,11 +8042,11 @@
       <c r="G284" s="9"/>
       <c r="H284" s="9"/>
       <c r="I284" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J284" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K284" s="11"/>
@@ -8040,11 +8064,11 @@
       <c r="G285" s="9"/>
       <c r="H285" s="9"/>
       <c r="I285" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J285" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K285" s="11"/>
@@ -8062,11 +8086,11 @@
       <c r="G286" s="9"/>
       <c r="H286" s="9"/>
       <c r="I286" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J286" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K286" s="11"/>
@@ -8084,11 +8108,11 @@
       <c r="G287" s="9"/>
       <c r="H287" s="9"/>
       <c r="I287" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J287" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K287" s="11"/>
@@ -8106,11 +8130,11 @@
       <c r="G288" s="9"/>
       <c r="H288" s="9"/>
       <c r="I288" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J288" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K288" s="11"/>
@@ -8128,11 +8152,11 @@
       <c r="G289" s="9"/>
       <c r="H289" s="9"/>
       <c r="I289" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J289" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K289" s="11"/>
@@ -8150,11 +8174,11 @@
       <c r="G290" s="9"/>
       <c r="H290" s="9"/>
       <c r="I290" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J290" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K290" s="11"/>
@@ -8172,11 +8196,11 @@
       <c r="G291" s="9"/>
       <c r="H291" s="9"/>
       <c r="I291" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J291" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K291" s="11"/>
@@ -8194,11 +8218,11 @@
       <c r="G292" s="9"/>
       <c r="H292" s="9"/>
       <c r="I292" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J292" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K292" s="11"/>
@@ -8216,11 +8240,11 @@
       <c r="G293" s="9"/>
       <c r="H293" s="9"/>
       <c r="I293" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J293" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K293" s="11"/>
@@ -8238,11 +8262,11 @@
       <c r="G294" s="9"/>
       <c r="H294" s="9"/>
       <c r="I294" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J294" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K294" s="11"/>
@@ -8260,11 +8284,11 @@
       <c r="G295" s="9"/>
       <c r="H295" s="9"/>
       <c r="I295" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J295" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K295" s="11"/>
@@ -8282,11 +8306,11 @@
       <c r="G296" s="9"/>
       <c r="H296" s="9"/>
       <c r="I296" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J296" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K296" s="11"/>
@@ -8304,11 +8328,11 @@
       <c r="G297" s="9"/>
       <c r="H297" s="9"/>
       <c r="I297" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J297" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K297" s="11"/>
@@ -8326,11 +8350,11 @@
       <c r="G298" s="9"/>
       <c r="H298" s="9"/>
       <c r="I298" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J298" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K298" s="11"/>
@@ -8348,11 +8372,11 @@
       <c r="G299" s="9"/>
       <c r="H299" s="9"/>
       <c r="I299" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J299" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K299" s="11"/>
@@ -8370,11 +8394,11 @@
       <c r="G300" s="9"/>
       <c r="H300" s="9"/>
       <c r="I300" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J300" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K300" s="11"/>
@@ -8392,11 +8416,11 @@
       <c r="G301" s="9"/>
       <c r="H301" s="9"/>
       <c r="I301" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J301" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K301" s="11"/>
@@ -8414,11 +8438,11 @@
       <c r="G302" s="9"/>
       <c r="H302" s="9"/>
       <c r="I302" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J302" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K302" s="11"/>
@@ -8436,11 +8460,11 @@
       <c r="G303" s="9"/>
       <c r="H303" s="9"/>
       <c r="I303" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J303" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K303" s="11"/>
@@ -8458,11 +8482,11 @@
       <c r="G304" s="9"/>
       <c r="H304" s="9"/>
       <c r="I304" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J304" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K304" s="11"/>
@@ -8480,11 +8504,11 @@
       <c r="G305" s="9"/>
       <c r="H305" s="9"/>
       <c r="I305" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J305" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K305" s="11"/>
@@ -8502,11 +8526,11 @@
       <c r="G306" s="9"/>
       <c r="H306" s="9"/>
       <c r="I306" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J306" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K306" s="11"/>
@@ -8524,11 +8548,11 @@
       <c r="G307" s="9"/>
       <c r="H307" s="9"/>
       <c r="I307" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J307" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K307" s="11"/>
@@ -8546,11 +8570,11 @@
       <c r="G308" s="9"/>
       <c r="H308" s="9"/>
       <c r="I308" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J308" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K308" s="11"/>
@@ -8568,11 +8592,11 @@
       <c r="G309" s="9"/>
       <c r="H309" s="9"/>
       <c r="I309" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J309" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K309" s="11"/>
@@ -8590,11 +8614,11 @@
       <c r="G310" s="9"/>
       <c r="H310" s="9"/>
       <c r="I310" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J310" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K310" s="11"/>
@@ -8612,11 +8636,11 @@
       <c r="G311" s="9"/>
       <c r="H311" s="9"/>
       <c r="I311" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J311" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K311" s="11"/>
@@ -8634,11 +8658,11 @@
       <c r="G312" s="9"/>
       <c r="H312" s="9"/>
       <c r="I312" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J312" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K312" s="11"/>
@@ -8656,11 +8680,11 @@
       <c r="G313" s="9"/>
       <c r="H313" s="9"/>
       <c r="I313" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J313" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K313" s="11"/>
@@ -8678,11 +8702,11 @@
       <c r="G314" s="9"/>
       <c r="H314" s="9"/>
       <c r="I314" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J314" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K314" s="11"/>
@@ -8700,11 +8724,11 @@
       <c r="G315" s="9"/>
       <c r="H315" s="9"/>
       <c r="I315" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J315" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K315" s="11"/>
@@ -8722,11 +8746,11 @@
       <c r="G316" s="9"/>
       <c r="H316" s="9"/>
       <c r="I316" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J316" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K316" s="11"/>
@@ -8744,11 +8768,11 @@
       <c r="G317" s="9"/>
       <c r="H317" s="9"/>
       <c r="I317" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J317" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K317" s="11"/>
@@ -8766,11 +8790,11 @@
       <c r="G318" s="9"/>
       <c r="H318" s="9"/>
       <c r="I318" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J318" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K318" s="11"/>
@@ -8788,11 +8812,11 @@
       <c r="G319" s="9"/>
       <c r="H319" s="9"/>
       <c r="I319" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J319" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K319" s="11"/>
@@ -8810,11 +8834,11 @@
       <c r="G320" s="9"/>
       <c r="H320" s="9"/>
       <c r="I320" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J320" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K320" s="11"/>
@@ -8832,11 +8856,11 @@
       <c r="G321" s="9"/>
       <c r="H321" s="9"/>
       <c r="I321" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J321" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K321" s="11"/>
@@ -8854,11 +8878,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -8876,11 +8900,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -8898,11 +8922,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -8920,11 +8944,11 @@
       <c r="G325" s="9"/>
       <c r="H325" s="9"/>
       <c r="I325" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J325" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K325" s="11"/>
@@ -8942,11 +8966,11 @@
       <c r="G326" s="9"/>
       <c r="H326" s="9"/>
       <c r="I326" s="10" t="str">
-        <f t="shared" ref="I326:I389" si="62">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="64">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="10" t="str">
-        <f t="shared" ref="J326:J389" si="63">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="65">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="11"/>
@@ -8964,11 +8988,11 @@
       <c r="G327" s="9"/>
       <c r="H327" s="9"/>
       <c r="I327" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J327" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K327" s="11"/>
@@ -8986,11 +9010,11 @@
       <c r="G328" s="9"/>
       <c r="H328" s="9"/>
       <c r="I328" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J328" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K328" s="11"/>
@@ -9008,11 +9032,11 @@
       <c r="G329" s="9"/>
       <c r="H329" s="9"/>
       <c r="I329" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J329" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K329" s="11"/>
@@ -9030,11 +9054,11 @@
       <c r="G330" s="9"/>
       <c r="H330" s="9"/>
       <c r="I330" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J330" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K330" s="11"/>
@@ -9052,11 +9076,11 @@
       <c r="G331" s="9"/>
       <c r="H331" s="9"/>
       <c r="I331" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J331" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K331" s="11"/>
@@ -9074,11 +9098,11 @@
       <c r="G332" s="9"/>
       <c r="H332" s="9"/>
       <c r="I332" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J332" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K332" s="11"/>
@@ -9096,11 +9120,11 @@
       <c r="G333" s="9"/>
       <c r="H333" s="9"/>
       <c r="I333" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J333" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K333" s="11"/>
@@ -9118,11 +9142,11 @@
       <c r="G334" s="9"/>
       <c r="H334" s="9"/>
       <c r="I334" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J334" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K334" s="11"/>
@@ -9140,11 +9164,11 @@
       <c r="G335" s="9"/>
       <c r="H335" s="9"/>
       <c r="I335" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J335" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K335" s="11"/>
@@ -9162,11 +9186,11 @@
       <c r="G336" s="9"/>
       <c r="H336" s="9"/>
       <c r="I336" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J336" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K336" s="11"/>
@@ -9184,11 +9208,11 @@
       <c r="G337" s="9"/>
       <c r="H337" s="9"/>
       <c r="I337" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J337" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K337" s="11"/>
@@ -9206,11 +9230,11 @@
       <c r="G338" s="9"/>
       <c r="H338" s="9"/>
       <c r="I338" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J338" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K338" s="11"/>
@@ -9228,11 +9252,11 @@
       <c r="G339" s="9"/>
       <c r="H339" s="9"/>
       <c r="I339" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J339" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K339" s="11"/>
@@ -9250,11 +9274,11 @@
       <c r="G340" s="9"/>
       <c r="H340" s="9"/>
       <c r="I340" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J340" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K340" s="11"/>
@@ -9272,11 +9296,11 @@
       <c r="G341" s="9"/>
       <c r="H341" s="9"/>
       <c r="I341" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J341" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K341" s="11"/>
@@ -9294,11 +9318,11 @@
       <c r="G342" s="9"/>
       <c r="H342" s="9"/>
       <c r="I342" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J342" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K342" s="11"/>
@@ -9316,11 +9340,11 @@
       <c r="G343" s="9"/>
       <c r="H343" s="9"/>
       <c r="I343" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J343" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K343" s="11"/>
@@ -9338,11 +9362,11 @@
       <c r="G344" s="9"/>
       <c r="H344" s="9"/>
       <c r="I344" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J344" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K344" s="11"/>
@@ -9360,11 +9384,11 @@
       <c r="G345" s="9"/>
       <c r="H345" s="9"/>
       <c r="I345" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J345" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K345" s="11"/>
@@ -9382,11 +9406,11 @@
       <c r="G346" s="9"/>
       <c r="H346" s="9"/>
       <c r="I346" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J346" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K346" s="11"/>
@@ -9404,11 +9428,11 @@
       <c r="G347" s="9"/>
       <c r="H347" s="9"/>
       <c r="I347" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J347" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K347" s="11"/>
@@ -9426,11 +9450,11 @@
       <c r="G348" s="9"/>
       <c r="H348" s="9"/>
       <c r="I348" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J348" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K348" s="11"/>
@@ -9448,11 +9472,11 @@
       <c r="G349" s="9"/>
       <c r="H349" s="9"/>
       <c r="I349" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J349" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K349" s="11"/>
@@ -9470,11 +9494,11 @@
       <c r="G350" s="9"/>
       <c r="H350" s="9"/>
       <c r="I350" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J350" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K350" s="11"/>
@@ -9492,11 +9516,11 @@
       <c r="G351" s="9"/>
       <c r="H351" s="9"/>
       <c r="I351" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J351" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K351" s="11"/>
@@ -9514,11 +9538,11 @@
       <c r="G352" s="9"/>
       <c r="H352" s="9"/>
       <c r="I352" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J352" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K352" s="11"/>
@@ -9536,11 +9560,11 @@
       <c r="G353" s="9"/>
       <c r="H353" s="9"/>
       <c r="I353" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J353" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K353" s="11"/>
@@ -9558,11 +9582,11 @@
       <c r="G354" s="9"/>
       <c r="H354" s="9"/>
       <c r="I354" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J354" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K354" s="11"/>
@@ -9580,11 +9604,11 @@
       <c r="G355" s="9"/>
       <c r="H355" s="9"/>
       <c r="I355" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J355" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K355" s="11"/>
@@ -9602,11 +9626,11 @@
       <c r="G356" s="9"/>
       <c r="H356" s="9"/>
       <c r="I356" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J356" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K356" s="11"/>
@@ -9624,11 +9648,11 @@
       <c r="G357" s="9"/>
       <c r="H357" s="9"/>
       <c r="I357" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J357" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K357" s="11"/>
@@ -9646,11 +9670,11 @@
       <c r="G358" s="9"/>
       <c r="H358" s="9"/>
       <c r="I358" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J358" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K358" s="11"/>
@@ -9668,11 +9692,11 @@
       <c r="G359" s="9"/>
       <c r="H359" s="9"/>
       <c r="I359" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J359" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K359" s="11"/>
@@ -9690,11 +9714,11 @@
       <c r="G360" s="9"/>
       <c r="H360" s="9"/>
       <c r="I360" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J360" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K360" s="11"/>
@@ -9712,11 +9736,11 @@
       <c r="G361" s="9"/>
       <c r="H361" s="9"/>
       <c r="I361" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J361" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K361" s="11"/>
@@ -9734,11 +9758,11 @@
       <c r="G362" s="9"/>
       <c r="H362" s="9"/>
       <c r="I362" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J362" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K362" s="11"/>
@@ -9756,11 +9780,11 @@
       <c r="G363" s="9"/>
       <c r="H363" s="9"/>
       <c r="I363" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J363" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K363" s="11"/>
@@ -9778,11 +9802,11 @@
       <c r="G364" s="9"/>
       <c r="H364" s="9"/>
       <c r="I364" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J364" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K364" s="11"/>
@@ -9800,11 +9824,11 @@
       <c r="G365" s="9"/>
       <c r="H365" s="9"/>
       <c r="I365" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J365" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K365" s="11"/>
@@ -9822,11 +9846,11 @@
       <c r="G366" s="9"/>
       <c r="H366" s="9"/>
       <c r="I366" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J366" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K366" s="11"/>
@@ -9844,11 +9868,11 @@
       <c r="G367" s="9"/>
       <c r="H367" s="9"/>
       <c r="I367" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J367" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K367" s="11"/>
@@ -9866,11 +9890,11 @@
       <c r="G368" s="9"/>
       <c r="H368" s="9"/>
       <c r="I368" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J368" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K368" s="11"/>
@@ -9888,11 +9912,11 @@
       <c r="G369" s="9"/>
       <c r="H369" s="9"/>
       <c r="I369" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J369" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K369" s="11"/>
@@ -9910,11 +9934,11 @@
       <c r="G370" s="9"/>
       <c r="H370" s="9"/>
       <c r="I370" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J370" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K370" s="11"/>
@@ -9932,11 +9956,11 @@
       <c r="G371" s="9"/>
       <c r="H371" s="9"/>
       <c r="I371" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J371" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K371" s="11"/>
@@ -9954,11 +9978,11 @@
       <c r="G372" s="9"/>
       <c r="H372" s="9"/>
       <c r="I372" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J372" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K372" s="11"/>
@@ -9976,11 +10000,11 @@
       <c r="G373" s="9"/>
       <c r="H373" s="9"/>
       <c r="I373" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J373" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K373" s="11"/>
@@ -9998,11 +10022,11 @@
       <c r="G374" s="9"/>
       <c r="H374" s="9"/>
       <c r="I374" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J374" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K374" s="11"/>
@@ -10020,11 +10044,11 @@
       <c r="G375" s="9"/>
       <c r="H375" s="9"/>
       <c r="I375" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J375" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K375" s="11"/>
@@ -10042,11 +10066,11 @@
       <c r="G376" s="9"/>
       <c r="H376" s="9"/>
       <c r="I376" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J376" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K376" s="11"/>
@@ -10064,11 +10088,11 @@
       <c r="G377" s="9"/>
       <c r="H377" s="9"/>
       <c r="I377" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J377" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K377" s="11"/>
@@ -10086,11 +10110,11 @@
       <c r="G378" s="9"/>
       <c r="H378" s="9"/>
       <c r="I378" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J378" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K378" s="11"/>
@@ -10108,11 +10132,11 @@
       <c r="G379" s="9"/>
       <c r="H379" s="9"/>
       <c r="I379" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J379" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K379" s="11"/>
@@ -10130,11 +10154,11 @@
       <c r="G380" s="9"/>
       <c r="H380" s="9"/>
       <c r="I380" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J380" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K380" s="11"/>
@@ -10152,11 +10176,11 @@
       <c r="G381" s="9"/>
       <c r="H381" s="9"/>
       <c r="I381" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J381" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K381" s="11"/>
@@ -10174,11 +10198,11 @@
       <c r="G382" s="9"/>
       <c r="H382" s="9"/>
       <c r="I382" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J382" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K382" s="11"/>
@@ -10196,11 +10220,11 @@
       <c r="G383" s="9"/>
       <c r="H383" s="9"/>
       <c r="I383" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J383" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K383" s="11"/>
@@ -10218,11 +10242,11 @@
       <c r="G384" s="9"/>
       <c r="H384" s="9"/>
       <c r="I384" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J384" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K384" s="11"/>
@@ -10240,11 +10264,11 @@
       <c r="G385" s="9"/>
       <c r="H385" s="9"/>
       <c r="I385" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J385" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K385" s="11"/>
@@ -10262,11 +10286,11 @@
       <c r="G386" s="9"/>
       <c r="H386" s="9"/>
       <c r="I386" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J386" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K386" s="11"/>
@@ -10284,11 +10308,11 @@
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J387" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K387" s="11"/>
@@ -10306,11 +10330,11 @@
       <c r="G388" s="9"/>
       <c r="H388" s="9"/>
       <c r="I388" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J388" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K388" s="11"/>
@@ -10328,11 +10352,11 @@
       <c r="G389" s="9"/>
       <c r="H389" s="9"/>
       <c r="I389" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J389" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K389" s="11"/>
@@ -10350,11 +10374,11 @@
       <c r="G390" s="9"/>
       <c r="H390" s="9"/>
       <c r="I390" s="10" t="str">
-        <f t="shared" ref="I390:I401" si="64">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="66">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="10" t="str">
-        <f t="shared" ref="J390:J401" si="65">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="67">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="11"/>
@@ -10372,11 +10396,11 @@
       <c r="G391" s="9"/>
       <c r="H391" s="9"/>
       <c r="I391" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J391" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K391" s="11"/>
@@ -10394,11 +10418,11 @@
       <c r="G392" s="9"/>
       <c r="H392" s="9"/>
       <c r="I392" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J392" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K392" s="11"/>
@@ -10416,11 +10440,11 @@
       <c r="G393" s="9"/>
       <c r="H393" s="9"/>
       <c r="I393" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J393" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K393" s="11"/>
@@ -10438,11 +10462,11 @@
       <c r="G394" s="9"/>
       <c r="H394" s="9"/>
       <c r="I394" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J394" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K394" s="11"/>
@@ -10460,11 +10484,11 @@
       <c r="G395" s="9"/>
       <c r="H395" s="9"/>
       <c r="I395" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J395" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K395" s="11"/>
@@ -10482,11 +10506,11 @@
       <c r="G396" s="9"/>
       <c r="H396" s="9"/>
       <c r="I396" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J396" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K396" s="11"/>
@@ -10504,11 +10528,11 @@
       <c r="G397" s="9"/>
       <c r="H397" s="9"/>
       <c r="I397" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J397" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K397" s="11"/>
@@ -10526,11 +10550,11 @@
       <c r="G398" s="9"/>
       <c r="H398" s="9"/>
       <c r="I398" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J398" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K398" s="11"/>
@@ -10548,11 +10572,11 @@
       <c r="G399" s="9"/>
       <c r="H399" s="9"/>
       <c r="I399" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J399" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K399" s="11"/>
@@ -10570,11 +10594,11 @@
       <c r="G400" s="9"/>
       <c r="H400" s="9"/>
       <c r="I400" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J400" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K400" s="11"/>
@@ -10592,11 +10616,11 @@
       <c r="G401" s="9"/>
       <c r="H401" s="9"/>
       <c r="I401" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J401" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K401" s="11"/>

--- a/12626731.xlsx
+++ b/12626731.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHIVEN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA5829E7-E615-4049-8A22-6FB29237E6C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{222F683E-AF70-4786-B208-C236B0C2486A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2709,26 +2709,48 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="8"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="11"/>
-      <c r="L42" s="11"/>
-      <c r="M42" s="11"/>
-      <c r="N42" s="12"/>
+      <c r="A42" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B42" s="14">
+        <v>400</v>
+      </c>
+      <c r="C42" s="14">
+        <v>0</v>
+      </c>
+      <c r="D42" s="14">
+        <v>120</v>
+      </c>
+      <c r="E42" s="14">
+        <v>20</v>
+      </c>
+      <c r="F42" s="14">
+        <v>350</v>
+      </c>
+      <c r="G42" s="14">
+        <v>7</v>
+      </c>
+      <c r="H42" s="14">
+        <v>270</v>
+      </c>
+      <c r="I42" s="15">
+        <f t="shared" ref="I42" si="56">IF(SUM(B42:F42,H42)=0,"",SUM(B42:F42,H42))</f>
+        <v>1160</v>
+      </c>
+      <c r="J42" s="15">
+        <f t="shared" ref="J42" si="57">IF(I42="","",1440-I42)</f>
+        <v>280</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N42" s="17"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="8"/>
@@ -3334,11 +3356,11 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
       <c r="I70" s="10" t="str">
-        <f t="shared" ref="I70:I133" si="56">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="58">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="10" t="str">
-        <f t="shared" ref="J70:J133" si="57">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="59">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="11"/>
@@ -3356,11 +3378,11 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
       <c r="I71" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J71" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K71" s="11"/>
@@ -3378,11 +3400,11 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
       <c r="I72" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J72" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K72" s="11"/>
@@ -3400,11 +3422,11 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
       <c r="I73" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J73" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K73" s="11"/>
@@ -3422,11 +3444,11 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
       <c r="I74" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J74" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K74" s="11"/>
@@ -3444,11 +3466,11 @@
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="I75" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J75" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K75" s="11"/>
@@ -3466,11 +3488,11 @@
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="I76" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J76" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K76" s="11"/>
@@ -3488,11 +3510,11 @@
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J77" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K77" s="11"/>
@@ -3510,11 +3532,11 @@
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J78" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K78" s="11"/>
@@ -3532,11 +3554,11 @@
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J79" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K79" s="11"/>
@@ -3554,11 +3576,11 @@
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J80" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K80" s="11"/>
@@ -3576,11 +3598,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J81" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -3598,11 +3620,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J82" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -3620,11 +3642,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J83" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -3642,11 +3664,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J84" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -3664,11 +3686,11 @@
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
       <c r="I85" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J85" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K85" s="11"/>
@@ -3686,11 +3708,11 @@
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J86" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K86" s="11"/>
@@ -3708,11 +3730,11 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
       <c r="I87" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J87" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K87" s="11"/>
@@ -3730,11 +3752,11 @@
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
       <c r="I88" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J88" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K88" s="11"/>
@@ -3752,11 +3774,11 @@
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
       <c r="I89" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J89" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K89" s="11"/>
@@ -3774,11 +3796,11 @@
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
       <c r="I90" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J90" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K90" s="11"/>
@@ -3796,11 +3818,11 @@
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
       <c r="I91" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J91" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K91" s="11"/>
@@ -3818,11 +3840,11 @@
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
       <c r="I92" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J92" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K92" s="11"/>
@@ -3840,11 +3862,11 @@
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
       <c r="I93" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J93" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K93" s="11"/>
@@ -3862,11 +3884,11 @@
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
       <c r="I94" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J94" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K94" s="11"/>
@@ -3884,11 +3906,11 @@
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
       <c r="I95" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J95" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K95" s="11"/>
@@ -3906,11 +3928,11 @@
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
       <c r="I96" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J96" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K96" s="11"/>
@@ -3928,11 +3950,11 @@
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J97" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K97" s="11"/>
@@ -3950,11 +3972,11 @@
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
       <c r="I98" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J98" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K98" s="11"/>
@@ -3972,11 +3994,11 @@
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
       <c r="I99" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J99" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K99" s="11"/>
@@ -3994,11 +4016,11 @@
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
       <c r="I100" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J100" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K100" s="11"/>
@@ -4016,11 +4038,11 @@
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
       <c r="I101" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J101" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K101" s="11"/>
@@ -4038,11 +4060,11 @@
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
       <c r="I102" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J102" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K102" s="11"/>
@@ -4060,11 +4082,11 @@
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J103" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K103" s="11"/>
@@ -4082,11 +4104,11 @@
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
       <c r="I104" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J104" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K104" s="11"/>
@@ -4104,11 +4126,11 @@
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
       <c r="I105" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J105" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K105" s="11"/>
@@ -4126,11 +4148,11 @@
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
       <c r="I106" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J106" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K106" s="11"/>
@@ -4148,11 +4170,11 @@
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J107" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K107" s="11"/>
@@ -4170,11 +4192,11 @@
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
       <c r="I108" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J108" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K108" s="11"/>
@@ -4192,11 +4214,11 @@
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J109" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K109" s="11"/>
@@ -4214,11 +4236,11 @@
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J110" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K110" s="11"/>
@@ -4236,11 +4258,11 @@
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J111" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K111" s="11"/>
@@ -4258,11 +4280,11 @@
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J112" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K112" s="11"/>
@@ -4280,11 +4302,11 @@
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J113" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K113" s="11"/>
@@ -4302,11 +4324,11 @@
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
       <c r="I114" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J114" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K114" s="11"/>
@@ -4324,11 +4346,11 @@
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
       <c r="I115" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J115" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K115" s="11"/>
@@ -4346,11 +4368,11 @@
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
       <c r="I116" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J116" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K116" s="11"/>
@@ -4368,11 +4390,11 @@
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
       <c r="I117" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J117" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K117" s="11"/>
@@ -4390,11 +4412,11 @@
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J118" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K118" s="11"/>
@@ -4412,11 +4434,11 @@
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
       <c r="I119" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J119" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K119" s="11"/>
@@ -4434,11 +4456,11 @@
       <c r="G120" s="9"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J120" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K120" s="11"/>
@@ -4456,11 +4478,11 @@
       <c r="G121" s="9"/>
       <c r="H121" s="9"/>
       <c r="I121" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J121" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K121" s="11"/>
@@ -4478,11 +4500,11 @@
       <c r="G122" s="9"/>
       <c r="H122" s="9"/>
       <c r="I122" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J122" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K122" s="11"/>
@@ -4500,11 +4522,11 @@
       <c r="G123" s="9"/>
       <c r="H123" s="9"/>
       <c r="I123" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J123" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K123" s="11"/>
@@ -4522,11 +4544,11 @@
       <c r="G124" s="9"/>
       <c r="H124" s="9"/>
       <c r="I124" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J124" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K124" s="11"/>
@@ -4544,11 +4566,11 @@
       <c r="G125" s="9"/>
       <c r="H125" s="9"/>
       <c r="I125" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J125" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K125" s="11"/>
@@ -4566,11 +4588,11 @@
       <c r="G126" s="9"/>
       <c r="H126" s="9"/>
       <c r="I126" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J126" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K126" s="11"/>
@@ -4588,11 +4610,11 @@
       <c r="G127" s="9"/>
       <c r="H127" s="9"/>
       <c r="I127" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J127" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K127" s="11"/>
@@ -4610,11 +4632,11 @@
       <c r="G128" s="9"/>
       <c r="H128" s="9"/>
       <c r="I128" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J128" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K128" s="11"/>
@@ -4632,11 +4654,11 @@
       <c r="G129" s="9"/>
       <c r="H129" s="9"/>
       <c r="I129" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J129" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K129" s="11"/>
@@ -4654,11 +4676,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -4676,11 +4698,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -4698,11 +4720,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -4720,11 +4742,11 @@
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
       <c r="I133" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J133" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K133" s="11"/>
@@ -4742,11 +4764,11 @@
       <c r="G134" s="9"/>
       <c r="H134" s="9"/>
       <c r="I134" s="10" t="str">
-        <f t="shared" ref="I134:I197" si="58">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="60">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="10" t="str">
-        <f t="shared" ref="J134:J197" si="59">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="61">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="11"/>
@@ -4764,11 +4786,11 @@
       <c r="G135" s="9"/>
       <c r="H135" s="9"/>
       <c r="I135" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J135" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K135" s="11"/>
@@ -4786,11 +4808,11 @@
       <c r="G136" s="9"/>
       <c r="H136" s="9"/>
       <c r="I136" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J136" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K136" s="11"/>
@@ -4808,11 +4830,11 @@
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
       <c r="I137" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J137" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K137" s="11"/>
@@ -4830,11 +4852,11 @@
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J138" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K138" s="11"/>
@@ -4852,11 +4874,11 @@
       <c r="G139" s="9"/>
       <c r="H139" s="9"/>
       <c r="I139" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J139" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K139" s="11"/>
@@ -4874,11 +4896,11 @@
       <c r="G140" s="9"/>
       <c r="H140" s="9"/>
       <c r="I140" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J140" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K140" s="11"/>
@@ -4896,11 +4918,11 @@
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
       <c r="I141" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J141" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K141" s="11"/>
@@ -4918,11 +4940,11 @@
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J142" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K142" s="11"/>
@@ -4940,11 +4962,11 @@
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
       <c r="I143" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J143" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K143" s="11"/>
@@ -4962,11 +4984,11 @@
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
       <c r="I144" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J144" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K144" s="11"/>
@@ -4984,11 +5006,11 @@
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J145" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K145" s="11"/>
@@ -5006,11 +5028,11 @@
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J146" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K146" s="11"/>
@@ -5028,11 +5050,11 @@
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
       <c r="I147" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J147" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K147" s="11"/>
@@ -5050,11 +5072,11 @@
       <c r="G148" s="9"/>
       <c r="H148" s="9"/>
       <c r="I148" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J148" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K148" s="11"/>
@@ -5072,11 +5094,11 @@
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
       <c r="I149" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J149" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K149" s="11"/>
@@ -5094,11 +5116,11 @@
       <c r="G150" s="9"/>
       <c r="H150" s="9"/>
       <c r="I150" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J150" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K150" s="11"/>
@@ -5116,11 +5138,11 @@
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
       <c r="I151" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J151" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K151" s="11"/>
@@ -5138,11 +5160,11 @@
       <c r="G152" s="9"/>
       <c r="H152" s="9"/>
       <c r="I152" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J152" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K152" s="11"/>
@@ -5160,11 +5182,11 @@
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
       <c r="I153" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J153" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K153" s="11"/>
@@ -5182,11 +5204,11 @@
       <c r="G154" s="9"/>
       <c r="H154" s="9"/>
       <c r="I154" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J154" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K154" s="11"/>
@@ -5204,11 +5226,11 @@
       <c r="G155" s="9"/>
       <c r="H155" s="9"/>
       <c r="I155" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J155" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K155" s="11"/>
@@ -5226,11 +5248,11 @@
       <c r="G156" s="9"/>
       <c r="H156" s="9"/>
       <c r="I156" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J156" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K156" s="11"/>
@@ -5248,11 +5270,11 @@
       <c r="G157" s="9"/>
       <c r="H157" s="9"/>
       <c r="I157" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J157" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K157" s="11"/>
@@ -5270,11 +5292,11 @@
       <c r="G158" s="9"/>
       <c r="H158" s="9"/>
       <c r="I158" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J158" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K158" s="11"/>
@@ -5292,11 +5314,11 @@
       <c r="G159" s="9"/>
       <c r="H159" s="9"/>
       <c r="I159" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J159" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K159" s="11"/>
@@ -5314,11 +5336,11 @@
       <c r="G160" s="9"/>
       <c r="H160" s="9"/>
       <c r="I160" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J160" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K160" s="11"/>
@@ -5336,11 +5358,11 @@
       <c r="G161" s="9"/>
       <c r="H161" s="9"/>
       <c r="I161" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J161" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K161" s="11"/>
@@ -5358,11 +5380,11 @@
       <c r="G162" s="9"/>
       <c r="H162" s="9"/>
       <c r="I162" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J162" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K162" s="11"/>
@@ -5380,11 +5402,11 @@
       <c r="G163" s="9"/>
       <c r="H163" s="9"/>
       <c r="I163" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J163" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K163" s="11"/>
@@ -5402,11 +5424,11 @@
       <c r="G164" s="9"/>
       <c r="H164" s="9"/>
       <c r="I164" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J164" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K164" s="11"/>
@@ -5424,11 +5446,11 @@
       <c r="G165" s="9"/>
       <c r="H165" s="9"/>
       <c r="I165" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J165" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K165" s="11"/>
@@ -5446,11 +5468,11 @@
       <c r="G166" s="9"/>
       <c r="H166" s="9"/>
       <c r="I166" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J166" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K166" s="11"/>
@@ -5468,11 +5490,11 @@
       <c r="G167" s="9"/>
       <c r="H167" s="9"/>
       <c r="I167" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J167" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K167" s="11"/>
@@ -5490,11 +5512,11 @@
       <c r="G168" s="9"/>
       <c r="H168" s="9"/>
       <c r="I168" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J168" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K168" s="11"/>
@@ -5512,11 +5534,11 @@
       <c r="G169" s="9"/>
       <c r="H169" s="9"/>
       <c r="I169" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J169" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K169" s="11"/>
@@ -5534,11 +5556,11 @@
       <c r="G170" s="9"/>
       <c r="H170" s="9"/>
       <c r="I170" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J170" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K170" s="11"/>
@@ -5556,11 +5578,11 @@
       <c r="G171" s="9"/>
       <c r="H171" s="9"/>
       <c r="I171" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J171" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K171" s="11"/>
@@ -5578,11 +5600,11 @@
       <c r="G172" s="9"/>
       <c r="H172" s="9"/>
       <c r="I172" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J172" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K172" s="11"/>
@@ -5600,11 +5622,11 @@
       <c r="G173" s="9"/>
       <c r="H173" s="9"/>
       <c r="I173" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J173" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K173" s="11"/>
@@ -5622,11 +5644,11 @@
       <c r="G174" s="9"/>
       <c r="H174" s="9"/>
       <c r="I174" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J174" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K174" s="11"/>
@@ -5644,11 +5666,11 @@
       <c r="G175" s="9"/>
       <c r="H175" s="9"/>
       <c r="I175" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J175" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K175" s="11"/>
@@ -5666,11 +5688,11 @@
       <c r="G176" s="9"/>
       <c r="H176" s="9"/>
       <c r="I176" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J176" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K176" s="11"/>
@@ -5688,11 +5710,11 @@
       <c r="G177" s="9"/>
       <c r="H177" s="9"/>
       <c r="I177" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J177" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K177" s="11"/>
@@ -5710,11 +5732,11 @@
       <c r="G178" s="9"/>
       <c r="H178" s="9"/>
       <c r="I178" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J178" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K178" s="11"/>
@@ -5732,11 +5754,11 @@
       <c r="G179" s="9"/>
       <c r="H179" s="9"/>
       <c r="I179" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J179" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K179" s="11"/>
@@ -5754,11 +5776,11 @@
       <c r="G180" s="9"/>
       <c r="H180" s="9"/>
       <c r="I180" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J180" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K180" s="11"/>
@@ -5776,11 +5798,11 @@
       <c r="G181" s="9"/>
       <c r="H181" s="9"/>
       <c r="I181" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J181" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K181" s="11"/>
@@ -5798,11 +5820,11 @@
       <c r="G182" s="9"/>
       <c r="H182" s="9"/>
       <c r="I182" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J182" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K182" s="11"/>
@@ -5820,11 +5842,11 @@
       <c r="G183" s="9"/>
       <c r="H183" s="9"/>
       <c r="I183" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J183" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K183" s="11"/>
@@ -5842,11 +5864,11 @@
       <c r="G184" s="9"/>
       <c r="H184" s="9"/>
       <c r="I184" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J184" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K184" s="11"/>
@@ -5864,11 +5886,11 @@
       <c r="G185" s="9"/>
       <c r="H185" s="9"/>
       <c r="I185" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J185" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K185" s="11"/>
@@ -5886,11 +5908,11 @@
       <c r="G186" s="9"/>
       <c r="H186" s="9"/>
       <c r="I186" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J186" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K186" s="11"/>
@@ -5908,11 +5930,11 @@
       <c r="G187" s="9"/>
       <c r="H187" s="9"/>
       <c r="I187" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J187" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K187" s="11"/>
@@ -5930,11 +5952,11 @@
       <c r="G188" s="9"/>
       <c r="H188" s="9"/>
       <c r="I188" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J188" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K188" s="11"/>
@@ -5952,11 +5974,11 @@
       <c r="G189" s="9"/>
       <c r="H189" s="9"/>
       <c r="I189" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J189" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K189" s="11"/>
@@ -5974,11 +5996,11 @@
       <c r="G190" s="9"/>
       <c r="H190" s="9"/>
       <c r="I190" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J190" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K190" s="11"/>
@@ -5996,11 +6018,11 @@
       <c r="G191" s="9"/>
       <c r="H191" s="9"/>
       <c r="I191" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J191" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K191" s="11"/>
@@ -6018,11 +6040,11 @@
       <c r="G192" s="9"/>
       <c r="H192" s="9"/>
       <c r="I192" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J192" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K192" s="11"/>
@@ -6040,11 +6062,11 @@
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J193" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K193" s="11"/>
@@ -6062,11 +6084,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -6084,11 +6106,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -6106,11 +6128,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -6128,11 +6150,11 @@
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J197" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K197" s="11"/>
@@ -6150,11 +6172,11 @@
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
       <c r="I198" s="10" t="str">
-        <f t="shared" ref="I198:I261" si="60">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="62">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="10" t="str">
-        <f t="shared" ref="J198:J261" si="61">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="63">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="11"/>
@@ -6172,11 +6194,11 @@
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
       <c r="I199" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J199" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K199" s="11"/>
@@ -6194,11 +6216,11 @@
       <c r="G200" s="9"/>
       <c r="H200" s="9"/>
       <c r="I200" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J200" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K200" s="11"/>
@@ -6216,11 +6238,11 @@
       <c r="G201" s="9"/>
       <c r="H201" s="9"/>
       <c r="I201" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J201" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K201" s="11"/>
@@ -6238,11 +6260,11 @@
       <c r="G202" s="9"/>
       <c r="H202" s="9"/>
       <c r="I202" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J202" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K202" s="11"/>
@@ -6260,11 +6282,11 @@
       <c r="G203" s="9"/>
       <c r="H203" s="9"/>
       <c r="I203" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J203" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K203" s="11"/>
@@ -6282,11 +6304,11 @@
       <c r="G204" s="9"/>
       <c r="H204" s="9"/>
       <c r="I204" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J204" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K204" s="11"/>
@@ -6304,11 +6326,11 @@
       <c r="G205" s="9"/>
       <c r="H205" s="9"/>
       <c r="I205" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J205" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K205" s="11"/>
@@ -6326,11 +6348,11 @@
       <c r="G206" s="9"/>
       <c r="H206" s="9"/>
       <c r="I206" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J206" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K206" s="11"/>
@@ -6348,11 +6370,11 @@
       <c r="G207" s="9"/>
       <c r="H207" s="9"/>
       <c r="I207" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J207" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K207" s="11"/>
@@ -6370,11 +6392,11 @@
       <c r="G208" s="9"/>
       <c r="H208" s="9"/>
       <c r="I208" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J208" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K208" s="11"/>
@@ -6392,11 +6414,11 @@
       <c r="G209" s="9"/>
       <c r="H209" s="9"/>
       <c r="I209" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J209" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K209" s="11"/>
@@ -6414,11 +6436,11 @@
       <c r="G210" s="9"/>
       <c r="H210" s="9"/>
       <c r="I210" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J210" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K210" s="11"/>
@@ -6436,11 +6458,11 @@
       <c r="G211" s="9"/>
       <c r="H211" s="9"/>
       <c r="I211" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J211" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K211" s="11"/>
@@ -6458,11 +6480,11 @@
       <c r="G212" s="9"/>
       <c r="H212" s="9"/>
       <c r="I212" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J212" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K212" s="11"/>
@@ -6480,11 +6502,11 @@
       <c r="G213" s="9"/>
       <c r="H213" s="9"/>
       <c r="I213" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J213" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K213" s="11"/>
@@ -6502,11 +6524,11 @@
       <c r="G214" s="9"/>
       <c r="H214" s="9"/>
       <c r="I214" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J214" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K214" s="11"/>
@@ -6524,11 +6546,11 @@
       <c r="G215" s="9"/>
       <c r="H215" s="9"/>
       <c r="I215" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J215" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K215" s="11"/>
@@ -6546,11 +6568,11 @@
       <c r="G216" s="9"/>
       <c r="H216" s="9"/>
       <c r="I216" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J216" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K216" s="11"/>
@@ -6568,11 +6590,11 @@
       <c r="G217" s="9"/>
       <c r="H217" s="9"/>
       <c r="I217" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J217" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K217" s="11"/>
@@ -6590,11 +6612,11 @@
       <c r="G218" s="9"/>
       <c r="H218" s="9"/>
       <c r="I218" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J218" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K218" s="11"/>
@@ -6612,11 +6634,11 @@
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
       <c r="I219" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J219" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K219" s="11"/>
@@ -6634,11 +6656,11 @@
       <c r="G220" s="9"/>
       <c r="H220" s="9"/>
       <c r="I220" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J220" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K220" s="11"/>
@@ -6656,11 +6678,11 @@
       <c r="G221" s="9"/>
       <c r="H221" s="9"/>
       <c r="I221" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J221" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K221" s="11"/>
@@ -6678,11 +6700,11 @@
       <c r="G222" s="9"/>
       <c r="H222" s="9"/>
       <c r="I222" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J222" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K222" s="11"/>
@@ -6700,11 +6722,11 @@
       <c r="G223" s="9"/>
       <c r="H223" s="9"/>
       <c r="I223" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J223" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K223" s="11"/>
@@ -6722,11 +6744,11 @@
       <c r="G224" s="9"/>
       <c r="H224" s="9"/>
       <c r="I224" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J224" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K224" s="11"/>
@@ -6744,11 +6766,11 @@
       <c r="G225" s="9"/>
       <c r="H225" s="9"/>
       <c r="I225" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J225" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K225" s="11"/>
@@ -6766,11 +6788,11 @@
       <c r="G226" s="9"/>
       <c r="H226" s="9"/>
       <c r="I226" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J226" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K226" s="11"/>
@@ -6788,11 +6810,11 @@
       <c r="G227" s="9"/>
       <c r="H227" s="9"/>
       <c r="I227" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J227" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K227" s="11"/>
@@ -6810,11 +6832,11 @@
       <c r="G228" s="9"/>
       <c r="H228" s="9"/>
       <c r="I228" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J228" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K228" s="11"/>
@@ -6832,11 +6854,11 @@
       <c r="G229" s="9"/>
       <c r="H229" s="9"/>
       <c r="I229" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J229" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K229" s="11"/>
@@ -6854,11 +6876,11 @@
       <c r="G230" s="9"/>
       <c r="H230" s="9"/>
       <c r="I230" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J230" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K230" s="11"/>
@@ -6876,11 +6898,11 @@
       <c r="G231" s="9"/>
       <c r="H231" s="9"/>
       <c r="I231" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J231" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K231" s="11"/>
@@ -6898,11 +6920,11 @@
       <c r="G232" s="9"/>
       <c r="H232" s="9"/>
       <c r="I232" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J232" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K232" s="11"/>
@@ -6920,11 +6942,11 @@
       <c r="G233" s="9"/>
       <c r="H233" s="9"/>
       <c r="I233" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J233" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K233" s="11"/>
@@ -6942,11 +6964,11 @@
       <c r="G234" s="9"/>
       <c r="H234" s="9"/>
       <c r="I234" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J234" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K234" s="11"/>
@@ -6964,11 +6986,11 @@
       <c r="G235" s="9"/>
       <c r="H235" s="9"/>
       <c r="I235" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J235" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K235" s="11"/>
@@ -6986,11 +7008,11 @@
       <c r="G236" s="9"/>
       <c r="H236" s="9"/>
       <c r="I236" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J236" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K236" s="11"/>
@@ -7008,11 +7030,11 @@
       <c r="G237" s="9"/>
       <c r="H237" s="9"/>
       <c r="I237" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J237" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K237" s="11"/>
@@ -7030,11 +7052,11 @@
       <c r="G238" s="9"/>
       <c r="H238" s="9"/>
       <c r="I238" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J238" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K238" s="11"/>
@@ -7052,11 +7074,11 @@
       <c r="G239" s="9"/>
       <c r="H239" s="9"/>
       <c r="I239" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J239" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K239" s="11"/>
@@ -7074,11 +7096,11 @@
       <c r="G240" s="9"/>
       <c r="H240" s="9"/>
       <c r="I240" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J240" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K240" s="11"/>
@@ -7096,11 +7118,11 @@
       <c r="G241" s="9"/>
       <c r="H241" s="9"/>
       <c r="I241" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J241" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K241" s="11"/>
@@ -7118,11 +7140,11 @@
       <c r="G242" s="9"/>
       <c r="H242" s="9"/>
       <c r="I242" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J242" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K242" s="11"/>
@@ -7140,11 +7162,11 @@
       <c r="G243" s="9"/>
       <c r="H243" s="9"/>
       <c r="I243" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J243" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K243" s="11"/>
@@ -7162,11 +7184,11 @@
       <c r="G244" s="9"/>
       <c r="H244" s="9"/>
       <c r="I244" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J244" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K244" s="11"/>
@@ -7184,11 +7206,11 @@
       <c r="G245" s="9"/>
       <c r="H245" s="9"/>
       <c r="I245" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J245" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K245" s="11"/>
@@ -7206,11 +7228,11 @@
       <c r="G246" s="9"/>
       <c r="H246" s="9"/>
       <c r="I246" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J246" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K246" s="11"/>
@@ -7228,11 +7250,11 @@
       <c r="G247" s="9"/>
       <c r="H247" s="9"/>
       <c r="I247" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J247" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K247" s="11"/>
@@ -7250,11 +7272,11 @@
       <c r="G248" s="9"/>
       <c r="H248" s="9"/>
       <c r="I248" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J248" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K248" s="11"/>
@@ -7272,11 +7294,11 @@
       <c r="G249" s="9"/>
       <c r="H249" s="9"/>
       <c r="I249" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J249" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K249" s="11"/>
@@ -7294,11 +7316,11 @@
       <c r="G250" s="9"/>
       <c r="H250" s="9"/>
       <c r="I250" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J250" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K250" s="11"/>
@@ -7316,11 +7338,11 @@
       <c r="G251" s="9"/>
       <c r="H251" s="9"/>
       <c r="I251" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J251" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K251" s="11"/>
@@ -7338,11 +7360,11 @@
       <c r="G252" s="9"/>
       <c r="H252" s="9"/>
       <c r="I252" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J252" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K252" s="11"/>
@@ -7360,11 +7382,11 @@
       <c r="G253" s="9"/>
       <c r="H253" s="9"/>
       <c r="I253" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J253" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K253" s="11"/>
@@ -7382,11 +7404,11 @@
       <c r="G254" s="9"/>
       <c r="H254" s="9"/>
       <c r="I254" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J254" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K254" s="11"/>
@@ -7404,11 +7426,11 @@
       <c r="G255" s="9"/>
       <c r="H255" s="9"/>
       <c r="I255" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J255" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K255" s="11"/>
@@ -7426,11 +7448,11 @@
       <c r="G256" s="9"/>
       <c r="H256" s="9"/>
       <c r="I256" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J256" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K256" s="11"/>
@@ -7448,11 +7470,11 @@
       <c r="G257" s="9"/>
       <c r="H257" s="9"/>
       <c r="I257" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J257" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K257" s="11"/>
@@ -7470,11 +7492,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -7492,11 +7514,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -7514,11 +7536,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -7536,11 +7558,11 @@
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
       <c r="I261" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J261" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K261" s="11"/>
@@ -7558,11 +7580,11 @@
       <c r="G262" s="9"/>
       <c r="H262" s="9"/>
       <c r="I262" s="10" t="str">
-        <f t="shared" ref="I262:I325" si="62">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="64">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="10" t="str">
-        <f t="shared" ref="J262:J325" si="63">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="65">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="11"/>
@@ -7580,11 +7602,11 @@
       <c r="G263" s="9"/>
       <c r="H263" s="9"/>
       <c r="I263" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J263" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K263" s="11"/>
@@ -7602,11 +7624,11 @@
       <c r="G264" s="9"/>
       <c r="H264" s="9"/>
       <c r="I264" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J264" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K264" s="11"/>
@@ -7624,11 +7646,11 @@
       <c r="G265" s="9"/>
       <c r="H265" s="9"/>
       <c r="I265" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J265" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K265" s="11"/>
@@ -7646,11 +7668,11 @@
       <c r="G266" s="9"/>
       <c r="H266" s="9"/>
       <c r="I266" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J266" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K266" s="11"/>
@@ -7668,11 +7690,11 @@
       <c r="G267" s="9"/>
       <c r="H267" s="9"/>
       <c r="I267" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J267" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K267" s="11"/>
@@ -7690,11 +7712,11 @@
       <c r="G268" s="9"/>
       <c r="H268" s="9"/>
       <c r="I268" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J268" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K268" s="11"/>
@@ -7712,11 +7734,11 @@
       <c r="G269" s="9"/>
       <c r="H269" s="9"/>
       <c r="I269" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J269" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K269" s="11"/>
@@ -7734,11 +7756,11 @@
       <c r="G270" s="9"/>
       <c r="H270" s="9"/>
       <c r="I270" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J270" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K270" s="11"/>
@@ -7756,11 +7778,11 @@
       <c r="G271" s="9"/>
       <c r="H271" s="9"/>
       <c r="I271" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J271" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K271" s="11"/>
@@ -7778,11 +7800,11 @@
       <c r="G272" s="9"/>
       <c r="H272" s="9"/>
       <c r="I272" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J272" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K272" s="11"/>
@@ -7800,11 +7822,11 @@
       <c r="G273" s="9"/>
       <c r="H273" s="9"/>
       <c r="I273" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J273" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K273" s="11"/>
@@ -7822,11 +7844,11 @@
       <c r="G274" s="9"/>
       <c r="H274" s="9"/>
       <c r="I274" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J274" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K274" s="11"/>
@@ -7844,11 +7866,11 @@
       <c r="G275" s="9"/>
       <c r="H275" s="9"/>
       <c r="I275" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J275" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K275" s="11"/>
@@ -7866,11 +7888,11 @@
       <c r="G276" s="9"/>
       <c r="H276" s="9"/>
       <c r="I276" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J276" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K276" s="11"/>
@@ -7888,11 +7910,11 @@
       <c r="G277" s="9"/>
       <c r="H277" s="9"/>
       <c r="I277" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J277" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K277" s="11"/>
@@ -7910,11 +7932,11 @@
       <c r="G278" s="9"/>
       <c r="H278" s="9"/>
       <c r="I278" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J278" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K278" s="11"/>
@@ -7932,11 +7954,11 @@
       <c r="G279" s="9"/>
       <c r="H279" s="9"/>
       <c r="I279" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J279" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K279" s="11"/>
@@ -7954,11 +7976,11 @@
       <c r="G280" s="9"/>
       <c r="H280" s="9"/>
       <c r="I280" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J280" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K280" s="11"/>
@@ -7976,11 +7998,11 @@
       <c r="G281" s="9"/>
       <c r="H281" s="9"/>
       <c r="I281" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J281" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K281" s="11"/>
@@ -7998,11 +8020,11 @@
       <c r="G282" s="9"/>
       <c r="H282" s="9"/>
       <c r="I282" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J282" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K282" s="11"/>
@@ -8020,11 +8042,11 @@
       <c r="G283" s="9"/>
       <c r="H283" s="9"/>
       <c r="I283" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J283" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K283" s="11"/>
@@ -8042,11 +8064,11 @@
       <c r="G284" s="9"/>
       <c r="H284" s="9"/>
       <c r="I284" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J284" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K284" s="11"/>
@@ -8064,11 +8086,11 @@
       <c r="G285" s="9"/>
       <c r="H285" s="9"/>
       <c r="I285" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J285" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K285" s="11"/>
@@ -8086,11 +8108,11 @@
       <c r="G286" s="9"/>
       <c r="H286" s="9"/>
       <c r="I286" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J286" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K286" s="11"/>
@@ -8108,11 +8130,11 @@
       <c r="G287" s="9"/>
       <c r="H287" s="9"/>
       <c r="I287" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J287" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K287" s="11"/>
@@ -8130,11 +8152,11 @@
       <c r="G288" s="9"/>
       <c r="H288" s="9"/>
       <c r="I288" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J288" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K288" s="11"/>
@@ -8152,11 +8174,11 @@
       <c r="G289" s="9"/>
       <c r="H289" s="9"/>
       <c r="I289" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J289" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K289" s="11"/>
@@ -8174,11 +8196,11 @@
       <c r="G290" s="9"/>
       <c r="H290" s="9"/>
       <c r="I290" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J290" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K290" s="11"/>
@@ -8196,11 +8218,11 @@
       <c r="G291" s="9"/>
       <c r="H291" s="9"/>
       <c r="I291" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J291" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K291" s="11"/>
@@ -8218,11 +8240,11 @@
       <c r="G292" s="9"/>
       <c r="H292" s="9"/>
       <c r="I292" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J292" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K292" s="11"/>
@@ -8240,11 +8262,11 @@
       <c r="G293" s="9"/>
       <c r="H293" s="9"/>
       <c r="I293" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J293" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K293" s="11"/>
@@ -8262,11 +8284,11 @@
       <c r="G294" s="9"/>
       <c r="H294" s="9"/>
       <c r="I294" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J294" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K294" s="11"/>
@@ -8284,11 +8306,11 @@
       <c r="G295" s="9"/>
       <c r="H295" s="9"/>
       <c r="I295" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J295" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K295" s="11"/>
@@ -8306,11 +8328,11 @@
       <c r="G296" s="9"/>
       <c r="H296" s="9"/>
       <c r="I296" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J296" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K296" s="11"/>
@@ -8328,11 +8350,11 @@
       <c r="G297" s="9"/>
       <c r="H297" s="9"/>
       <c r="I297" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J297" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K297" s="11"/>
@@ -8350,11 +8372,11 @@
       <c r="G298" s="9"/>
       <c r="H298" s="9"/>
       <c r="I298" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J298" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K298" s="11"/>
@@ -8372,11 +8394,11 @@
       <c r="G299" s="9"/>
       <c r="H299" s="9"/>
       <c r="I299" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J299" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K299" s="11"/>
@@ -8394,11 +8416,11 @@
       <c r="G300" s="9"/>
       <c r="H300" s="9"/>
       <c r="I300" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J300" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K300" s="11"/>
@@ -8416,11 +8438,11 @@
       <c r="G301" s="9"/>
       <c r="H301" s="9"/>
       <c r="I301" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J301" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K301" s="11"/>
@@ -8438,11 +8460,11 @@
       <c r="G302" s="9"/>
       <c r="H302" s="9"/>
       <c r="I302" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J302" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K302" s="11"/>
@@ -8460,11 +8482,11 @@
       <c r="G303" s="9"/>
       <c r="H303" s="9"/>
       <c r="I303" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J303" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K303" s="11"/>
@@ -8482,11 +8504,11 @@
       <c r="G304" s="9"/>
       <c r="H304" s="9"/>
       <c r="I304" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J304" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K304" s="11"/>
@@ -8504,11 +8526,11 @@
       <c r="G305" s="9"/>
       <c r="H305" s="9"/>
       <c r="I305" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J305" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K305" s="11"/>
@@ -8526,11 +8548,11 @@
       <c r="G306" s="9"/>
       <c r="H306" s="9"/>
       <c r="I306" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J306" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K306" s="11"/>
@@ -8548,11 +8570,11 @@
       <c r="G307" s="9"/>
       <c r="H307" s="9"/>
       <c r="I307" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J307" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K307" s="11"/>
@@ -8570,11 +8592,11 @@
       <c r="G308" s="9"/>
       <c r="H308" s="9"/>
       <c r="I308" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J308" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K308" s="11"/>
@@ -8592,11 +8614,11 @@
       <c r="G309" s="9"/>
       <c r="H309" s="9"/>
       <c r="I309" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J309" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K309" s="11"/>
@@ -8614,11 +8636,11 @@
       <c r="G310" s="9"/>
       <c r="H310" s="9"/>
       <c r="I310" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J310" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K310" s="11"/>
@@ -8636,11 +8658,11 @@
       <c r="G311" s="9"/>
       <c r="H311" s="9"/>
       <c r="I311" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J311" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K311" s="11"/>
@@ -8658,11 +8680,11 @@
       <c r="G312" s="9"/>
       <c r="H312" s="9"/>
       <c r="I312" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J312" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K312" s="11"/>
@@ -8680,11 +8702,11 @@
       <c r="G313" s="9"/>
       <c r="H313" s="9"/>
       <c r="I313" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J313" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K313" s="11"/>
@@ -8702,11 +8724,11 @@
       <c r="G314" s="9"/>
       <c r="H314" s="9"/>
       <c r="I314" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J314" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K314" s="11"/>
@@ -8724,11 +8746,11 @@
       <c r="G315" s="9"/>
       <c r="H315" s="9"/>
       <c r="I315" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J315" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K315" s="11"/>
@@ -8746,11 +8768,11 @@
       <c r="G316" s="9"/>
       <c r="H316" s="9"/>
       <c r="I316" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J316" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K316" s="11"/>
@@ -8768,11 +8790,11 @@
       <c r="G317" s="9"/>
       <c r="H317" s="9"/>
       <c r="I317" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J317" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K317" s="11"/>
@@ -8790,11 +8812,11 @@
       <c r="G318" s="9"/>
       <c r="H318" s="9"/>
       <c r="I318" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J318" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K318" s="11"/>
@@ -8812,11 +8834,11 @@
       <c r="G319" s="9"/>
       <c r="H319" s="9"/>
       <c r="I319" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J319" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K319" s="11"/>
@@ -8834,11 +8856,11 @@
       <c r="G320" s="9"/>
       <c r="H320" s="9"/>
       <c r="I320" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J320" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K320" s="11"/>
@@ -8856,11 +8878,11 @@
       <c r="G321" s="9"/>
       <c r="H321" s="9"/>
       <c r="I321" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J321" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K321" s="11"/>
@@ -8878,11 +8900,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -8900,11 +8922,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -8922,11 +8944,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -8944,11 +8966,11 @@
       <c r="G325" s="9"/>
       <c r="H325" s="9"/>
       <c r="I325" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J325" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K325" s="11"/>
@@ -8966,11 +8988,11 @@
       <c r="G326" s="9"/>
       <c r="H326" s="9"/>
       <c r="I326" s="10" t="str">
-        <f t="shared" ref="I326:I389" si="64">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="66">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="10" t="str">
-        <f t="shared" ref="J326:J389" si="65">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="67">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="11"/>
@@ -8988,11 +9010,11 @@
       <c r="G327" s="9"/>
       <c r="H327" s="9"/>
       <c r="I327" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J327" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K327" s="11"/>
@@ -9010,11 +9032,11 @@
       <c r="G328" s="9"/>
       <c r="H328" s="9"/>
       <c r="I328" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J328" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K328" s="11"/>
@@ -9032,11 +9054,11 @@
       <c r="G329" s="9"/>
       <c r="H329" s="9"/>
       <c r="I329" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J329" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K329" s="11"/>
@@ -9054,11 +9076,11 @@
       <c r="G330" s="9"/>
       <c r="H330" s="9"/>
       <c r="I330" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J330" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K330" s="11"/>
@@ -9076,11 +9098,11 @@
       <c r="G331" s="9"/>
       <c r="H331" s="9"/>
       <c r="I331" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J331" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K331" s="11"/>
@@ -9098,11 +9120,11 @@
       <c r="G332" s="9"/>
       <c r="H332" s="9"/>
       <c r="I332" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J332" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K332" s="11"/>
@@ -9120,11 +9142,11 @@
       <c r="G333" s="9"/>
       <c r="H333" s="9"/>
       <c r="I333" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J333" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K333" s="11"/>
@@ -9142,11 +9164,11 @@
       <c r="G334" s="9"/>
       <c r="H334" s="9"/>
       <c r="I334" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J334" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K334" s="11"/>
@@ -9164,11 +9186,11 @@
       <c r="G335" s="9"/>
       <c r="H335" s="9"/>
       <c r="I335" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J335" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K335" s="11"/>
@@ -9186,11 +9208,11 @@
       <c r="G336" s="9"/>
       <c r="H336" s="9"/>
       <c r="I336" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J336" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K336" s="11"/>
@@ -9208,11 +9230,11 @@
       <c r="G337" s="9"/>
       <c r="H337" s="9"/>
       <c r="I337" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J337" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K337" s="11"/>
@@ -9230,11 +9252,11 @@
       <c r="G338" s="9"/>
       <c r="H338" s="9"/>
       <c r="I338" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J338" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K338" s="11"/>
@@ -9252,11 +9274,11 @@
       <c r="G339" s="9"/>
       <c r="H339" s="9"/>
       <c r="I339" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J339" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K339" s="11"/>
@@ -9274,11 +9296,11 @@
       <c r="G340" s="9"/>
       <c r="H340" s="9"/>
       <c r="I340" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J340" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K340" s="11"/>
@@ -9296,11 +9318,11 @@
       <c r="G341" s="9"/>
       <c r="H341" s="9"/>
       <c r="I341" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J341" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K341" s="11"/>
@@ -9318,11 +9340,11 @@
       <c r="G342" s="9"/>
       <c r="H342" s="9"/>
       <c r="I342" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J342" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K342" s="11"/>
@@ -9340,11 +9362,11 @@
       <c r="G343" s="9"/>
       <c r="H343" s="9"/>
       <c r="I343" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J343" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K343" s="11"/>
@@ -9362,11 +9384,11 @@
       <c r="G344" s="9"/>
       <c r="H344" s="9"/>
       <c r="I344" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J344" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K344" s="11"/>
@@ -9384,11 +9406,11 @@
       <c r="G345" s="9"/>
       <c r="H345" s="9"/>
       <c r="I345" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J345" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K345" s="11"/>
@@ -9406,11 +9428,11 @@
       <c r="G346" s="9"/>
       <c r="H346" s="9"/>
       <c r="I346" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J346" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K346" s="11"/>
@@ -9428,11 +9450,11 @@
       <c r="G347" s="9"/>
       <c r="H347" s="9"/>
       <c r="I347" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J347" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K347" s="11"/>
@@ -9450,11 +9472,11 @@
       <c r="G348" s="9"/>
       <c r="H348" s="9"/>
       <c r="I348" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J348" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K348" s="11"/>
@@ -9472,11 +9494,11 @@
       <c r="G349" s="9"/>
       <c r="H349" s="9"/>
       <c r="I349" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J349" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K349" s="11"/>
@@ -9494,11 +9516,11 @@
       <c r="G350" s="9"/>
       <c r="H350" s="9"/>
       <c r="I350" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J350" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K350" s="11"/>
@@ -9516,11 +9538,11 @@
       <c r="G351" s="9"/>
       <c r="H351" s="9"/>
       <c r="I351" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J351" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K351" s="11"/>
@@ -9538,11 +9560,11 @@
       <c r="G352" s="9"/>
       <c r="H352" s="9"/>
       <c r="I352" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J352" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K352" s="11"/>
@@ -9560,11 +9582,11 @@
       <c r="G353" s="9"/>
       <c r="H353" s="9"/>
       <c r="I353" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J353" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K353" s="11"/>
@@ -9582,11 +9604,11 @@
       <c r="G354" s="9"/>
       <c r="H354" s="9"/>
       <c r="I354" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J354" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K354" s="11"/>
@@ -9604,11 +9626,11 @@
       <c r="G355" s="9"/>
       <c r="H355" s="9"/>
       <c r="I355" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J355" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K355" s="11"/>
@@ -9626,11 +9648,11 @@
       <c r="G356" s="9"/>
       <c r="H356" s="9"/>
       <c r="I356" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J356" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K356" s="11"/>
@@ -9648,11 +9670,11 @@
       <c r="G357" s="9"/>
       <c r="H357" s="9"/>
       <c r="I357" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J357" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K357" s="11"/>
@@ -9670,11 +9692,11 @@
       <c r="G358" s="9"/>
       <c r="H358" s="9"/>
       <c r="I358" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J358" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K358" s="11"/>
@@ -9692,11 +9714,11 @@
       <c r="G359" s="9"/>
       <c r="H359" s="9"/>
       <c r="I359" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J359" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K359" s="11"/>
@@ -9714,11 +9736,11 @@
       <c r="G360" s="9"/>
       <c r="H360" s="9"/>
       <c r="I360" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J360" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K360" s="11"/>
@@ -9736,11 +9758,11 @@
       <c r="G361" s="9"/>
       <c r="H361" s="9"/>
       <c r="I361" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J361" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K361" s="11"/>
@@ -9758,11 +9780,11 @@
       <c r="G362" s="9"/>
       <c r="H362" s="9"/>
       <c r="I362" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J362" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K362" s="11"/>
@@ -9780,11 +9802,11 @@
       <c r="G363" s="9"/>
       <c r="H363" s="9"/>
       <c r="I363" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J363" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K363" s="11"/>
@@ -9802,11 +9824,11 @@
       <c r="G364" s="9"/>
       <c r="H364" s="9"/>
       <c r="I364" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J364" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K364" s="11"/>
@@ -9824,11 +9846,11 @@
       <c r="G365" s="9"/>
       <c r="H365" s="9"/>
       <c r="I365" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J365" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K365" s="11"/>
@@ -9846,11 +9868,11 @@
       <c r="G366" s="9"/>
       <c r="H366" s="9"/>
       <c r="I366" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J366" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K366" s="11"/>
@@ -9868,11 +9890,11 @@
       <c r="G367" s="9"/>
       <c r="H367" s="9"/>
       <c r="I367" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J367" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K367" s="11"/>
@@ -9890,11 +9912,11 @@
       <c r="G368" s="9"/>
       <c r="H368" s="9"/>
       <c r="I368" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J368" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K368" s="11"/>
@@ -9912,11 +9934,11 @@
       <c r="G369" s="9"/>
       <c r="H369" s="9"/>
       <c r="I369" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J369" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K369" s="11"/>
@@ -9934,11 +9956,11 @@
       <c r="G370" s="9"/>
       <c r="H370" s="9"/>
       <c r="I370" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J370" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K370" s="11"/>
@@ -9956,11 +9978,11 @@
       <c r="G371" s="9"/>
       <c r="H371" s="9"/>
       <c r="I371" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J371" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K371" s="11"/>
@@ -9978,11 +10000,11 @@
       <c r="G372" s="9"/>
       <c r="H372" s="9"/>
       <c r="I372" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J372" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K372" s="11"/>
@@ -10000,11 +10022,11 @@
       <c r="G373" s="9"/>
       <c r="H373" s="9"/>
       <c r="I373" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J373" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K373" s="11"/>
@@ -10022,11 +10044,11 @@
       <c r="G374" s="9"/>
       <c r="H374" s="9"/>
       <c r="I374" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J374" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K374" s="11"/>
@@ -10044,11 +10066,11 @@
       <c r="G375" s="9"/>
       <c r="H375" s="9"/>
       <c r="I375" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J375" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K375" s="11"/>
@@ -10066,11 +10088,11 @@
       <c r="G376" s="9"/>
       <c r="H376" s="9"/>
       <c r="I376" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J376" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K376" s="11"/>
@@ -10088,11 +10110,11 @@
       <c r="G377" s="9"/>
       <c r="H377" s="9"/>
       <c r="I377" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J377" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K377" s="11"/>
@@ -10110,11 +10132,11 @@
       <c r="G378" s="9"/>
       <c r="H378" s="9"/>
       <c r="I378" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J378" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K378" s="11"/>
@@ -10132,11 +10154,11 @@
       <c r="G379" s="9"/>
       <c r="H379" s="9"/>
       <c r="I379" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J379" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K379" s="11"/>
@@ -10154,11 +10176,11 @@
       <c r="G380" s="9"/>
       <c r="H380" s="9"/>
       <c r="I380" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J380" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K380" s="11"/>
@@ -10176,11 +10198,11 @@
       <c r="G381" s="9"/>
       <c r="H381" s="9"/>
       <c r="I381" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J381" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K381" s="11"/>
@@ -10198,11 +10220,11 @@
       <c r="G382" s="9"/>
       <c r="H382" s="9"/>
       <c r="I382" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J382" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K382" s="11"/>
@@ -10220,11 +10242,11 @@
       <c r="G383" s="9"/>
       <c r="H383" s="9"/>
       <c r="I383" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J383" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K383" s="11"/>
@@ -10242,11 +10264,11 @@
       <c r="G384" s="9"/>
       <c r="H384" s="9"/>
       <c r="I384" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J384" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K384" s="11"/>
@@ -10264,11 +10286,11 @@
       <c r="G385" s="9"/>
       <c r="H385" s="9"/>
       <c r="I385" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J385" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K385" s="11"/>
@@ -10286,11 +10308,11 @@
       <c r="G386" s="9"/>
       <c r="H386" s="9"/>
       <c r="I386" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J386" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K386" s="11"/>
@@ -10308,11 +10330,11 @@
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J387" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K387" s="11"/>
@@ -10330,11 +10352,11 @@
       <c r="G388" s="9"/>
       <c r="H388" s="9"/>
       <c r="I388" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J388" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K388" s="11"/>
@@ -10352,11 +10374,11 @@
       <c r="G389" s="9"/>
       <c r="H389" s="9"/>
       <c r="I389" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J389" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K389" s="11"/>
@@ -10374,11 +10396,11 @@
       <c r="G390" s="9"/>
       <c r="H390" s="9"/>
       <c r="I390" s="10" t="str">
-        <f t="shared" ref="I390:I401" si="66">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="68">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="10" t="str">
-        <f t="shared" ref="J390:J401" si="67">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="69">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="11"/>
@@ -10396,11 +10418,11 @@
       <c r="G391" s="9"/>
       <c r="H391" s="9"/>
       <c r="I391" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J391" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K391" s="11"/>
@@ -10418,11 +10440,11 @@
       <c r="G392" s="9"/>
       <c r="H392" s="9"/>
       <c r="I392" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J392" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K392" s="11"/>
@@ -10440,11 +10462,11 @@
       <c r="G393" s="9"/>
       <c r="H393" s="9"/>
       <c r="I393" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J393" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K393" s="11"/>
@@ -10462,11 +10484,11 @@
       <c r="G394" s="9"/>
       <c r="H394" s="9"/>
       <c r="I394" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J394" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K394" s="11"/>
@@ -10484,11 +10506,11 @@
       <c r="G395" s="9"/>
       <c r="H395" s="9"/>
       <c r="I395" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J395" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K395" s="11"/>
@@ -10506,11 +10528,11 @@
       <c r="G396" s="9"/>
       <c r="H396" s="9"/>
       <c r="I396" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J396" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K396" s="11"/>
@@ -10528,11 +10550,11 @@
       <c r="G397" s="9"/>
       <c r="H397" s="9"/>
       <c r="I397" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J397" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K397" s="11"/>
@@ -10550,11 +10572,11 @@
       <c r="G398" s="9"/>
       <c r="H398" s="9"/>
       <c r="I398" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J398" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K398" s="11"/>
@@ -10572,11 +10594,11 @@
       <c r="G399" s="9"/>
       <c r="H399" s="9"/>
       <c r="I399" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J399" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K399" s="11"/>
@@ -10594,11 +10616,11 @@
       <c r="G400" s="9"/>
       <c r="H400" s="9"/>
       <c r="I400" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J400" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K400" s="11"/>
@@ -10616,11 +10638,11 @@
       <c r="G401" s="9"/>
       <c r="H401" s="9"/>
       <c r="I401" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J401" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K401" s="11"/>

--- a/12626731.xlsx
+++ b/12626731.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHIVEN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{222F683E-AF70-4786-B208-C236B0C2486A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B515A85-30C8-418A-8A19-B9F855D443E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2753,26 +2753,48 @@
       <c r="N42" s="17"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="8"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
-      <c r="I43" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="11"/>
-      <c r="L43" s="11"/>
-      <c r="M43" s="11"/>
-      <c r="N43" s="12"/>
+      <c r="A43" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B43" s="14">
+        <v>400</v>
+      </c>
+      <c r="C43" s="14">
+        <v>0</v>
+      </c>
+      <c r="D43" s="14">
+        <v>120</v>
+      </c>
+      <c r="E43" s="14">
+        <v>20</v>
+      </c>
+      <c r="F43" s="14">
+        <v>200</v>
+      </c>
+      <c r="G43" s="14">
+        <v>4</v>
+      </c>
+      <c r="H43" s="14">
+        <v>270</v>
+      </c>
+      <c r="I43" s="15">
+        <f t="shared" ref="I43" si="58">IF(SUM(B43:F43,H43)=0,"",SUM(B43:F43,H43))</f>
+        <v>1010</v>
+      </c>
+      <c r="J43" s="15">
+        <f>IF(I43="","",1440-I43)</f>
+        <v>430</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N43" s="17"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="8"/>
@@ -3356,11 +3378,11 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
       <c r="I70" s="10" t="str">
-        <f t="shared" ref="I70:I133" si="58">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="59">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="10" t="str">
-        <f t="shared" ref="J70:J133" si="59">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="60">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="11"/>
@@ -3378,11 +3400,11 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
       <c r="I71" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J71" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K71" s="11"/>
@@ -3400,11 +3422,11 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
       <c r="I72" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J72" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K72" s="11"/>
@@ -3422,11 +3444,11 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
       <c r="I73" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J73" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K73" s="11"/>
@@ -3444,11 +3466,11 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
       <c r="I74" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J74" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K74" s="11"/>
@@ -3466,11 +3488,11 @@
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="I75" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J75" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K75" s="11"/>
@@ -3488,11 +3510,11 @@
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="I76" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J76" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K76" s="11"/>
@@ -3510,11 +3532,11 @@
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J77" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K77" s="11"/>
@@ -3532,11 +3554,11 @@
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J78" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K78" s="11"/>
@@ -3554,11 +3576,11 @@
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J79" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K79" s="11"/>
@@ -3576,11 +3598,11 @@
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J80" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K80" s="11"/>
@@ -3598,11 +3620,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J81" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -3620,11 +3642,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J82" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -3642,11 +3664,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J83" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -3664,11 +3686,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J84" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -3686,11 +3708,11 @@
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
       <c r="I85" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J85" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K85" s="11"/>
@@ -3708,11 +3730,11 @@
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J86" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K86" s="11"/>
@@ -3730,11 +3752,11 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
       <c r="I87" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J87" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K87" s="11"/>
@@ -3752,11 +3774,11 @@
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
       <c r="I88" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J88" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K88" s="11"/>
@@ -3774,11 +3796,11 @@
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
       <c r="I89" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J89" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K89" s="11"/>
@@ -3796,11 +3818,11 @@
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
       <c r="I90" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J90" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K90" s="11"/>
@@ -3818,11 +3840,11 @@
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
       <c r="I91" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J91" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K91" s="11"/>
@@ -3840,11 +3862,11 @@
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
       <c r="I92" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J92" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K92" s="11"/>
@@ -3862,11 +3884,11 @@
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
       <c r="I93" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J93" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K93" s="11"/>
@@ -3884,11 +3906,11 @@
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
       <c r="I94" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J94" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K94" s="11"/>
@@ -3906,11 +3928,11 @@
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
       <c r="I95" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J95" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K95" s="11"/>
@@ -3928,11 +3950,11 @@
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
       <c r="I96" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J96" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K96" s="11"/>
@@ -3950,11 +3972,11 @@
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J97" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K97" s="11"/>
@@ -3972,11 +3994,11 @@
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
       <c r="I98" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J98" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K98" s="11"/>
@@ -3994,11 +4016,11 @@
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
       <c r="I99" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J99" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K99" s="11"/>
@@ -4016,11 +4038,11 @@
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
       <c r="I100" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J100" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K100" s="11"/>
@@ -4038,11 +4060,11 @@
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
       <c r="I101" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J101" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K101" s="11"/>
@@ -4060,11 +4082,11 @@
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
       <c r="I102" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J102" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K102" s="11"/>
@@ -4082,11 +4104,11 @@
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J103" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K103" s="11"/>
@@ -4104,11 +4126,11 @@
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
       <c r="I104" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J104" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K104" s="11"/>
@@ -4126,11 +4148,11 @@
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
       <c r="I105" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J105" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K105" s="11"/>
@@ -4148,11 +4170,11 @@
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
       <c r="I106" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J106" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K106" s="11"/>
@@ -4170,11 +4192,11 @@
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J107" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K107" s="11"/>
@@ -4192,11 +4214,11 @@
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
       <c r="I108" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J108" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K108" s="11"/>
@@ -4214,11 +4236,11 @@
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J109" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K109" s="11"/>
@@ -4236,11 +4258,11 @@
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J110" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K110" s="11"/>
@@ -4258,11 +4280,11 @@
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J111" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K111" s="11"/>
@@ -4280,11 +4302,11 @@
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J112" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K112" s="11"/>
@@ -4302,11 +4324,11 @@
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J113" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K113" s="11"/>
@@ -4324,11 +4346,11 @@
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
       <c r="I114" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J114" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K114" s="11"/>
@@ -4346,11 +4368,11 @@
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
       <c r="I115" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J115" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K115" s="11"/>
@@ -4368,11 +4390,11 @@
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
       <c r="I116" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J116" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K116" s="11"/>
@@ -4390,11 +4412,11 @@
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
       <c r="I117" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J117" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K117" s="11"/>
@@ -4412,11 +4434,11 @@
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J118" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K118" s="11"/>
@@ -4434,11 +4456,11 @@
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
       <c r="I119" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J119" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K119" s="11"/>
@@ -4456,11 +4478,11 @@
       <c r="G120" s="9"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J120" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K120" s="11"/>
@@ -4478,11 +4500,11 @@
       <c r="G121" s="9"/>
       <c r="H121" s="9"/>
       <c r="I121" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J121" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K121" s="11"/>
@@ -4500,11 +4522,11 @@
       <c r="G122" s="9"/>
       <c r="H122" s="9"/>
       <c r="I122" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J122" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K122" s="11"/>
@@ -4522,11 +4544,11 @@
       <c r="G123" s="9"/>
       <c r="H123" s="9"/>
       <c r="I123" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J123" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K123" s="11"/>
@@ -4544,11 +4566,11 @@
       <c r="G124" s="9"/>
       <c r="H124" s="9"/>
       <c r="I124" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J124" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K124" s="11"/>
@@ -4566,11 +4588,11 @@
       <c r="G125" s="9"/>
       <c r="H125" s="9"/>
       <c r="I125" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J125" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K125" s="11"/>
@@ -4588,11 +4610,11 @@
       <c r="G126" s="9"/>
       <c r="H126" s="9"/>
       <c r="I126" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J126" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K126" s="11"/>
@@ -4610,11 +4632,11 @@
       <c r="G127" s="9"/>
       <c r="H127" s="9"/>
       <c r="I127" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J127" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K127" s="11"/>
@@ -4632,11 +4654,11 @@
       <c r="G128" s="9"/>
       <c r="H128" s="9"/>
       <c r="I128" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J128" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K128" s="11"/>
@@ -4654,11 +4676,11 @@
       <c r="G129" s="9"/>
       <c r="H129" s="9"/>
       <c r="I129" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J129" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K129" s="11"/>
@@ -4676,11 +4698,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -4698,11 +4720,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -4720,11 +4742,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -4742,11 +4764,11 @@
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
       <c r="I133" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="J133" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="K133" s="11"/>
@@ -4764,11 +4786,11 @@
       <c r="G134" s="9"/>
       <c r="H134" s="9"/>
       <c r="I134" s="10" t="str">
-        <f t="shared" ref="I134:I197" si="60">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="61">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="10" t="str">
-        <f t="shared" ref="J134:J197" si="61">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="62">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="11"/>
@@ -4786,11 +4808,11 @@
       <c r="G135" s="9"/>
       <c r="H135" s="9"/>
       <c r="I135" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J135" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K135" s="11"/>
@@ -4808,11 +4830,11 @@
       <c r="G136" s="9"/>
       <c r="H136" s="9"/>
       <c r="I136" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J136" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K136" s="11"/>
@@ -4830,11 +4852,11 @@
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
       <c r="I137" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J137" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K137" s="11"/>
@@ -4852,11 +4874,11 @@
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J138" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K138" s="11"/>
@@ -4874,11 +4896,11 @@
       <c r="G139" s="9"/>
       <c r="H139" s="9"/>
       <c r="I139" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J139" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K139" s="11"/>
@@ -4896,11 +4918,11 @@
       <c r="G140" s="9"/>
       <c r="H140" s="9"/>
       <c r="I140" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J140" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K140" s="11"/>
@@ -4918,11 +4940,11 @@
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
       <c r="I141" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J141" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K141" s="11"/>
@@ -4940,11 +4962,11 @@
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J142" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K142" s="11"/>
@@ -4962,11 +4984,11 @@
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
       <c r="I143" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J143" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K143" s="11"/>
@@ -4984,11 +5006,11 @@
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
       <c r="I144" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J144" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K144" s="11"/>
@@ -5006,11 +5028,11 @@
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J145" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K145" s="11"/>
@@ -5028,11 +5050,11 @@
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J146" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K146" s="11"/>
@@ -5050,11 +5072,11 @@
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
       <c r="I147" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J147" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K147" s="11"/>
@@ -5072,11 +5094,11 @@
       <c r="G148" s="9"/>
       <c r="H148" s="9"/>
       <c r="I148" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J148" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K148" s="11"/>
@@ -5094,11 +5116,11 @@
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
       <c r="I149" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J149" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K149" s="11"/>
@@ -5116,11 +5138,11 @@
       <c r="G150" s="9"/>
       <c r="H150" s="9"/>
       <c r="I150" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J150" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K150" s="11"/>
@@ -5138,11 +5160,11 @@
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
       <c r="I151" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J151" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K151" s="11"/>
@@ -5160,11 +5182,11 @@
       <c r="G152" s="9"/>
       <c r="H152" s="9"/>
       <c r="I152" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J152" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K152" s="11"/>
@@ -5182,11 +5204,11 @@
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
       <c r="I153" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J153" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K153" s="11"/>
@@ -5204,11 +5226,11 @@
       <c r="G154" s="9"/>
       <c r="H154" s="9"/>
       <c r="I154" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J154" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K154" s="11"/>
@@ -5226,11 +5248,11 @@
       <c r="G155" s="9"/>
       <c r="H155" s="9"/>
       <c r="I155" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J155" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K155" s="11"/>
@@ -5248,11 +5270,11 @@
       <c r="G156" s="9"/>
       <c r="H156" s="9"/>
       <c r="I156" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J156" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K156" s="11"/>
@@ -5270,11 +5292,11 @@
       <c r="G157" s="9"/>
       <c r="H157" s="9"/>
       <c r="I157" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J157" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K157" s="11"/>
@@ -5292,11 +5314,11 @@
       <c r="G158" s="9"/>
       <c r="H158" s="9"/>
       <c r="I158" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J158" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K158" s="11"/>
@@ -5314,11 +5336,11 @@
       <c r="G159" s="9"/>
       <c r="H159" s="9"/>
       <c r="I159" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J159" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K159" s="11"/>
@@ -5336,11 +5358,11 @@
       <c r="G160" s="9"/>
       <c r="H160" s="9"/>
       <c r="I160" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J160" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K160" s="11"/>
@@ -5358,11 +5380,11 @@
       <c r="G161" s="9"/>
       <c r="H161" s="9"/>
       <c r="I161" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J161" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K161" s="11"/>
@@ -5380,11 +5402,11 @@
       <c r="G162" s="9"/>
       <c r="H162" s="9"/>
       <c r="I162" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J162" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K162" s="11"/>
@@ -5402,11 +5424,11 @@
       <c r="G163" s="9"/>
       <c r="H163" s="9"/>
       <c r="I163" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J163" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K163" s="11"/>
@@ -5424,11 +5446,11 @@
       <c r="G164" s="9"/>
       <c r="H164" s="9"/>
       <c r="I164" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J164" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K164" s="11"/>
@@ -5446,11 +5468,11 @@
       <c r="G165" s="9"/>
       <c r="H165" s="9"/>
       <c r="I165" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J165" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K165" s="11"/>
@@ -5468,11 +5490,11 @@
       <c r="G166" s="9"/>
       <c r="H166" s="9"/>
       <c r="I166" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J166" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K166" s="11"/>
@@ -5490,11 +5512,11 @@
       <c r="G167" s="9"/>
       <c r="H167" s="9"/>
       <c r="I167" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J167" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K167" s="11"/>
@@ -5512,11 +5534,11 @@
       <c r="G168" s="9"/>
       <c r="H168" s="9"/>
       <c r="I168" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J168" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K168" s="11"/>
@@ -5534,11 +5556,11 @@
       <c r="G169" s="9"/>
       <c r="H169" s="9"/>
       <c r="I169" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J169" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K169" s="11"/>
@@ -5556,11 +5578,11 @@
       <c r="G170" s="9"/>
       <c r="H170" s="9"/>
       <c r="I170" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J170" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K170" s="11"/>
@@ -5578,11 +5600,11 @@
       <c r="G171" s="9"/>
       <c r="H171" s="9"/>
       <c r="I171" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J171" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K171" s="11"/>
@@ -5600,11 +5622,11 @@
       <c r="G172" s="9"/>
       <c r="H172" s="9"/>
       <c r="I172" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J172" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K172" s="11"/>
@@ -5622,11 +5644,11 @@
       <c r="G173" s="9"/>
       <c r="H173" s="9"/>
       <c r="I173" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J173" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K173" s="11"/>
@@ -5644,11 +5666,11 @@
       <c r="G174" s="9"/>
       <c r="H174" s="9"/>
       <c r="I174" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J174" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K174" s="11"/>
@@ -5666,11 +5688,11 @@
       <c r="G175" s="9"/>
       <c r="H175" s="9"/>
       <c r="I175" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J175" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K175" s="11"/>
@@ -5688,11 +5710,11 @@
       <c r="G176" s="9"/>
       <c r="H176" s="9"/>
       <c r="I176" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J176" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K176" s="11"/>
@@ -5710,11 +5732,11 @@
       <c r="G177" s="9"/>
       <c r="H177" s="9"/>
       <c r="I177" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J177" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K177" s="11"/>
@@ -5732,11 +5754,11 @@
       <c r="G178" s="9"/>
       <c r="H178" s="9"/>
       <c r="I178" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J178" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K178" s="11"/>
@@ -5754,11 +5776,11 @@
       <c r="G179" s="9"/>
       <c r="H179" s="9"/>
       <c r="I179" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J179" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K179" s="11"/>
@@ -5776,11 +5798,11 @@
       <c r="G180" s="9"/>
       <c r="H180" s="9"/>
       <c r="I180" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J180" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K180" s="11"/>
@@ -5798,11 +5820,11 @@
       <c r="G181" s="9"/>
       <c r="H181" s="9"/>
       <c r="I181" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J181" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K181" s="11"/>
@@ -5820,11 +5842,11 @@
       <c r="G182" s="9"/>
       <c r="H182" s="9"/>
       <c r="I182" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J182" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K182" s="11"/>
@@ -5842,11 +5864,11 @@
       <c r="G183" s="9"/>
       <c r="H183" s="9"/>
       <c r="I183" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J183" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K183" s="11"/>
@@ -5864,11 +5886,11 @@
       <c r="G184" s="9"/>
       <c r="H184" s="9"/>
       <c r="I184" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J184" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K184" s="11"/>
@@ -5886,11 +5908,11 @@
       <c r="G185" s="9"/>
       <c r="H185" s="9"/>
       <c r="I185" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J185" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K185" s="11"/>
@@ -5908,11 +5930,11 @@
       <c r="G186" s="9"/>
       <c r="H186" s="9"/>
       <c r="I186" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J186" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K186" s="11"/>
@@ -5930,11 +5952,11 @@
       <c r="G187" s="9"/>
       <c r="H187" s="9"/>
       <c r="I187" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J187" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K187" s="11"/>
@@ -5952,11 +5974,11 @@
       <c r="G188" s="9"/>
       <c r="H188" s="9"/>
       <c r="I188" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J188" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K188" s="11"/>
@@ -5974,11 +5996,11 @@
       <c r="G189" s="9"/>
       <c r="H189" s="9"/>
       <c r="I189" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J189" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K189" s="11"/>
@@ -5996,11 +6018,11 @@
       <c r="G190" s="9"/>
       <c r="H190" s="9"/>
       <c r="I190" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J190" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K190" s="11"/>
@@ -6018,11 +6040,11 @@
       <c r="G191" s="9"/>
       <c r="H191" s="9"/>
       <c r="I191" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J191" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K191" s="11"/>
@@ -6040,11 +6062,11 @@
       <c r="G192" s="9"/>
       <c r="H192" s="9"/>
       <c r="I192" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J192" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K192" s="11"/>
@@ -6062,11 +6084,11 @@
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J193" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K193" s="11"/>
@@ -6084,11 +6106,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -6106,11 +6128,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -6128,11 +6150,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -6150,11 +6172,11 @@
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J197" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="K197" s="11"/>
@@ -6172,11 +6194,11 @@
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
       <c r="I198" s="10" t="str">
-        <f t="shared" ref="I198:I261" si="62">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="63">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="10" t="str">
-        <f t="shared" ref="J198:J261" si="63">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="64">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="11"/>
@@ -6194,11 +6216,11 @@
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
       <c r="I199" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J199" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K199" s="11"/>
@@ -6216,11 +6238,11 @@
       <c r="G200" s="9"/>
       <c r="H200" s="9"/>
       <c r="I200" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J200" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K200" s="11"/>
@@ -6238,11 +6260,11 @@
       <c r="G201" s="9"/>
       <c r="H201" s="9"/>
       <c r="I201" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J201" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K201" s="11"/>
@@ -6260,11 +6282,11 @@
       <c r="G202" s="9"/>
       <c r="H202" s="9"/>
       <c r="I202" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J202" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K202" s="11"/>
@@ -6282,11 +6304,11 @@
       <c r="G203" s="9"/>
       <c r="H203" s="9"/>
       <c r="I203" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J203" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K203" s="11"/>
@@ -6304,11 +6326,11 @@
       <c r="G204" s="9"/>
       <c r="H204" s="9"/>
       <c r="I204" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J204" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K204" s="11"/>
@@ -6326,11 +6348,11 @@
       <c r="G205" s="9"/>
       <c r="H205" s="9"/>
       <c r="I205" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J205" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K205" s="11"/>
@@ -6348,11 +6370,11 @@
       <c r="G206" s="9"/>
       <c r="H206" s="9"/>
       <c r="I206" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J206" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K206" s="11"/>
@@ -6370,11 +6392,11 @@
       <c r="G207" s="9"/>
       <c r="H207" s="9"/>
       <c r="I207" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J207" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K207" s="11"/>
@@ -6392,11 +6414,11 @@
       <c r="G208" s="9"/>
       <c r="H208" s="9"/>
       <c r="I208" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J208" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K208" s="11"/>
@@ -6414,11 +6436,11 @@
       <c r="G209" s="9"/>
       <c r="H209" s="9"/>
       <c r="I209" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J209" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K209" s="11"/>
@@ -6436,11 +6458,11 @@
       <c r="G210" s="9"/>
       <c r="H210" s="9"/>
       <c r="I210" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J210" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K210" s="11"/>
@@ -6458,11 +6480,11 @@
       <c r="G211" s="9"/>
       <c r="H211" s="9"/>
       <c r="I211" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J211" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K211" s="11"/>
@@ -6480,11 +6502,11 @@
       <c r="G212" s="9"/>
       <c r="H212" s="9"/>
       <c r="I212" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J212" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K212" s="11"/>
@@ -6502,11 +6524,11 @@
       <c r="G213" s="9"/>
       <c r="H213" s="9"/>
       <c r="I213" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J213" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K213" s="11"/>
@@ -6524,11 +6546,11 @@
       <c r="G214" s="9"/>
       <c r="H214" s="9"/>
       <c r="I214" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J214" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K214" s="11"/>
@@ -6546,11 +6568,11 @@
       <c r="G215" s="9"/>
       <c r="H215" s="9"/>
       <c r="I215" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J215" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K215" s="11"/>
@@ -6568,11 +6590,11 @@
       <c r="G216" s="9"/>
       <c r="H216" s="9"/>
       <c r="I216" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J216" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K216" s="11"/>
@@ -6590,11 +6612,11 @@
       <c r="G217" s="9"/>
       <c r="H217" s="9"/>
       <c r="I217" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J217" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K217" s="11"/>
@@ -6612,11 +6634,11 @@
       <c r="G218" s="9"/>
       <c r="H218" s="9"/>
       <c r="I218" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J218" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K218" s="11"/>
@@ -6634,11 +6656,11 @@
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
       <c r="I219" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J219" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K219" s="11"/>
@@ -6656,11 +6678,11 @@
       <c r="G220" s="9"/>
       <c r="H220" s="9"/>
       <c r="I220" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J220" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K220" s="11"/>
@@ -6678,11 +6700,11 @@
       <c r="G221" s="9"/>
       <c r="H221" s="9"/>
       <c r="I221" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J221" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K221" s="11"/>
@@ -6700,11 +6722,11 @@
       <c r="G222" s="9"/>
       <c r="H222" s="9"/>
       <c r="I222" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J222" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K222" s="11"/>
@@ -6722,11 +6744,11 @@
       <c r="G223" s="9"/>
       <c r="H223" s="9"/>
       <c r="I223" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J223" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K223" s="11"/>
@@ -6744,11 +6766,11 @@
       <c r="G224" s="9"/>
       <c r="H224" s="9"/>
       <c r="I224" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J224" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K224" s="11"/>
@@ -6766,11 +6788,11 @@
       <c r="G225" s="9"/>
       <c r="H225" s="9"/>
       <c r="I225" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J225" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K225" s="11"/>
@@ -6788,11 +6810,11 @@
       <c r="G226" s="9"/>
       <c r="H226" s="9"/>
       <c r="I226" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J226" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K226" s="11"/>
@@ -6810,11 +6832,11 @@
       <c r="G227" s="9"/>
       <c r="H227" s="9"/>
       <c r="I227" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J227" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K227" s="11"/>
@@ -6832,11 +6854,11 @@
       <c r="G228" s="9"/>
       <c r="H228" s="9"/>
       <c r="I228" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J228" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K228" s="11"/>
@@ -6854,11 +6876,11 @@
       <c r="G229" s="9"/>
       <c r="H229" s="9"/>
       <c r="I229" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J229" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K229" s="11"/>
@@ -6876,11 +6898,11 @@
       <c r="G230" s="9"/>
       <c r="H230" s="9"/>
       <c r="I230" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J230" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K230" s="11"/>
@@ -6898,11 +6920,11 @@
       <c r="G231" s="9"/>
       <c r="H231" s="9"/>
       <c r="I231" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J231" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K231" s="11"/>
@@ -6920,11 +6942,11 @@
       <c r="G232" s="9"/>
       <c r="H232" s="9"/>
       <c r="I232" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J232" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K232" s="11"/>
@@ -6942,11 +6964,11 @@
       <c r="G233" s="9"/>
       <c r="H233" s="9"/>
       <c r="I233" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J233" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K233" s="11"/>
@@ -6964,11 +6986,11 @@
       <c r="G234" s="9"/>
       <c r="H234" s="9"/>
       <c r="I234" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J234" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K234" s="11"/>
@@ -6986,11 +7008,11 @@
       <c r="G235" s="9"/>
       <c r="H235" s="9"/>
       <c r="I235" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J235" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K235" s="11"/>
@@ -7008,11 +7030,11 @@
       <c r="G236" s="9"/>
       <c r="H236" s="9"/>
       <c r="I236" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J236" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K236" s="11"/>
@@ -7030,11 +7052,11 @@
       <c r="G237" s="9"/>
       <c r="H237" s="9"/>
       <c r="I237" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J237" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K237" s="11"/>
@@ -7052,11 +7074,11 @@
       <c r="G238" s="9"/>
       <c r="H238" s="9"/>
       <c r="I238" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J238" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K238" s="11"/>
@@ -7074,11 +7096,11 @@
       <c r="G239" s="9"/>
       <c r="H239" s="9"/>
       <c r="I239" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J239" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K239" s="11"/>
@@ -7096,11 +7118,11 @@
       <c r="G240" s="9"/>
       <c r="H240" s="9"/>
       <c r="I240" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J240" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K240" s="11"/>
@@ -7118,11 +7140,11 @@
       <c r="G241" s="9"/>
       <c r="H241" s="9"/>
       <c r="I241" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J241" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K241" s="11"/>
@@ -7140,11 +7162,11 @@
       <c r="G242" s="9"/>
       <c r="H242" s="9"/>
       <c r="I242" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J242" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K242" s="11"/>
@@ -7162,11 +7184,11 @@
       <c r="G243" s="9"/>
       <c r="H243" s="9"/>
       <c r="I243" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J243" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K243" s="11"/>
@@ -7184,11 +7206,11 @@
       <c r="G244" s="9"/>
       <c r="H244" s="9"/>
       <c r="I244" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J244" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K244" s="11"/>
@@ -7206,11 +7228,11 @@
       <c r="G245" s="9"/>
       <c r="H245" s="9"/>
       <c r="I245" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J245" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K245" s="11"/>
@@ -7228,11 +7250,11 @@
       <c r="G246" s="9"/>
       <c r="H246" s="9"/>
       <c r="I246" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J246" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K246" s="11"/>
@@ -7250,11 +7272,11 @@
       <c r="G247" s="9"/>
       <c r="H247" s="9"/>
       <c r="I247" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J247" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K247" s="11"/>
@@ -7272,11 +7294,11 @@
       <c r="G248" s="9"/>
       <c r="H248" s="9"/>
       <c r="I248" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J248" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K248" s="11"/>
@@ -7294,11 +7316,11 @@
       <c r="G249" s="9"/>
       <c r="H249" s="9"/>
       <c r="I249" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J249" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K249" s="11"/>
@@ -7316,11 +7338,11 @@
       <c r="G250" s="9"/>
       <c r="H250" s="9"/>
       <c r="I250" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J250" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K250" s="11"/>
@@ -7338,11 +7360,11 @@
       <c r="G251" s="9"/>
       <c r="H251" s="9"/>
       <c r="I251" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J251" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K251" s="11"/>
@@ -7360,11 +7382,11 @@
       <c r="G252" s="9"/>
       <c r="H252" s="9"/>
       <c r="I252" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J252" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K252" s="11"/>
@@ -7382,11 +7404,11 @@
       <c r="G253" s="9"/>
       <c r="H253" s="9"/>
       <c r="I253" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J253" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K253" s="11"/>
@@ -7404,11 +7426,11 @@
       <c r="G254" s="9"/>
       <c r="H254" s="9"/>
       <c r="I254" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J254" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K254" s="11"/>
@@ -7426,11 +7448,11 @@
       <c r="G255" s="9"/>
       <c r="H255" s="9"/>
       <c r="I255" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J255" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K255" s="11"/>
@@ -7448,11 +7470,11 @@
       <c r="G256" s="9"/>
       <c r="H256" s="9"/>
       <c r="I256" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J256" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K256" s="11"/>
@@ -7470,11 +7492,11 @@
       <c r="G257" s="9"/>
       <c r="H257" s="9"/>
       <c r="I257" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J257" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K257" s="11"/>
@@ -7492,11 +7514,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -7514,11 +7536,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -7536,11 +7558,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -7558,11 +7580,11 @@
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
       <c r="I261" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="J261" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="K261" s="11"/>
@@ -7580,11 +7602,11 @@
       <c r="G262" s="9"/>
       <c r="H262" s="9"/>
       <c r="I262" s="10" t="str">
-        <f t="shared" ref="I262:I325" si="64">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="65">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="10" t="str">
-        <f t="shared" ref="J262:J325" si="65">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="66">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="11"/>
@@ -7602,11 +7624,11 @@
       <c r="G263" s="9"/>
       <c r="H263" s="9"/>
       <c r="I263" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J263" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K263" s="11"/>
@@ -7624,11 +7646,11 @@
       <c r="G264" s="9"/>
       <c r="H264" s="9"/>
       <c r="I264" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J264" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K264" s="11"/>
@@ -7646,11 +7668,11 @@
       <c r="G265" s="9"/>
       <c r="H265" s="9"/>
       <c r="I265" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J265" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K265" s="11"/>
@@ -7668,11 +7690,11 @@
       <c r="G266" s="9"/>
       <c r="H266" s="9"/>
       <c r="I266" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J266" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K266" s="11"/>
@@ -7690,11 +7712,11 @@
       <c r="G267" s="9"/>
       <c r="H267" s="9"/>
       <c r="I267" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J267" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K267" s="11"/>
@@ -7712,11 +7734,11 @@
       <c r="G268" s="9"/>
       <c r="H268" s="9"/>
       <c r="I268" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J268" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K268" s="11"/>
@@ -7734,11 +7756,11 @@
       <c r="G269" s="9"/>
       <c r="H269" s="9"/>
       <c r="I269" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J269" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K269" s="11"/>
@@ -7756,11 +7778,11 @@
       <c r="G270" s="9"/>
       <c r="H270" s="9"/>
       <c r="I270" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J270" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K270" s="11"/>
@@ -7778,11 +7800,11 @@
       <c r="G271" s="9"/>
       <c r="H271" s="9"/>
       <c r="I271" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J271" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K271" s="11"/>
@@ -7800,11 +7822,11 @@
       <c r="G272" s="9"/>
       <c r="H272" s="9"/>
       <c r="I272" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J272" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K272" s="11"/>
@@ -7822,11 +7844,11 @@
       <c r="G273" s="9"/>
       <c r="H273" s="9"/>
       <c r="I273" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J273" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K273" s="11"/>
@@ -7844,11 +7866,11 @@
       <c r="G274" s="9"/>
       <c r="H274" s="9"/>
       <c r="I274" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J274" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K274" s="11"/>
@@ -7866,11 +7888,11 @@
       <c r="G275" s="9"/>
       <c r="H275" s="9"/>
       <c r="I275" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J275" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K275" s="11"/>
@@ -7888,11 +7910,11 @@
       <c r="G276" s="9"/>
       <c r="H276" s="9"/>
       <c r="I276" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J276" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K276" s="11"/>
@@ -7910,11 +7932,11 @@
       <c r="G277" s="9"/>
       <c r="H277" s="9"/>
       <c r="I277" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J277" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K277" s="11"/>
@@ -7932,11 +7954,11 @@
       <c r="G278" s="9"/>
       <c r="H278" s="9"/>
       <c r="I278" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J278" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K278" s="11"/>
@@ -7954,11 +7976,11 @@
       <c r="G279" s="9"/>
       <c r="H279" s="9"/>
       <c r="I279" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J279" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K279" s="11"/>
@@ -7976,11 +7998,11 @@
       <c r="G280" s="9"/>
       <c r="H280" s="9"/>
       <c r="I280" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J280" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K280" s="11"/>
@@ -7998,11 +8020,11 @@
       <c r="G281" s="9"/>
       <c r="H281" s="9"/>
       <c r="I281" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J281" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K281" s="11"/>
@@ -8020,11 +8042,11 @@
       <c r="G282" s="9"/>
       <c r="H282" s="9"/>
       <c r="I282" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J282" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K282" s="11"/>
@@ -8042,11 +8064,11 @@
       <c r="G283" s="9"/>
       <c r="H283" s="9"/>
       <c r="I283" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J283" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K283" s="11"/>
@@ -8064,11 +8086,11 @@
       <c r="G284" s="9"/>
       <c r="H284" s="9"/>
       <c r="I284" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J284" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K284" s="11"/>
@@ -8086,11 +8108,11 @@
       <c r="G285" s="9"/>
       <c r="H285" s="9"/>
       <c r="I285" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J285" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K285" s="11"/>
@@ -8108,11 +8130,11 @@
       <c r="G286" s="9"/>
       <c r="H286" s="9"/>
       <c r="I286" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J286" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K286" s="11"/>
@@ -8130,11 +8152,11 @@
       <c r="G287" s="9"/>
       <c r="H287" s="9"/>
       <c r="I287" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J287" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K287" s="11"/>
@@ -8152,11 +8174,11 @@
       <c r="G288" s="9"/>
       <c r="H288" s="9"/>
       <c r="I288" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J288" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K288" s="11"/>
@@ -8174,11 +8196,11 @@
       <c r="G289" s="9"/>
       <c r="H289" s="9"/>
       <c r="I289" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J289" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K289" s="11"/>
@@ -8196,11 +8218,11 @@
       <c r="G290" s="9"/>
       <c r="H290" s="9"/>
       <c r="I290" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J290" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K290" s="11"/>
@@ -8218,11 +8240,11 @@
       <c r="G291" s="9"/>
       <c r="H291" s="9"/>
       <c r="I291" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J291" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K291" s="11"/>
@@ -8240,11 +8262,11 @@
       <c r="G292" s="9"/>
       <c r="H292" s="9"/>
       <c r="I292" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J292" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K292" s="11"/>
@@ -8262,11 +8284,11 @@
       <c r="G293" s="9"/>
       <c r="H293" s="9"/>
       <c r="I293" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J293" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K293" s="11"/>
@@ -8284,11 +8306,11 @@
       <c r="G294" s="9"/>
       <c r="H294" s="9"/>
       <c r="I294" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J294" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K294" s="11"/>
@@ -8306,11 +8328,11 @@
       <c r="G295" s="9"/>
       <c r="H295" s="9"/>
       <c r="I295" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J295" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K295" s="11"/>
@@ -8328,11 +8350,11 @@
       <c r="G296" s="9"/>
       <c r="H296" s="9"/>
       <c r="I296" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J296" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K296" s="11"/>
@@ -8350,11 +8372,11 @@
       <c r="G297" s="9"/>
       <c r="H297" s="9"/>
       <c r="I297" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J297" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K297" s="11"/>
@@ -8372,11 +8394,11 @@
       <c r="G298" s="9"/>
       <c r="H298" s="9"/>
       <c r="I298" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J298" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K298" s="11"/>
@@ -8394,11 +8416,11 @@
       <c r="G299" s="9"/>
       <c r="H299" s="9"/>
       <c r="I299" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J299" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K299" s="11"/>
@@ -8416,11 +8438,11 @@
       <c r="G300" s="9"/>
       <c r="H300" s="9"/>
       <c r="I300" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J300" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K300" s="11"/>
@@ -8438,11 +8460,11 @@
       <c r="G301" s="9"/>
       <c r="H301" s="9"/>
       <c r="I301" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J301" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K301" s="11"/>
@@ -8460,11 +8482,11 @@
       <c r="G302" s="9"/>
       <c r="H302" s="9"/>
       <c r="I302" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J302" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K302" s="11"/>
@@ -8482,11 +8504,11 @@
       <c r="G303" s="9"/>
       <c r="H303" s="9"/>
       <c r="I303" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J303" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K303" s="11"/>
@@ -8504,11 +8526,11 @@
       <c r="G304" s="9"/>
       <c r="H304" s="9"/>
       <c r="I304" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J304" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K304" s="11"/>
@@ -8526,11 +8548,11 @@
       <c r="G305" s="9"/>
       <c r="H305" s="9"/>
       <c r="I305" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J305" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K305" s="11"/>
@@ -8548,11 +8570,11 @@
       <c r="G306" s="9"/>
       <c r="H306" s="9"/>
       <c r="I306" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J306" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K306" s="11"/>
@@ -8570,11 +8592,11 @@
       <c r="G307" s="9"/>
       <c r="H307" s="9"/>
       <c r="I307" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J307" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K307" s="11"/>
@@ -8592,11 +8614,11 @@
       <c r="G308" s="9"/>
       <c r="H308" s="9"/>
       <c r="I308" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J308" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K308" s="11"/>
@@ -8614,11 +8636,11 @@
       <c r="G309" s="9"/>
       <c r="H309" s="9"/>
       <c r="I309" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J309" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K309" s="11"/>
@@ -8636,11 +8658,11 @@
       <c r="G310" s="9"/>
       <c r="H310" s="9"/>
       <c r="I310" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J310" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K310" s="11"/>
@@ -8658,11 +8680,11 @@
       <c r="G311" s="9"/>
       <c r="H311" s="9"/>
       <c r="I311" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J311" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K311" s="11"/>
@@ -8680,11 +8702,11 @@
       <c r="G312" s="9"/>
       <c r="H312" s="9"/>
       <c r="I312" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J312" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K312" s="11"/>
@@ -8702,11 +8724,11 @@
       <c r="G313" s="9"/>
       <c r="H313" s="9"/>
       <c r="I313" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J313" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K313" s="11"/>
@@ -8724,11 +8746,11 @@
       <c r="G314" s="9"/>
       <c r="H314" s="9"/>
       <c r="I314" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J314" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K314" s="11"/>
@@ -8746,11 +8768,11 @@
       <c r="G315" s="9"/>
       <c r="H315" s="9"/>
       <c r="I315" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J315" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K315" s="11"/>
@@ -8768,11 +8790,11 @@
       <c r="G316" s="9"/>
       <c r="H316" s="9"/>
       <c r="I316" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J316" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K316" s="11"/>
@@ -8790,11 +8812,11 @@
       <c r="G317" s="9"/>
       <c r="H317" s="9"/>
       <c r="I317" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J317" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K317" s="11"/>
@@ -8812,11 +8834,11 @@
       <c r="G318" s="9"/>
       <c r="H318" s="9"/>
       <c r="I318" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J318" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K318" s="11"/>
@@ -8834,11 +8856,11 @@
       <c r="G319" s="9"/>
       <c r="H319" s="9"/>
       <c r="I319" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J319" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K319" s="11"/>
@@ -8856,11 +8878,11 @@
       <c r="G320" s="9"/>
       <c r="H320" s="9"/>
       <c r="I320" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J320" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K320" s="11"/>
@@ -8878,11 +8900,11 @@
       <c r="G321" s="9"/>
       <c r="H321" s="9"/>
       <c r="I321" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J321" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K321" s="11"/>
@@ -8900,11 +8922,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -8922,11 +8944,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -8944,11 +8966,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -8966,11 +8988,11 @@
       <c r="G325" s="9"/>
       <c r="H325" s="9"/>
       <c r="I325" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J325" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="K325" s="11"/>
@@ -8988,11 +9010,11 @@
       <c r="G326" s="9"/>
       <c r="H326" s="9"/>
       <c r="I326" s="10" t="str">
-        <f t="shared" ref="I326:I389" si="66">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="67">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="10" t="str">
-        <f t="shared" ref="J326:J389" si="67">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="68">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="11"/>
@@ -9010,11 +9032,11 @@
       <c r="G327" s="9"/>
       <c r="H327" s="9"/>
       <c r="I327" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J327" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K327" s="11"/>
@@ -9032,11 +9054,11 @@
       <c r="G328" s="9"/>
       <c r="H328" s="9"/>
       <c r="I328" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J328" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K328" s="11"/>
@@ -9054,11 +9076,11 @@
       <c r="G329" s="9"/>
       <c r="H329" s="9"/>
       <c r="I329" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J329" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K329" s="11"/>
@@ -9076,11 +9098,11 @@
       <c r="G330" s="9"/>
       <c r="H330" s="9"/>
       <c r="I330" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J330" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K330" s="11"/>
@@ -9098,11 +9120,11 @@
       <c r="G331" s="9"/>
       <c r="H331" s="9"/>
       <c r="I331" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J331" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K331" s="11"/>
@@ -9120,11 +9142,11 @@
       <c r="G332" s="9"/>
       <c r="H332" s="9"/>
       <c r="I332" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J332" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K332" s="11"/>
@@ -9142,11 +9164,11 @@
       <c r="G333" s="9"/>
       <c r="H333" s="9"/>
       <c r="I333" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J333" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K333" s="11"/>
@@ -9164,11 +9186,11 @@
       <c r="G334" s="9"/>
       <c r="H334" s="9"/>
       <c r="I334" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J334" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K334" s="11"/>
@@ -9186,11 +9208,11 @@
       <c r="G335" s="9"/>
       <c r="H335" s="9"/>
       <c r="I335" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J335" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K335" s="11"/>
@@ -9208,11 +9230,11 @@
       <c r="G336" s="9"/>
       <c r="H336" s="9"/>
       <c r="I336" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J336" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K336" s="11"/>
@@ -9230,11 +9252,11 @@
       <c r="G337" s="9"/>
       <c r="H337" s="9"/>
       <c r="I337" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J337" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K337" s="11"/>
@@ -9252,11 +9274,11 @@
       <c r="G338" s="9"/>
       <c r="H338" s="9"/>
       <c r="I338" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J338" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K338" s="11"/>
@@ -9274,11 +9296,11 @@
       <c r="G339" s="9"/>
       <c r="H339" s="9"/>
       <c r="I339" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J339" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K339" s="11"/>
@@ -9296,11 +9318,11 @@
       <c r="G340" s="9"/>
       <c r="H340" s="9"/>
       <c r="I340" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J340" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K340" s="11"/>
@@ -9318,11 +9340,11 @@
       <c r="G341" s="9"/>
       <c r="H341" s="9"/>
       <c r="I341" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J341" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K341" s="11"/>
@@ -9340,11 +9362,11 @@
       <c r="G342" s="9"/>
       <c r="H342" s="9"/>
       <c r="I342" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J342" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K342" s="11"/>
@@ -9362,11 +9384,11 @@
       <c r="G343" s="9"/>
       <c r="H343" s="9"/>
       <c r="I343" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J343" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K343" s="11"/>
@@ -9384,11 +9406,11 @@
       <c r="G344" s="9"/>
       <c r="H344" s="9"/>
       <c r="I344" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J344" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K344" s="11"/>
@@ -9406,11 +9428,11 @@
       <c r="G345" s="9"/>
       <c r="H345" s="9"/>
       <c r="I345" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J345" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K345" s="11"/>
@@ -9428,11 +9450,11 @@
       <c r="G346" s="9"/>
       <c r="H346" s="9"/>
       <c r="I346" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J346" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K346" s="11"/>
@@ -9450,11 +9472,11 @@
       <c r="G347" s="9"/>
       <c r="H347" s="9"/>
       <c r="I347" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J347" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K347" s="11"/>
@@ -9472,11 +9494,11 @@
       <c r="G348" s="9"/>
       <c r="H348" s="9"/>
       <c r="I348" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J348" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K348" s="11"/>
@@ -9494,11 +9516,11 @@
       <c r="G349" s="9"/>
       <c r="H349" s="9"/>
       <c r="I349" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J349" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K349" s="11"/>
@@ -9516,11 +9538,11 @@
       <c r="G350" s="9"/>
       <c r="H350" s="9"/>
       <c r="I350" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J350" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K350" s="11"/>
@@ -9538,11 +9560,11 @@
       <c r="G351" s="9"/>
       <c r="H351" s="9"/>
       <c r="I351" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J351" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K351" s="11"/>
@@ -9560,11 +9582,11 @@
       <c r="G352" s="9"/>
       <c r="H352" s="9"/>
       <c r="I352" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J352" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K352" s="11"/>
@@ -9582,11 +9604,11 @@
       <c r="G353" s="9"/>
       <c r="H353" s="9"/>
       <c r="I353" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J353" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K353" s="11"/>
@@ -9604,11 +9626,11 @@
       <c r="G354" s="9"/>
       <c r="H354" s="9"/>
       <c r="I354" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J354" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K354" s="11"/>
@@ -9626,11 +9648,11 @@
       <c r="G355" s="9"/>
       <c r="H355" s="9"/>
       <c r="I355" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J355" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K355" s="11"/>
@@ -9648,11 +9670,11 @@
       <c r="G356" s="9"/>
       <c r="H356" s="9"/>
       <c r="I356" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J356" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K356" s="11"/>
@@ -9670,11 +9692,11 @@
       <c r="G357" s="9"/>
       <c r="H357" s="9"/>
       <c r="I357" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J357" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K357" s="11"/>
@@ -9692,11 +9714,11 @@
       <c r="G358" s="9"/>
       <c r="H358" s="9"/>
       <c r="I358" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J358" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K358" s="11"/>
@@ -9714,11 +9736,11 @@
       <c r="G359" s="9"/>
       <c r="H359" s="9"/>
       <c r="I359" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J359" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K359" s="11"/>
@@ -9736,11 +9758,11 @@
       <c r="G360" s="9"/>
       <c r="H360" s="9"/>
       <c r="I360" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J360" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K360" s="11"/>
@@ -9758,11 +9780,11 @@
       <c r="G361" s="9"/>
       <c r="H361" s="9"/>
       <c r="I361" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J361" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K361" s="11"/>
@@ -9780,11 +9802,11 @@
       <c r="G362" s="9"/>
       <c r="H362" s="9"/>
       <c r="I362" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J362" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K362" s="11"/>
@@ -9802,11 +9824,11 @@
       <c r="G363" s="9"/>
       <c r="H363" s="9"/>
       <c r="I363" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J363" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K363" s="11"/>
@@ -9824,11 +9846,11 @@
       <c r="G364" s="9"/>
       <c r="H364" s="9"/>
       <c r="I364" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J364" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K364" s="11"/>
@@ -9846,11 +9868,11 @@
       <c r="G365" s="9"/>
       <c r="H365" s="9"/>
       <c r="I365" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J365" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K365" s="11"/>
@@ -9868,11 +9890,11 @@
       <c r="G366" s="9"/>
       <c r="H366" s="9"/>
       <c r="I366" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J366" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K366" s="11"/>
@@ -9890,11 +9912,11 @@
       <c r="G367" s="9"/>
       <c r="H367" s="9"/>
       <c r="I367" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J367" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K367" s="11"/>
@@ -9912,11 +9934,11 @@
       <c r="G368" s="9"/>
       <c r="H368" s="9"/>
       <c r="I368" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J368" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K368" s="11"/>
@@ -9934,11 +9956,11 @@
       <c r="G369" s="9"/>
       <c r="H369" s="9"/>
       <c r="I369" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J369" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K369" s="11"/>
@@ -9956,11 +9978,11 @@
       <c r="G370" s="9"/>
       <c r="H370" s="9"/>
       <c r="I370" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J370" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K370" s="11"/>
@@ -9978,11 +10000,11 @@
       <c r="G371" s="9"/>
       <c r="H371" s="9"/>
       <c r="I371" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J371" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K371" s="11"/>
@@ -10000,11 +10022,11 @@
       <c r="G372" s="9"/>
       <c r="H372" s="9"/>
       <c r="I372" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J372" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K372" s="11"/>
@@ -10022,11 +10044,11 @@
       <c r="G373" s="9"/>
       <c r="H373" s="9"/>
       <c r="I373" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J373" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K373" s="11"/>
@@ -10044,11 +10066,11 @@
       <c r="G374" s="9"/>
       <c r="H374" s="9"/>
       <c r="I374" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J374" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K374" s="11"/>
@@ -10066,11 +10088,11 @@
       <c r="G375" s="9"/>
       <c r="H375" s="9"/>
       <c r="I375" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J375" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K375" s="11"/>
@@ -10088,11 +10110,11 @@
       <c r="G376" s="9"/>
       <c r="H376" s="9"/>
       <c r="I376" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J376" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K376" s="11"/>
@@ -10110,11 +10132,11 @@
       <c r="G377" s="9"/>
       <c r="H377" s="9"/>
       <c r="I377" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J377" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K377" s="11"/>
@@ -10132,11 +10154,11 @@
       <c r="G378" s="9"/>
       <c r="H378" s="9"/>
       <c r="I378" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J378" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K378" s="11"/>
@@ -10154,11 +10176,11 @@
       <c r="G379" s="9"/>
       <c r="H379" s="9"/>
       <c r="I379" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J379" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K379" s="11"/>
@@ -10176,11 +10198,11 @@
       <c r="G380" s="9"/>
       <c r="H380" s="9"/>
       <c r="I380" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J380" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K380" s="11"/>
@@ -10198,11 +10220,11 @@
       <c r="G381" s="9"/>
       <c r="H381" s="9"/>
       <c r="I381" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J381" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K381" s="11"/>
@@ -10220,11 +10242,11 @@
       <c r="G382" s="9"/>
       <c r="H382" s="9"/>
       <c r="I382" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J382" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K382" s="11"/>
@@ -10242,11 +10264,11 @@
       <c r="G383" s="9"/>
       <c r="H383" s="9"/>
       <c r="I383" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J383" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K383" s="11"/>
@@ -10264,11 +10286,11 @@
       <c r="G384" s="9"/>
       <c r="H384" s="9"/>
       <c r="I384" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J384" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K384" s="11"/>
@@ -10286,11 +10308,11 @@
       <c r="G385" s="9"/>
       <c r="H385" s="9"/>
       <c r="I385" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J385" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K385" s="11"/>
@@ -10308,11 +10330,11 @@
       <c r="G386" s="9"/>
       <c r="H386" s="9"/>
       <c r="I386" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J386" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K386" s="11"/>
@@ -10330,11 +10352,11 @@
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J387" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K387" s="11"/>
@@ -10352,11 +10374,11 @@
       <c r="G388" s="9"/>
       <c r="H388" s="9"/>
       <c r="I388" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J388" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K388" s="11"/>
@@ -10374,11 +10396,11 @@
       <c r="G389" s="9"/>
       <c r="H389" s="9"/>
       <c r="I389" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J389" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="K389" s="11"/>
@@ -10396,11 +10418,11 @@
       <c r="G390" s="9"/>
       <c r="H390" s="9"/>
       <c r="I390" s="10" t="str">
-        <f t="shared" ref="I390:I401" si="68">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="69">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="10" t="str">
-        <f t="shared" ref="J390:J401" si="69">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="70">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="11"/>
@@ -10418,11 +10440,11 @@
       <c r="G391" s="9"/>
       <c r="H391" s="9"/>
       <c r="I391" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="J391" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="K391" s="11"/>
@@ -10440,11 +10462,11 @@
       <c r="G392" s="9"/>
       <c r="H392" s="9"/>
       <c r="I392" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="J392" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="K392" s="11"/>
@@ -10462,11 +10484,11 @@
       <c r="G393" s="9"/>
       <c r="H393" s="9"/>
       <c r="I393" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="J393" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="K393" s="11"/>
@@ -10484,11 +10506,11 @@
       <c r="G394" s="9"/>
       <c r="H394" s="9"/>
       <c r="I394" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="J394" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="K394" s="11"/>
@@ -10506,11 +10528,11 @@
       <c r="G395" s="9"/>
       <c r="H395" s="9"/>
       <c r="I395" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="J395" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="K395" s="11"/>
@@ -10528,11 +10550,11 @@
       <c r="G396" s="9"/>
       <c r="H396" s="9"/>
       <c r="I396" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="J396" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="K396" s="11"/>
@@ -10550,11 +10572,11 @@
       <c r="G397" s="9"/>
       <c r="H397" s="9"/>
       <c r="I397" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="J397" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="K397" s="11"/>
@@ -10572,11 +10594,11 @@
       <c r="G398" s="9"/>
       <c r="H398" s="9"/>
       <c r="I398" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="J398" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="K398" s="11"/>
@@ -10594,11 +10616,11 @@
       <c r="G399" s="9"/>
       <c r="H399" s="9"/>
       <c r="I399" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="J399" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="K399" s="11"/>
@@ -10616,11 +10638,11 @@
       <c r="G400" s="9"/>
       <c r="H400" s="9"/>
       <c r="I400" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="J400" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="K400" s="11"/>
@@ -10638,11 +10660,11 @@
       <c r="G401" s="9"/>
       <c r="H401" s="9"/>
       <c r="I401" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="J401" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="K401" s="11"/>

--- a/12626731.xlsx
+++ b/12626731.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHIVEN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B515A85-30C8-418A-8A19-B9F855D443E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA721837-A712-4AFA-A943-A4701901C8F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2763,27 +2763,27 @@
         <v>0</v>
       </c>
       <c r="D43" s="14">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="E43" s="14">
         <v>20</v>
       </c>
       <c r="F43" s="14">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="G43" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H43" s="14">
         <v>270</v>
       </c>
       <c r="I43" s="15">
         <f t="shared" ref="I43" si="58">IF(SUM(B43:F43,H43)=0,"",SUM(B43:F43,H43))</f>
-        <v>1010</v>
+        <v>1080</v>
       </c>
       <c r="J43" s="15">
         <f>IF(I43="","",1440-I43)</f>
-        <v>430</v>
+        <v>360</v>
       </c>
       <c r="K43" s="16" t="s">
         <v>61</v>

--- a/12626731.xlsx
+++ b/12626731.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHIVEN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA721837-A712-4AFA-A943-A4701901C8F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73D2D594-B144-489F-8B22-84AD3954E8CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -272,6 +272,12 @@
   </si>
   <si>
     <t>Today, I worked on Coding Hackathon.</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Low</t>
   </si>
 </sst>
 </file>
@@ -2778,11 +2784,11 @@
         <v>270</v>
       </c>
       <c r="I43" s="15">
-        <f t="shared" ref="I43" si="58">IF(SUM(B43:F43,H43)=0,"",SUM(B43:F43,H43))</f>
+        <f t="shared" ref="I43:I48" si="58">IF(SUM(B43:F43,H43)=0,"",SUM(B43:F43,H43))</f>
         <v>1080</v>
       </c>
       <c r="J43" s="15">
-        <f>IF(I43="","",1440-I43)</f>
+        <f t="shared" ref="J43:J48" si="59">IF(I43="","",1440-I43)</f>
         <v>360</v>
       </c>
       <c r="K43" s="16" t="s">
@@ -2797,114 +2803,224 @@
       <c r="N43" s="17"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="8"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="11"/>
-      <c r="L44" s="11"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="12"/>
+      <c r="A44" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B44" s="14">
+        <v>400</v>
+      </c>
+      <c r="C44" s="14">
+        <v>0</v>
+      </c>
+      <c r="D44" s="14">
+        <v>240</v>
+      </c>
+      <c r="E44" s="14">
+        <v>0</v>
+      </c>
+      <c r="F44" s="14">
+        <v>0</v>
+      </c>
+      <c r="G44" s="14">
+        <v>0</v>
+      </c>
+      <c r="H44" s="14">
+        <v>270</v>
+      </c>
+      <c r="I44" s="15">
+        <f t="shared" si="58"/>
+        <v>910</v>
+      </c>
+      <c r="J44" s="15">
+        <f t="shared" si="59"/>
+        <v>530</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N44" s="17"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="8"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="11"/>
-      <c r="L45" s="11"/>
-      <c r="M45" s="11"/>
-      <c r="N45" s="12"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="8"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9"/>
-      <c r="I46" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="11"/>
-      <c r="L46" s="11"/>
-      <c r="M46" s="11"/>
-      <c r="N46" s="12"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="8"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="9"/>
-      <c r="H47" s="9"/>
-      <c r="I47" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="11"/>
-      <c r="L47" s="11"/>
-      <c r="M47" s="11"/>
-      <c r="N47" s="12"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="8"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="9"/>
-      <c r="H48" s="9"/>
-      <c r="I48" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="11"/>
-      <c r="L48" s="11"/>
-      <c r="M48" s="11"/>
-      <c r="N48" s="12"/>
+      <c r="A45" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B45" s="14">
+        <v>400</v>
+      </c>
+      <c r="C45" s="14">
+        <v>0</v>
+      </c>
+      <c r="D45" s="14">
+        <v>180</v>
+      </c>
+      <c r="E45" s="14">
+        <v>0</v>
+      </c>
+      <c r="F45" s="14">
+        <v>0</v>
+      </c>
+      <c r="G45" s="14">
+        <v>0</v>
+      </c>
+      <c r="H45" s="14">
+        <v>270</v>
+      </c>
+      <c r="I45" s="15">
+        <f t="shared" si="58"/>
+        <v>850</v>
+      </c>
+      <c r="J45" s="15">
+        <f t="shared" si="59"/>
+        <v>590</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N45" s="17"/>
+    </row>
+    <row r="46" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B46" s="14">
+        <v>400</v>
+      </c>
+      <c r="C46" s="14">
+        <v>0</v>
+      </c>
+      <c r="D46" s="14">
+        <v>0</v>
+      </c>
+      <c r="E46" s="14">
+        <v>0</v>
+      </c>
+      <c r="F46" s="14">
+        <v>0</v>
+      </c>
+      <c r="G46" s="14">
+        <v>0</v>
+      </c>
+      <c r="H46" s="14">
+        <v>270</v>
+      </c>
+      <c r="I46" s="15">
+        <f t="shared" si="58"/>
+        <v>670</v>
+      </c>
+      <c r="J46" s="15">
+        <f t="shared" si="59"/>
+        <v>770</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N46" s="17"/>
+    </row>
+    <row r="47" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B47" s="14">
+        <v>400</v>
+      </c>
+      <c r="C47" s="14">
+        <v>0</v>
+      </c>
+      <c r="D47" s="14">
+        <v>0</v>
+      </c>
+      <c r="E47" s="14">
+        <v>20</v>
+      </c>
+      <c r="F47" s="14">
+        <v>0</v>
+      </c>
+      <c r="G47" s="14">
+        <v>0</v>
+      </c>
+      <c r="H47" s="14">
+        <v>270</v>
+      </c>
+      <c r="I47" s="15">
+        <f t="shared" si="58"/>
+        <v>690</v>
+      </c>
+      <c r="J47" s="15">
+        <f t="shared" si="59"/>
+        <v>750</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N47" s="17"/>
+    </row>
+    <row r="48" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B48" s="14">
+        <v>400</v>
+      </c>
+      <c r="C48" s="14">
+        <v>0</v>
+      </c>
+      <c r="D48" s="14">
+        <v>70</v>
+      </c>
+      <c r="E48" s="14">
+        <v>50</v>
+      </c>
+      <c r="F48" s="14">
+        <v>300</v>
+      </c>
+      <c r="G48" s="14">
+        <v>6</v>
+      </c>
+      <c r="H48" s="14">
+        <v>270</v>
+      </c>
+      <c r="I48" s="15">
+        <f t="shared" si="58"/>
+        <v>1090</v>
+      </c>
+      <c r="J48" s="15">
+        <f t="shared" si="59"/>
+        <v>350</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N48" s="17"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="8"/>
@@ -3378,11 +3494,11 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
       <c r="I70" s="10" t="str">
-        <f t="shared" ref="I70:I133" si="59">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="60">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="10" t="str">
-        <f t="shared" ref="J70:J133" si="60">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="61">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="11"/>
@@ -3400,11 +3516,11 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
       <c r="I71" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J71" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K71" s="11"/>
@@ -3422,11 +3538,11 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
       <c r="I72" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J72" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K72" s="11"/>
@@ -3444,11 +3560,11 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
       <c r="I73" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J73" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K73" s="11"/>
@@ -3466,11 +3582,11 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
       <c r="I74" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J74" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K74" s="11"/>
@@ -3488,11 +3604,11 @@
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="I75" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J75" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K75" s="11"/>
@@ -3510,11 +3626,11 @@
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="I76" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J76" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K76" s="11"/>
@@ -3532,11 +3648,11 @@
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J77" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K77" s="11"/>
@@ -3554,11 +3670,11 @@
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J78" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K78" s="11"/>
@@ -3576,11 +3692,11 @@
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J79" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K79" s="11"/>
@@ -3598,11 +3714,11 @@
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J80" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K80" s="11"/>
@@ -3620,11 +3736,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J81" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -3642,11 +3758,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J82" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -3664,11 +3780,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J83" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -3686,11 +3802,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J84" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -3708,11 +3824,11 @@
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
       <c r="I85" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J85" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K85" s="11"/>
@@ -3730,11 +3846,11 @@
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J86" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K86" s="11"/>
@@ -3752,11 +3868,11 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
       <c r="I87" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J87" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K87" s="11"/>
@@ -3774,11 +3890,11 @@
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
       <c r="I88" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J88" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K88" s="11"/>
@@ -3796,11 +3912,11 @@
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
       <c r="I89" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J89" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K89" s="11"/>
@@ -3818,11 +3934,11 @@
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
       <c r="I90" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J90" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K90" s="11"/>
@@ -3840,11 +3956,11 @@
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
       <c r="I91" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J91" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K91" s="11"/>
@@ -3862,11 +3978,11 @@
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
       <c r="I92" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J92" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K92" s="11"/>
@@ -3884,11 +4000,11 @@
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
       <c r="I93" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J93" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K93" s="11"/>
@@ -3906,11 +4022,11 @@
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
       <c r="I94" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J94" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K94" s="11"/>
@@ -3928,11 +4044,11 @@
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
       <c r="I95" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J95" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K95" s="11"/>
@@ -3950,11 +4066,11 @@
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
       <c r="I96" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J96" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K96" s="11"/>
@@ -3972,11 +4088,11 @@
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J97" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K97" s="11"/>
@@ -3994,11 +4110,11 @@
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
       <c r="I98" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J98" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K98" s="11"/>
@@ -4016,11 +4132,11 @@
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
       <c r="I99" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J99" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K99" s="11"/>
@@ -4038,11 +4154,11 @@
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
       <c r="I100" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J100" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K100" s="11"/>
@@ -4060,11 +4176,11 @@
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
       <c r="I101" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J101" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K101" s="11"/>
@@ -4082,11 +4198,11 @@
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
       <c r="I102" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J102" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K102" s="11"/>
@@ -4104,11 +4220,11 @@
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J103" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K103" s="11"/>
@@ -4126,11 +4242,11 @@
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
       <c r="I104" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J104" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K104" s="11"/>
@@ -4148,11 +4264,11 @@
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
       <c r="I105" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J105" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K105" s="11"/>
@@ -4170,11 +4286,11 @@
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
       <c r="I106" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J106" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K106" s="11"/>
@@ -4192,11 +4308,11 @@
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J107" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K107" s="11"/>
@@ -4214,11 +4330,11 @@
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
       <c r="I108" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J108" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K108" s="11"/>
@@ -4236,11 +4352,11 @@
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J109" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K109" s="11"/>
@@ -4258,11 +4374,11 @@
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J110" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K110" s="11"/>
@@ -4280,11 +4396,11 @@
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J111" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K111" s="11"/>
@@ -4302,11 +4418,11 @@
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J112" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K112" s="11"/>
@@ -4324,11 +4440,11 @@
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J113" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K113" s="11"/>
@@ -4346,11 +4462,11 @@
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
       <c r="I114" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J114" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K114" s="11"/>
@@ -4368,11 +4484,11 @@
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
       <c r="I115" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J115" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K115" s="11"/>
@@ -4390,11 +4506,11 @@
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
       <c r="I116" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J116" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K116" s="11"/>
@@ -4412,11 +4528,11 @@
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
       <c r="I117" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J117" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K117" s="11"/>
@@ -4434,11 +4550,11 @@
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J118" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K118" s="11"/>
@@ -4456,11 +4572,11 @@
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
       <c r="I119" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J119" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K119" s="11"/>
@@ -4478,11 +4594,11 @@
       <c r="G120" s="9"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J120" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K120" s="11"/>
@@ -4500,11 +4616,11 @@
       <c r="G121" s="9"/>
       <c r="H121" s="9"/>
       <c r="I121" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J121" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K121" s="11"/>
@@ -4522,11 +4638,11 @@
       <c r="G122" s="9"/>
       <c r="H122" s="9"/>
       <c r="I122" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J122" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K122" s="11"/>
@@ -4544,11 +4660,11 @@
       <c r="G123" s="9"/>
       <c r="H123" s="9"/>
       <c r="I123" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J123" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K123" s="11"/>
@@ -4566,11 +4682,11 @@
       <c r="G124" s="9"/>
       <c r="H124" s="9"/>
       <c r="I124" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J124" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K124" s="11"/>
@@ -4588,11 +4704,11 @@
       <c r="G125" s="9"/>
       <c r="H125" s="9"/>
       <c r="I125" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J125" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K125" s="11"/>
@@ -4610,11 +4726,11 @@
       <c r="G126" s="9"/>
       <c r="H126" s="9"/>
       <c r="I126" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J126" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K126" s="11"/>
@@ -4632,11 +4748,11 @@
       <c r="G127" s="9"/>
       <c r="H127" s="9"/>
       <c r="I127" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J127" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K127" s="11"/>
@@ -4654,11 +4770,11 @@
       <c r="G128" s="9"/>
       <c r="H128" s="9"/>
       <c r="I128" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J128" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K128" s="11"/>
@@ -4676,11 +4792,11 @@
       <c r="G129" s="9"/>
       <c r="H129" s="9"/>
       <c r="I129" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J129" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K129" s="11"/>
@@ -4698,11 +4814,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -4720,11 +4836,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -4742,11 +4858,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -4764,11 +4880,11 @@
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
       <c r="I133" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J133" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K133" s="11"/>
@@ -4786,11 +4902,11 @@
       <c r="G134" s="9"/>
       <c r="H134" s="9"/>
       <c r="I134" s="10" t="str">
-        <f t="shared" ref="I134:I197" si="61">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="62">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="10" t="str">
-        <f t="shared" ref="J134:J197" si="62">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="63">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="11"/>
@@ -4808,11 +4924,11 @@
       <c r="G135" s="9"/>
       <c r="H135" s="9"/>
       <c r="I135" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J135" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K135" s="11"/>
@@ -4830,11 +4946,11 @@
       <c r="G136" s="9"/>
       <c r="H136" s="9"/>
       <c r="I136" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J136" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K136" s="11"/>
@@ -4852,11 +4968,11 @@
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
       <c r="I137" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J137" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K137" s="11"/>
@@ -4874,11 +4990,11 @@
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J138" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K138" s="11"/>
@@ -4896,11 +5012,11 @@
       <c r="G139" s="9"/>
       <c r="H139" s="9"/>
       <c r="I139" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J139" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K139" s="11"/>
@@ -4918,11 +5034,11 @@
       <c r="G140" s="9"/>
       <c r="H140" s="9"/>
       <c r="I140" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J140" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K140" s="11"/>
@@ -4940,11 +5056,11 @@
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
       <c r="I141" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J141" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K141" s="11"/>
@@ -4962,11 +5078,11 @@
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J142" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K142" s="11"/>
@@ -4984,11 +5100,11 @@
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
       <c r="I143" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J143" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K143" s="11"/>
@@ -5006,11 +5122,11 @@
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
       <c r="I144" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J144" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K144" s="11"/>
@@ -5028,11 +5144,11 @@
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J145" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K145" s="11"/>
@@ -5050,11 +5166,11 @@
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J146" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K146" s="11"/>
@@ -5072,11 +5188,11 @@
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
       <c r="I147" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J147" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K147" s="11"/>
@@ -5094,11 +5210,11 @@
       <c r="G148" s="9"/>
       <c r="H148" s="9"/>
       <c r="I148" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J148" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K148" s="11"/>
@@ -5116,11 +5232,11 @@
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
       <c r="I149" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J149" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K149" s="11"/>
@@ -5138,11 +5254,11 @@
       <c r="G150" s="9"/>
       <c r="H150" s="9"/>
       <c r="I150" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J150" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K150" s="11"/>
@@ -5160,11 +5276,11 @@
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
       <c r="I151" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J151" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K151" s="11"/>
@@ -5182,11 +5298,11 @@
       <c r="G152" s="9"/>
       <c r="H152" s="9"/>
       <c r="I152" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J152" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K152" s="11"/>
@@ -5204,11 +5320,11 @@
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
       <c r="I153" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J153" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K153" s="11"/>
@@ -5226,11 +5342,11 @@
       <c r="G154" s="9"/>
       <c r="H154" s="9"/>
       <c r="I154" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J154" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K154" s="11"/>
@@ -5248,11 +5364,11 @@
       <c r="G155" s="9"/>
       <c r="H155" s="9"/>
       <c r="I155" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J155" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K155" s="11"/>
@@ -5270,11 +5386,11 @@
       <c r="G156" s="9"/>
       <c r="H156" s="9"/>
       <c r="I156" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J156" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K156" s="11"/>
@@ -5292,11 +5408,11 @@
       <c r="G157" s="9"/>
       <c r="H157" s="9"/>
       <c r="I157" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J157" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K157" s="11"/>
@@ -5314,11 +5430,11 @@
       <c r="G158" s="9"/>
       <c r="H158" s="9"/>
       <c r="I158" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J158" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K158" s="11"/>
@@ -5336,11 +5452,11 @@
       <c r="G159" s="9"/>
       <c r="H159" s="9"/>
       <c r="I159" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J159" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K159" s="11"/>
@@ -5358,11 +5474,11 @@
       <c r="G160" s="9"/>
       <c r="H160" s="9"/>
       <c r="I160" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J160" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K160" s="11"/>
@@ -5380,11 +5496,11 @@
       <c r="G161" s="9"/>
       <c r="H161" s="9"/>
       <c r="I161" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J161" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K161" s="11"/>
@@ -5402,11 +5518,11 @@
       <c r="G162" s="9"/>
       <c r="H162" s="9"/>
       <c r="I162" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J162" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K162" s="11"/>
@@ -5424,11 +5540,11 @@
       <c r="G163" s="9"/>
       <c r="H163" s="9"/>
       <c r="I163" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J163" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K163" s="11"/>
@@ -5446,11 +5562,11 @@
       <c r="G164" s="9"/>
       <c r="H164" s="9"/>
       <c r="I164" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J164" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K164" s="11"/>
@@ -5468,11 +5584,11 @@
       <c r="G165" s="9"/>
       <c r="H165" s="9"/>
       <c r="I165" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J165" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K165" s="11"/>
@@ -5490,11 +5606,11 @@
       <c r="G166" s="9"/>
       <c r="H166" s="9"/>
       <c r="I166" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J166" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K166" s="11"/>
@@ -5512,11 +5628,11 @@
       <c r="G167" s="9"/>
       <c r="H167" s="9"/>
       <c r="I167" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J167" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K167" s="11"/>
@@ -5534,11 +5650,11 @@
       <c r="G168" s="9"/>
       <c r="H168" s="9"/>
       <c r="I168" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J168" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K168" s="11"/>
@@ -5556,11 +5672,11 @@
       <c r="G169" s="9"/>
       <c r="H169" s="9"/>
       <c r="I169" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J169" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K169" s="11"/>
@@ -5578,11 +5694,11 @@
       <c r="G170" s="9"/>
       <c r="H170" s="9"/>
       <c r="I170" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J170" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K170" s="11"/>
@@ -5600,11 +5716,11 @@
       <c r="G171" s="9"/>
       <c r="H171" s="9"/>
       <c r="I171" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J171" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K171" s="11"/>
@@ -5622,11 +5738,11 @@
       <c r="G172" s="9"/>
       <c r="H172" s="9"/>
       <c r="I172" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J172" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K172" s="11"/>
@@ -5644,11 +5760,11 @@
       <c r="G173" s="9"/>
       <c r="H173" s="9"/>
       <c r="I173" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J173" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K173" s="11"/>
@@ -5666,11 +5782,11 @@
       <c r="G174" s="9"/>
       <c r="H174" s="9"/>
       <c r="I174" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J174" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K174" s="11"/>
@@ -5688,11 +5804,11 @@
       <c r="G175" s="9"/>
       <c r="H175" s="9"/>
       <c r="I175" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J175" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K175" s="11"/>
@@ -5710,11 +5826,11 @@
       <c r="G176" s="9"/>
       <c r="H176" s="9"/>
       <c r="I176" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J176" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K176" s="11"/>
@@ -5732,11 +5848,11 @@
       <c r="G177" s="9"/>
       <c r="H177" s="9"/>
       <c r="I177" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J177" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K177" s="11"/>
@@ -5754,11 +5870,11 @@
       <c r="G178" s="9"/>
       <c r="H178" s="9"/>
       <c r="I178" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J178" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K178" s="11"/>
@@ -5776,11 +5892,11 @@
       <c r="G179" s="9"/>
       <c r="H179" s="9"/>
       <c r="I179" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J179" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K179" s="11"/>
@@ -5798,11 +5914,11 @@
       <c r="G180" s="9"/>
       <c r="H180" s="9"/>
       <c r="I180" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J180" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K180" s="11"/>
@@ -5820,11 +5936,11 @@
       <c r="G181" s="9"/>
       <c r="H181" s="9"/>
       <c r="I181" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J181" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K181" s="11"/>
@@ -5842,11 +5958,11 @@
       <c r="G182" s="9"/>
       <c r="H182" s="9"/>
       <c r="I182" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J182" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K182" s="11"/>
@@ -5864,11 +5980,11 @@
       <c r="G183" s="9"/>
       <c r="H183" s="9"/>
       <c r="I183" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J183" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K183" s="11"/>
@@ -5886,11 +6002,11 @@
       <c r="G184" s="9"/>
       <c r="H184" s="9"/>
       <c r="I184" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J184" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K184" s="11"/>
@@ -5908,11 +6024,11 @@
       <c r="G185" s="9"/>
       <c r="H185" s="9"/>
       <c r="I185" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J185" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K185" s="11"/>
@@ -5930,11 +6046,11 @@
       <c r="G186" s="9"/>
       <c r="H186" s="9"/>
       <c r="I186" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J186" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K186" s="11"/>
@@ -5952,11 +6068,11 @@
       <c r="G187" s="9"/>
       <c r="H187" s="9"/>
       <c r="I187" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J187" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K187" s="11"/>
@@ -5974,11 +6090,11 @@
       <c r="G188" s="9"/>
       <c r="H188" s="9"/>
       <c r="I188" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J188" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K188" s="11"/>
@@ -5996,11 +6112,11 @@
       <c r="G189" s="9"/>
       <c r="H189" s="9"/>
       <c r="I189" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J189" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K189" s="11"/>
@@ -6018,11 +6134,11 @@
       <c r="G190" s="9"/>
       <c r="H190" s="9"/>
       <c r="I190" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J190" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K190" s="11"/>
@@ -6040,11 +6156,11 @@
       <c r="G191" s="9"/>
       <c r="H191" s="9"/>
       <c r="I191" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J191" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K191" s="11"/>
@@ -6062,11 +6178,11 @@
       <c r="G192" s="9"/>
       <c r="H192" s="9"/>
       <c r="I192" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J192" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K192" s="11"/>
@@ -6084,11 +6200,11 @@
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J193" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K193" s="11"/>
@@ -6106,11 +6222,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -6128,11 +6244,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -6150,11 +6266,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -6172,11 +6288,11 @@
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J197" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K197" s="11"/>
@@ -6194,11 +6310,11 @@
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
       <c r="I198" s="10" t="str">
-        <f t="shared" ref="I198:I261" si="63">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="64">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="10" t="str">
-        <f t="shared" ref="J198:J261" si="64">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="65">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="11"/>
@@ -6216,11 +6332,11 @@
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
       <c r="I199" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J199" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K199" s="11"/>
@@ -6238,11 +6354,11 @@
       <c r="G200" s="9"/>
       <c r="H200" s="9"/>
       <c r="I200" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J200" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K200" s="11"/>
@@ -6260,11 +6376,11 @@
       <c r="G201" s="9"/>
       <c r="H201" s="9"/>
       <c r="I201" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J201" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K201" s="11"/>
@@ -6282,11 +6398,11 @@
       <c r="G202" s="9"/>
       <c r="H202" s="9"/>
       <c r="I202" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J202" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K202" s="11"/>
@@ -6304,11 +6420,11 @@
       <c r="G203" s="9"/>
       <c r="H203" s="9"/>
       <c r="I203" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J203" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K203" s="11"/>
@@ -6326,11 +6442,11 @@
       <c r="G204" s="9"/>
       <c r="H204" s="9"/>
       <c r="I204" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J204" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K204" s="11"/>
@@ -6348,11 +6464,11 @@
       <c r="G205" s="9"/>
       <c r="H205" s="9"/>
       <c r="I205" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J205" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K205" s="11"/>
@@ -6370,11 +6486,11 @@
       <c r="G206" s="9"/>
       <c r="H206" s="9"/>
       <c r="I206" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J206" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K206" s="11"/>
@@ -6392,11 +6508,11 @@
       <c r="G207" s="9"/>
       <c r="H207" s="9"/>
       <c r="I207" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J207" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K207" s="11"/>
@@ -6414,11 +6530,11 @@
       <c r="G208" s="9"/>
       <c r="H208" s="9"/>
       <c r="I208" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J208" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K208" s="11"/>
@@ -6436,11 +6552,11 @@
       <c r="G209" s="9"/>
       <c r="H209" s="9"/>
       <c r="I209" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J209" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K209" s="11"/>
@@ -6458,11 +6574,11 @@
       <c r="G210" s="9"/>
       <c r="H210" s="9"/>
       <c r="I210" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J210" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K210" s="11"/>
@@ -6480,11 +6596,11 @@
       <c r="G211" s="9"/>
       <c r="H211" s="9"/>
       <c r="I211" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J211" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K211" s="11"/>
@@ -6502,11 +6618,11 @@
       <c r="G212" s="9"/>
       <c r="H212" s="9"/>
       <c r="I212" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J212" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K212" s="11"/>
@@ -6524,11 +6640,11 @@
       <c r="G213" s="9"/>
       <c r="H213" s="9"/>
       <c r="I213" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J213" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K213" s="11"/>
@@ -6546,11 +6662,11 @@
       <c r="G214" s="9"/>
       <c r="H214" s="9"/>
       <c r="I214" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J214" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K214" s="11"/>
@@ -6568,11 +6684,11 @@
       <c r="G215" s="9"/>
       <c r="H215" s="9"/>
       <c r="I215" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J215" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K215" s="11"/>
@@ -6590,11 +6706,11 @@
       <c r="G216" s="9"/>
       <c r="H216" s="9"/>
       <c r="I216" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J216" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K216" s="11"/>
@@ -6612,11 +6728,11 @@
       <c r="G217" s="9"/>
       <c r="H217" s="9"/>
       <c r="I217" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J217" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K217" s="11"/>
@@ -6634,11 +6750,11 @@
       <c r="G218" s="9"/>
       <c r="H218" s="9"/>
       <c r="I218" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J218" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K218" s="11"/>
@@ -6656,11 +6772,11 @@
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
       <c r="I219" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J219" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K219" s="11"/>
@@ -6678,11 +6794,11 @@
       <c r="G220" s="9"/>
       <c r="H220" s="9"/>
       <c r="I220" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J220" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K220" s="11"/>
@@ -6700,11 +6816,11 @@
       <c r="G221" s="9"/>
       <c r="H221" s="9"/>
       <c r="I221" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J221" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K221" s="11"/>
@@ -6722,11 +6838,11 @@
       <c r="G222" s="9"/>
       <c r="H222" s="9"/>
       <c r="I222" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J222" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K222" s="11"/>
@@ -6744,11 +6860,11 @@
       <c r="G223" s="9"/>
       <c r="H223" s="9"/>
       <c r="I223" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J223" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K223" s="11"/>
@@ -6766,11 +6882,11 @@
       <c r="G224" s="9"/>
       <c r="H224" s="9"/>
       <c r="I224" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J224" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K224" s="11"/>
@@ -6788,11 +6904,11 @@
       <c r="G225" s="9"/>
       <c r="H225" s="9"/>
       <c r="I225" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J225" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K225" s="11"/>
@@ -6810,11 +6926,11 @@
       <c r="G226" s="9"/>
       <c r="H226" s="9"/>
       <c r="I226" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J226" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K226" s="11"/>
@@ -6832,11 +6948,11 @@
       <c r="G227" s="9"/>
       <c r="H227" s="9"/>
       <c r="I227" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J227" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K227" s="11"/>
@@ -6854,11 +6970,11 @@
       <c r="G228" s="9"/>
       <c r="H228" s="9"/>
       <c r="I228" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J228" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K228" s="11"/>
@@ -6876,11 +6992,11 @@
       <c r="G229" s="9"/>
       <c r="H229" s="9"/>
       <c r="I229" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J229" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K229" s="11"/>
@@ -6898,11 +7014,11 @@
       <c r="G230" s="9"/>
       <c r="H230" s="9"/>
       <c r="I230" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J230" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K230" s="11"/>
@@ -6920,11 +7036,11 @@
       <c r="G231" s="9"/>
       <c r="H231" s="9"/>
       <c r="I231" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J231" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K231" s="11"/>
@@ -6942,11 +7058,11 @@
       <c r="G232" s="9"/>
       <c r="H232" s="9"/>
       <c r="I232" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J232" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K232" s="11"/>
@@ -6964,11 +7080,11 @@
       <c r="G233" s="9"/>
       <c r="H233" s="9"/>
       <c r="I233" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J233" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K233" s="11"/>
@@ -6986,11 +7102,11 @@
       <c r="G234" s="9"/>
       <c r="H234" s="9"/>
       <c r="I234" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J234" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K234" s="11"/>
@@ -7008,11 +7124,11 @@
       <c r="G235" s="9"/>
       <c r="H235" s="9"/>
       <c r="I235" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J235" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K235" s="11"/>
@@ -7030,11 +7146,11 @@
       <c r="G236" s="9"/>
       <c r="H236" s="9"/>
       <c r="I236" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J236" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K236" s="11"/>
@@ -7052,11 +7168,11 @@
       <c r="G237" s="9"/>
       <c r="H237" s="9"/>
       <c r="I237" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J237" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K237" s="11"/>
@@ -7074,11 +7190,11 @@
       <c r="G238" s="9"/>
       <c r="H238" s="9"/>
       <c r="I238" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J238" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K238" s="11"/>
@@ -7096,11 +7212,11 @@
       <c r="G239" s="9"/>
       <c r="H239" s="9"/>
       <c r="I239" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J239" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K239" s="11"/>
@@ -7118,11 +7234,11 @@
       <c r="G240" s="9"/>
       <c r="H240" s="9"/>
       <c r="I240" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J240" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K240" s="11"/>
@@ -7140,11 +7256,11 @@
       <c r="G241" s="9"/>
       <c r="H241" s="9"/>
       <c r="I241" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J241" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K241" s="11"/>
@@ -7162,11 +7278,11 @@
       <c r="G242" s="9"/>
       <c r="H242" s="9"/>
       <c r="I242" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J242" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K242" s="11"/>
@@ -7184,11 +7300,11 @@
       <c r="G243" s="9"/>
       <c r="H243" s="9"/>
       <c r="I243" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J243" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K243" s="11"/>
@@ -7206,11 +7322,11 @@
       <c r="G244" s="9"/>
       <c r="H244" s="9"/>
       <c r="I244" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J244" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K244" s="11"/>
@@ -7228,11 +7344,11 @@
       <c r="G245" s="9"/>
       <c r="H245" s="9"/>
       <c r="I245" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J245" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K245" s="11"/>
@@ -7250,11 +7366,11 @@
       <c r="G246" s="9"/>
       <c r="H246" s="9"/>
       <c r="I246" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J246" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K246" s="11"/>
@@ -7272,11 +7388,11 @@
       <c r="G247" s="9"/>
       <c r="H247" s="9"/>
       <c r="I247" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J247" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K247" s="11"/>
@@ -7294,11 +7410,11 @@
       <c r="G248" s="9"/>
       <c r="H248" s="9"/>
       <c r="I248" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J248" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K248" s="11"/>
@@ -7316,11 +7432,11 @@
       <c r="G249" s="9"/>
       <c r="H249" s="9"/>
       <c r="I249" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J249" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K249" s="11"/>
@@ -7338,11 +7454,11 @@
       <c r="G250" s="9"/>
       <c r="H250" s="9"/>
       <c r="I250" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J250" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K250" s="11"/>
@@ -7360,11 +7476,11 @@
       <c r="G251" s="9"/>
       <c r="H251" s="9"/>
       <c r="I251" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J251" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K251" s="11"/>
@@ -7382,11 +7498,11 @@
       <c r="G252" s="9"/>
       <c r="H252" s="9"/>
       <c r="I252" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J252" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K252" s="11"/>
@@ -7404,11 +7520,11 @@
       <c r="G253" s="9"/>
       <c r="H253" s="9"/>
       <c r="I253" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J253" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K253" s="11"/>
@@ -7426,11 +7542,11 @@
       <c r="G254" s="9"/>
       <c r="H254" s="9"/>
       <c r="I254" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J254" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K254" s="11"/>
@@ -7448,11 +7564,11 @@
       <c r="G255" s="9"/>
       <c r="H255" s="9"/>
       <c r="I255" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J255" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K255" s="11"/>
@@ -7470,11 +7586,11 @@
       <c r="G256" s="9"/>
       <c r="H256" s="9"/>
       <c r="I256" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J256" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K256" s="11"/>
@@ -7492,11 +7608,11 @@
       <c r="G257" s="9"/>
       <c r="H257" s="9"/>
       <c r="I257" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J257" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K257" s="11"/>
@@ -7514,11 +7630,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -7536,11 +7652,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -7558,11 +7674,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -7580,11 +7696,11 @@
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
       <c r="I261" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J261" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K261" s="11"/>
@@ -7602,11 +7718,11 @@
       <c r="G262" s="9"/>
       <c r="H262" s="9"/>
       <c r="I262" s="10" t="str">
-        <f t="shared" ref="I262:I325" si="65">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="66">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="10" t="str">
-        <f t="shared" ref="J262:J325" si="66">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="67">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="11"/>
@@ -7624,11 +7740,11 @@
       <c r="G263" s="9"/>
       <c r="H263" s="9"/>
       <c r="I263" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J263" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K263" s="11"/>
@@ -7646,11 +7762,11 @@
       <c r="G264" s="9"/>
       <c r="H264" s="9"/>
       <c r="I264" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J264" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K264" s="11"/>
@@ -7668,11 +7784,11 @@
       <c r="G265" s="9"/>
       <c r="H265" s="9"/>
       <c r="I265" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J265" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K265" s="11"/>
@@ -7690,11 +7806,11 @@
       <c r="G266" s="9"/>
       <c r="H266" s="9"/>
       <c r="I266" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J266" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K266" s="11"/>
@@ -7712,11 +7828,11 @@
       <c r="G267" s="9"/>
       <c r="H267" s="9"/>
       <c r="I267" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J267" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K267" s="11"/>
@@ -7734,11 +7850,11 @@
       <c r="G268" s="9"/>
       <c r="H268" s="9"/>
       <c r="I268" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J268" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K268" s="11"/>
@@ -7756,11 +7872,11 @@
       <c r="G269" s="9"/>
       <c r="H269" s="9"/>
       <c r="I269" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J269" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K269" s="11"/>
@@ -7778,11 +7894,11 @@
       <c r="G270" s="9"/>
       <c r="H270" s="9"/>
       <c r="I270" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J270" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K270" s="11"/>
@@ -7800,11 +7916,11 @@
       <c r="G271" s="9"/>
       <c r="H271" s="9"/>
       <c r="I271" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J271" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K271" s="11"/>
@@ -7822,11 +7938,11 @@
       <c r="G272" s="9"/>
       <c r="H272" s="9"/>
       <c r="I272" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J272" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K272" s="11"/>
@@ -7844,11 +7960,11 @@
       <c r="G273" s="9"/>
       <c r="H273" s="9"/>
       <c r="I273" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J273" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K273" s="11"/>
@@ -7866,11 +7982,11 @@
       <c r="G274" s="9"/>
       <c r="H274" s="9"/>
       <c r="I274" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J274" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K274" s="11"/>
@@ -7888,11 +8004,11 @@
       <c r="G275" s="9"/>
       <c r="H275" s="9"/>
       <c r="I275" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J275" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K275" s="11"/>
@@ -7910,11 +8026,11 @@
       <c r="G276" s="9"/>
       <c r="H276" s="9"/>
       <c r="I276" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J276" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K276" s="11"/>
@@ -7932,11 +8048,11 @@
       <c r="G277" s="9"/>
       <c r="H277" s="9"/>
       <c r="I277" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J277" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K277" s="11"/>
@@ -7954,11 +8070,11 @@
       <c r="G278" s="9"/>
       <c r="H278" s="9"/>
       <c r="I278" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J278" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K278" s="11"/>
@@ -7976,11 +8092,11 @@
       <c r="G279" s="9"/>
       <c r="H279" s="9"/>
       <c r="I279" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J279" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K279" s="11"/>
@@ -7998,11 +8114,11 @@
       <c r="G280" s="9"/>
       <c r="H280" s="9"/>
       <c r="I280" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J280" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K280" s="11"/>
@@ -8020,11 +8136,11 @@
       <c r="G281" s="9"/>
       <c r="H281" s="9"/>
       <c r="I281" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J281" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K281" s="11"/>
@@ -8042,11 +8158,11 @@
       <c r="G282" s="9"/>
       <c r="H282" s="9"/>
       <c r="I282" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J282" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K282" s="11"/>
@@ -8064,11 +8180,11 @@
       <c r="G283" s="9"/>
       <c r="H283" s="9"/>
       <c r="I283" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J283" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K283" s="11"/>
@@ -8086,11 +8202,11 @@
       <c r="G284" s="9"/>
       <c r="H284" s="9"/>
       <c r="I284" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J284" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K284" s="11"/>
@@ -8108,11 +8224,11 @@
       <c r="G285" s="9"/>
       <c r="H285" s="9"/>
       <c r="I285" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J285" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K285" s="11"/>
@@ -8130,11 +8246,11 @@
       <c r="G286" s="9"/>
       <c r="H286" s="9"/>
       <c r="I286" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J286" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K286" s="11"/>
@@ -8152,11 +8268,11 @@
       <c r="G287" s="9"/>
       <c r="H287" s="9"/>
       <c r="I287" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J287" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K287" s="11"/>
@@ -8174,11 +8290,11 @@
       <c r="G288" s="9"/>
       <c r="H288" s="9"/>
       <c r="I288" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J288" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K288" s="11"/>
@@ -8196,11 +8312,11 @@
       <c r="G289" s="9"/>
       <c r="H289" s="9"/>
       <c r="I289" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J289" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K289" s="11"/>
@@ -8218,11 +8334,11 @@
       <c r="G290" s="9"/>
       <c r="H290" s="9"/>
       <c r="I290" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J290" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K290" s="11"/>
@@ -8240,11 +8356,11 @@
       <c r="G291" s="9"/>
       <c r="H291" s="9"/>
       <c r="I291" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J291" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K291" s="11"/>
@@ -8262,11 +8378,11 @@
       <c r="G292" s="9"/>
       <c r="H292" s="9"/>
       <c r="I292" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J292" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K292" s="11"/>
@@ -8284,11 +8400,11 @@
       <c r="G293" s="9"/>
       <c r="H293" s="9"/>
       <c r="I293" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J293" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K293" s="11"/>
@@ -8306,11 +8422,11 @@
       <c r="G294" s="9"/>
       <c r="H294" s="9"/>
       <c r="I294" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J294" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K294" s="11"/>
@@ -8328,11 +8444,11 @@
       <c r="G295" s="9"/>
       <c r="H295" s="9"/>
       <c r="I295" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J295" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K295" s="11"/>
@@ -8350,11 +8466,11 @@
       <c r="G296" s="9"/>
       <c r="H296" s="9"/>
       <c r="I296" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J296" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K296" s="11"/>
@@ -8372,11 +8488,11 @@
       <c r="G297" s="9"/>
       <c r="H297" s="9"/>
       <c r="I297" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J297" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K297" s="11"/>
@@ -8394,11 +8510,11 @@
       <c r="G298" s="9"/>
       <c r="H298" s="9"/>
       <c r="I298" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J298" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K298" s="11"/>
@@ -8416,11 +8532,11 @@
       <c r="G299" s="9"/>
       <c r="H299" s="9"/>
       <c r="I299" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J299" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K299" s="11"/>
@@ -8438,11 +8554,11 @@
       <c r="G300" s="9"/>
       <c r="H300" s="9"/>
       <c r="I300" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J300" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K300" s="11"/>
@@ -8460,11 +8576,11 @@
       <c r="G301" s="9"/>
       <c r="H301" s="9"/>
       <c r="I301" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J301" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K301" s="11"/>
@@ -8482,11 +8598,11 @@
       <c r="G302" s="9"/>
       <c r="H302" s="9"/>
       <c r="I302" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J302" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K302" s="11"/>
@@ -8504,11 +8620,11 @@
       <c r="G303" s="9"/>
       <c r="H303" s="9"/>
       <c r="I303" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J303" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K303" s="11"/>
@@ -8526,11 +8642,11 @@
       <c r="G304" s="9"/>
       <c r="H304" s="9"/>
       <c r="I304" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J304" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K304" s="11"/>
@@ -8548,11 +8664,11 @@
       <c r="G305" s="9"/>
       <c r="H305" s="9"/>
       <c r="I305" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J305" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K305" s="11"/>
@@ -8570,11 +8686,11 @@
       <c r="G306" s="9"/>
       <c r="H306" s="9"/>
       <c r="I306" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J306" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K306" s="11"/>
@@ -8592,11 +8708,11 @@
       <c r="G307" s="9"/>
       <c r="H307" s="9"/>
       <c r="I307" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J307" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K307" s="11"/>
@@ -8614,11 +8730,11 @@
       <c r="G308" s="9"/>
       <c r="H308" s="9"/>
       <c r="I308" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J308" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K308" s="11"/>
@@ -8636,11 +8752,11 @@
       <c r="G309" s="9"/>
       <c r="H309" s="9"/>
       <c r="I309" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J309" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K309" s="11"/>
@@ -8658,11 +8774,11 @@
       <c r="G310" s="9"/>
       <c r="H310" s="9"/>
       <c r="I310" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J310" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K310" s="11"/>
@@ -8680,11 +8796,11 @@
       <c r="G311" s="9"/>
       <c r="H311" s="9"/>
       <c r="I311" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J311" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K311" s="11"/>
@@ -8702,11 +8818,11 @@
       <c r="G312" s="9"/>
       <c r="H312" s="9"/>
       <c r="I312" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J312" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K312" s="11"/>
@@ -8724,11 +8840,11 @@
       <c r="G313" s="9"/>
       <c r="H313" s="9"/>
       <c r="I313" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J313" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K313" s="11"/>
@@ -8746,11 +8862,11 @@
       <c r="G314" s="9"/>
       <c r="H314" s="9"/>
       <c r="I314" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J314" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K314" s="11"/>
@@ -8768,11 +8884,11 @@
       <c r="G315" s="9"/>
       <c r="H315" s="9"/>
       <c r="I315" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J315" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K315" s="11"/>
@@ -8790,11 +8906,11 @@
       <c r="G316" s="9"/>
       <c r="H316" s="9"/>
       <c r="I316" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J316" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K316" s="11"/>
@@ -8812,11 +8928,11 @@
       <c r="G317" s="9"/>
       <c r="H317" s="9"/>
       <c r="I317" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J317" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K317" s="11"/>
@@ -8834,11 +8950,11 @@
       <c r="G318" s="9"/>
       <c r="H318" s="9"/>
       <c r="I318" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J318" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K318" s="11"/>
@@ -8856,11 +8972,11 @@
       <c r="G319" s="9"/>
       <c r="H319" s="9"/>
       <c r="I319" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J319" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K319" s="11"/>
@@ -8878,11 +8994,11 @@
       <c r="G320" s="9"/>
       <c r="H320" s="9"/>
       <c r="I320" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J320" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K320" s="11"/>
@@ -8900,11 +9016,11 @@
       <c r="G321" s="9"/>
       <c r="H321" s="9"/>
       <c r="I321" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J321" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K321" s="11"/>
@@ -8922,11 +9038,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -8944,11 +9060,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -8966,11 +9082,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -8988,11 +9104,11 @@
       <c r="G325" s="9"/>
       <c r="H325" s="9"/>
       <c r="I325" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J325" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K325" s="11"/>
@@ -9010,11 +9126,11 @@
       <c r="G326" s="9"/>
       <c r="H326" s="9"/>
       <c r="I326" s="10" t="str">
-        <f t="shared" ref="I326:I389" si="67">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="68">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="10" t="str">
-        <f t="shared" ref="J326:J389" si="68">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="69">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="11"/>
@@ -9032,11 +9148,11 @@
       <c r="G327" s="9"/>
       <c r="H327" s="9"/>
       <c r="I327" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J327" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K327" s="11"/>
@@ -9054,11 +9170,11 @@
       <c r="G328" s="9"/>
       <c r="H328" s="9"/>
       <c r="I328" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J328" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K328" s="11"/>
@@ -9076,11 +9192,11 @@
       <c r="G329" s="9"/>
       <c r="H329" s="9"/>
       <c r="I329" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J329" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K329" s="11"/>
@@ -9098,11 +9214,11 @@
       <c r="G330" s="9"/>
       <c r="H330" s="9"/>
       <c r="I330" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J330" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K330" s="11"/>
@@ -9120,11 +9236,11 @@
       <c r="G331" s="9"/>
       <c r="H331" s="9"/>
       <c r="I331" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J331" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K331" s="11"/>
@@ -9142,11 +9258,11 @@
       <c r="G332" s="9"/>
       <c r="H332" s="9"/>
       <c r="I332" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J332" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K332" s="11"/>
@@ -9164,11 +9280,11 @@
       <c r="G333" s="9"/>
       <c r="H333" s="9"/>
       <c r="I333" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J333" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K333" s="11"/>
@@ -9186,11 +9302,11 @@
       <c r="G334" s="9"/>
       <c r="H334" s="9"/>
       <c r="I334" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J334" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K334" s="11"/>
@@ -9208,11 +9324,11 @@
       <c r="G335" s="9"/>
       <c r="H335" s="9"/>
       <c r="I335" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J335" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K335" s="11"/>
@@ -9230,11 +9346,11 @@
       <c r="G336" s="9"/>
       <c r="H336" s="9"/>
       <c r="I336" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J336" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K336" s="11"/>
@@ -9252,11 +9368,11 @@
       <c r="G337" s="9"/>
       <c r="H337" s="9"/>
       <c r="I337" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J337" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K337" s="11"/>
@@ -9274,11 +9390,11 @@
       <c r="G338" s="9"/>
       <c r="H338" s="9"/>
       <c r="I338" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J338" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K338" s="11"/>
@@ -9296,11 +9412,11 @@
       <c r="G339" s="9"/>
       <c r="H339" s="9"/>
       <c r="I339" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J339" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K339" s="11"/>
@@ -9318,11 +9434,11 @@
       <c r="G340" s="9"/>
       <c r="H340" s="9"/>
       <c r="I340" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J340" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K340" s="11"/>
@@ -9340,11 +9456,11 @@
       <c r="G341" s="9"/>
       <c r="H341" s="9"/>
       <c r="I341" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J341" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K341" s="11"/>
@@ -9362,11 +9478,11 @@
       <c r="G342" s="9"/>
       <c r="H342" s="9"/>
       <c r="I342" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J342" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K342" s="11"/>
@@ -9384,11 +9500,11 @@
       <c r="G343" s="9"/>
       <c r="H343" s="9"/>
       <c r="I343" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J343" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K343" s="11"/>
@@ -9406,11 +9522,11 @@
       <c r="G344" s="9"/>
       <c r="H344" s="9"/>
       <c r="I344" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J344" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K344" s="11"/>
@@ -9428,11 +9544,11 @@
       <c r="G345" s="9"/>
       <c r="H345" s="9"/>
       <c r="I345" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J345" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K345" s="11"/>
@@ -9450,11 +9566,11 @@
       <c r="G346" s="9"/>
       <c r="H346" s="9"/>
       <c r="I346" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J346" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K346" s="11"/>
@@ -9472,11 +9588,11 @@
       <c r="G347" s="9"/>
       <c r="H347" s="9"/>
       <c r="I347" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J347" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K347" s="11"/>
@@ -9494,11 +9610,11 @@
       <c r="G348" s="9"/>
       <c r="H348" s="9"/>
       <c r="I348" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J348" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K348" s="11"/>
@@ -9516,11 +9632,11 @@
       <c r="G349" s="9"/>
       <c r="H349" s="9"/>
       <c r="I349" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J349" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K349" s="11"/>
@@ -9538,11 +9654,11 @@
       <c r="G350" s="9"/>
       <c r="H350" s="9"/>
       <c r="I350" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J350" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K350" s="11"/>
@@ -9560,11 +9676,11 @@
       <c r="G351" s="9"/>
       <c r="H351" s="9"/>
       <c r="I351" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J351" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K351" s="11"/>
@@ -9582,11 +9698,11 @@
       <c r="G352" s="9"/>
       <c r="H352" s="9"/>
       <c r="I352" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J352" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K352" s="11"/>
@@ -9604,11 +9720,11 @@
       <c r="G353" s="9"/>
       <c r="H353" s="9"/>
       <c r="I353" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J353" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K353" s="11"/>
@@ -9626,11 +9742,11 @@
       <c r="G354" s="9"/>
       <c r="H354" s="9"/>
       <c r="I354" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J354" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K354" s="11"/>
@@ -9648,11 +9764,11 @@
       <c r="G355" s="9"/>
       <c r="H355" s="9"/>
       <c r="I355" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J355" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K355" s="11"/>
@@ -9670,11 +9786,11 @@
       <c r="G356" s="9"/>
       <c r="H356" s="9"/>
       <c r="I356" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J356" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K356" s="11"/>
@@ -9692,11 +9808,11 @@
       <c r="G357" s="9"/>
       <c r="H357" s="9"/>
       <c r="I357" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J357" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K357" s="11"/>
@@ -9714,11 +9830,11 @@
       <c r="G358" s="9"/>
       <c r="H358" s="9"/>
       <c r="I358" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J358" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K358" s="11"/>
@@ -9736,11 +9852,11 @@
       <c r="G359" s="9"/>
       <c r="H359" s="9"/>
       <c r="I359" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J359" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K359" s="11"/>
@@ -9758,11 +9874,11 @@
       <c r="G360" s="9"/>
       <c r="H360" s="9"/>
       <c r="I360" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J360" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K360" s="11"/>
@@ -9780,11 +9896,11 @@
       <c r="G361" s="9"/>
       <c r="H361" s="9"/>
       <c r="I361" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J361" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K361" s="11"/>
@@ -9802,11 +9918,11 @@
       <c r="G362" s="9"/>
       <c r="H362" s="9"/>
       <c r="I362" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J362" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K362" s="11"/>
@@ -9824,11 +9940,11 @@
       <c r="G363" s="9"/>
       <c r="H363" s="9"/>
       <c r="I363" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J363" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K363" s="11"/>
@@ -9846,11 +9962,11 @@
       <c r="G364" s="9"/>
       <c r="H364" s="9"/>
       <c r="I364" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J364" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K364" s="11"/>
@@ -9868,11 +9984,11 @@
       <c r="G365" s="9"/>
       <c r="H365" s="9"/>
       <c r="I365" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J365" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K365" s="11"/>
@@ -9890,11 +10006,11 @@
       <c r="G366" s="9"/>
       <c r="H366" s="9"/>
       <c r="I366" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J366" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K366" s="11"/>
@@ -9912,11 +10028,11 @@
       <c r="G367" s="9"/>
       <c r="H367" s="9"/>
       <c r="I367" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J367" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K367" s="11"/>
@@ -9934,11 +10050,11 @@
       <c r="G368" s="9"/>
       <c r="H368" s="9"/>
       <c r="I368" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J368" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K368" s="11"/>
@@ -9956,11 +10072,11 @@
       <c r="G369" s="9"/>
       <c r="H369" s="9"/>
       <c r="I369" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J369" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K369" s="11"/>
@@ -9978,11 +10094,11 @@
       <c r="G370" s="9"/>
       <c r="H370" s="9"/>
       <c r="I370" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J370" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K370" s="11"/>
@@ -10000,11 +10116,11 @@
       <c r="G371" s="9"/>
       <c r="H371" s="9"/>
       <c r="I371" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J371" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K371" s="11"/>
@@ -10022,11 +10138,11 @@
       <c r="G372" s="9"/>
       <c r="H372" s="9"/>
       <c r="I372" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J372" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K372" s="11"/>
@@ -10044,11 +10160,11 @@
       <c r="G373" s="9"/>
       <c r="H373" s="9"/>
       <c r="I373" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J373" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K373" s="11"/>
@@ -10066,11 +10182,11 @@
       <c r="G374" s="9"/>
       <c r="H374" s="9"/>
       <c r="I374" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J374" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K374" s="11"/>
@@ -10088,11 +10204,11 @@
       <c r="G375" s="9"/>
       <c r="H375" s="9"/>
       <c r="I375" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J375" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K375" s="11"/>
@@ -10110,11 +10226,11 @@
       <c r="G376" s="9"/>
       <c r="H376" s="9"/>
       <c r="I376" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J376" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K376" s="11"/>
@@ -10132,11 +10248,11 @@
       <c r="G377" s="9"/>
       <c r="H377" s="9"/>
       <c r="I377" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J377" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K377" s="11"/>
@@ -10154,11 +10270,11 @@
       <c r="G378" s="9"/>
       <c r="H378" s="9"/>
       <c r="I378" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J378" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K378" s="11"/>
@@ -10176,11 +10292,11 @@
       <c r="G379" s="9"/>
       <c r="H379" s="9"/>
       <c r="I379" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J379" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K379" s="11"/>
@@ -10198,11 +10314,11 @@
       <c r="G380" s="9"/>
       <c r="H380" s="9"/>
       <c r="I380" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J380" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K380" s="11"/>
@@ -10220,11 +10336,11 @@
       <c r="G381" s="9"/>
       <c r="H381" s="9"/>
       <c r="I381" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J381" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K381" s="11"/>
@@ -10242,11 +10358,11 @@
       <c r="G382" s="9"/>
       <c r="H382" s="9"/>
       <c r="I382" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J382" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K382" s="11"/>
@@ -10264,11 +10380,11 @@
       <c r="G383" s="9"/>
       <c r="H383" s="9"/>
       <c r="I383" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J383" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K383" s="11"/>
@@ -10286,11 +10402,11 @@
       <c r="G384" s="9"/>
       <c r="H384" s="9"/>
       <c r="I384" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J384" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K384" s="11"/>
@@ -10308,11 +10424,11 @@
       <c r="G385" s="9"/>
       <c r="H385" s="9"/>
       <c r="I385" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J385" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K385" s="11"/>
@@ -10330,11 +10446,11 @@
       <c r="G386" s="9"/>
       <c r="H386" s="9"/>
       <c r="I386" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J386" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K386" s="11"/>
@@ -10352,11 +10468,11 @@
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J387" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K387" s="11"/>
@@ -10374,11 +10490,11 @@
       <c r="G388" s="9"/>
       <c r="H388" s="9"/>
       <c r="I388" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J388" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K388" s="11"/>
@@ -10396,11 +10512,11 @@
       <c r="G389" s="9"/>
       <c r="H389" s="9"/>
       <c r="I389" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J389" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K389" s="11"/>
@@ -10418,11 +10534,11 @@
       <c r="G390" s="9"/>
       <c r="H390" s="9"/>
       <c r="I390" s="10" t="str">
-        <f t="shared" ref="I390:I401" si="69">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="70">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="10" t="str">
-        <f t="shared" ref="J390:J401" si="70">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="71">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="11"/>
@@ -10440,11 +10556,11 @@
       <c r="G391" s="9"/>
       <c r="H391" s="9"/>
       <c r="I391" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J391" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K391" s="11"/>
@@ -10462,11 +10578,11 @@
       <c r="G392" s="9"/>
       <c r="H392" s="9"/>
       <c r="I392" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J392" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K392" s="11"/>
@@ -10484,11 +10600,11 @@
       <c r="G393" s="9"/>
       <c r="H393" s="9"/>
       <c r="I393" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J393" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K393" s="11"/>
@@ -10506,11 +10622,11 @@
       <c r="G394" s="9"/>
       <c r="H394" s="9"/>
       <c r="I394" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J394" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K394" s="11"/>
@@ -10528,11 +10644,11 @@
       <c r="G395" s="9"/>
       <c r="H395" s="9"/>
       <c r="I395" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J395" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K395" s="11"/>
@@ -10550,11 +10666,11 @@
       <c r="G396" s="9"/>
       <c r="H396" s="9"/>
       <c r="I396" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J396" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K396" s="11"/>
@@ -10572,11 +10688,11 @@
       <c r="G397" s="9"/>
       <c r="H397" s="9"/>
       <c r="I397" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J397" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K397" s="11"/>
@@ -10594,11 +10710,11 @@
       <c r="G398" s="9"/>
       <c r="H398" s="9"/>
       <c r="I398" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J398" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K398" s="11"/>
@@ -10616,11 +10732,11 @@
       <c r="G399" s="9"/>
       <c r="H399" s="9"/>
       <c r="I399" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J399" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K399" s="11"/>
@@ -10638,11 +10754,11 @@
       <c r="G400" s="9"/>
       <c r="H400" s="9"/>
       <c r="I400" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J400" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K400" s="11"/>
@@ -10660,11 +10776,11 @@
       <c r="G401" s="9"/>
       <c r="H401" s="9"/>
       <c r="I401" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J401" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K401" s="11"/>

--- a/12626731.xlsx
+++ b/12626731.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHIVEN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73D2D594-B144-489F-8B22-84AD3954E8CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED23621A-C2E5-40CA-93FA-EA2621AA1B8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3022,26 +3022,48 @@
       </c>
       <c r="N48" s="17"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="8"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9"/>
-      <c r="H49" s="9"/>
-      <c r="I49" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="11"/>
-      <c r="L49" s="11"/>
-      <c r="M49" s="11"/>
+    <row r="49" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B49" s="14">
+        <v>400</v>
+      </c>
+      <c r="C49" s="14">
+        <v>0</v>
+      </c>
+      <c r="D49" s="14">
+        <v>180</v>
+      </c>
+      <c r="E49" s="14">
+        <v>50</v>
+      </c>
+      <c r="F49" s="14">
+        <v>350</v>
+      </c>
+      <c r="G49" s="14">
+        <v>7</v>
+      </c>
+      <c r="H49" s="14">
+        <v>270</v>
+      </c>
+      <c r="I49" s="15">
+        <f t="shared" ref="I49" si="60">IF(SUM(B49:F49,H49)=0,"",SUM(B49:F49,H49))</f>
+        <v>1250</v>
+      </c>
+      <c r="J49" s="15">
+        <f t="shared" ref="J49" si="61">IF(I49="","",1440-I49)</f>
+        <v>190</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N49" s="12"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
@@ -3494,11 +3516,11 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
       <c r="I70" s="10" t="str">
-        <f t="shared" ref="I70:I133" si="60">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="62">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="10" t="str">
-        <f t="shared" ref="J70:J133" si="61">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="63">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="11"/>
@@ -3516,11 +3538,11 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
       <c r="I71" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J71" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K71" s="11"/>
@@ -3538,11 +3560,11 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
       <c r="I72" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J72" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K72" s="11"/>
@@ -3560,11 +3582,11 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
       <c r="I73" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J73" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K73" s="11"/>
@@ -3582,11 +3604,11 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
       <c r="I74" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J74" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K74" s="11"/>
@@ -3604,11 +3626,11 @@
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="I75" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J75" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K75" s="11"/>
@@ -3626,11 +3648,11 @@
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="I76" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J76" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K76" s="11"/>
@@ -3648,11 +3670,11 @@
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J77" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K77" s="11"/>
@@ -3670,11 +3692,11 @@
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J78" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K78" s="11"/>
@@ -3692,11 +3714,11 @@
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J79" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K79" s="11"/>
@@ -3714,11 +3736,11 @@
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J80" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K80" s="11"/>
@@ -3736,11 +3758,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J81" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -3758,11 +3780,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J82" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -3780,11 +3802,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J83" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -3802,11 +3824,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J84" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -3824,11 +3846,11 @@
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
       <c r="I85" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J85" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K85" s="11"/>
@@ -3846,11 +3868,11 @@
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J86" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K86" s="11"/>
@@ -3868,11 +3890,11 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
       <c r="I87" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J87" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K87" s="11"/>
@@ -3890,11 +3912,11 @@
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
       <c r="I88" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J88" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K88" s="11"/>
@@ -3912,11 +3934,11 @@
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
       <c r="I89" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J89" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K89" s="11"/>
@@ -3934,11 +3956,11 @@
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
       <c r="I90" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J90" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K90" s="11"/>
@@ -3956,11 +3978,11 @@
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
       <c r="I91" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J91" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K91" s="11"/>
@@ -3978,11 +4000,11 @@
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
       <c r="I92" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J92" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K92" s="11"/>
@@ -4000,11 +4022,11 @@
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
       <c r="I93" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J93" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K93" s="11"/>
@@ -4022,11 +4044,11 @@
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
       <c r="I94" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J94" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K94" s="11"/>
@@ -4044,11 +4066,11 @@
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
       <c r="I95" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J95" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K95" s="11"/>
@@ -4066,11 +4088,11 @@
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
       <c r="I96" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J96" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K96" s="11"/>
@@ -4088,11 +4110,11 @@
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J97" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K97" s="11"/>
@@ -4110,11 +4132,11 @@
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
       <c r="I98" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J98" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K98" s="11"/>
@@ -4132,11 +4154,11 @@
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
       <c r="I99" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J99" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K99" s="11"/>
@@ -4154,11 +4176,11 @@
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
       <c r="I100" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J100" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K100" s="11"/>
@@ -4176,11 +4198,11 @@
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
       <c r="I101" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J101" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K101" s="11"/>
@@ -4198,11 +4220,11 @@
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
       <c r="I102" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J102" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K102" s="11"/>
@@ -4220,11 +4242,11 @@
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J103" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K103" s="11"/>
@@ -4242,11 +4264,11 @@
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
       <c r="I104" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J104" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K104" s="11"/>
@@ -4264,11 +4286,11 @@
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
       <c r="I105" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J105" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K105" s="11"/>
@@ -4286,11 +4308,11 @@
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
       <c r="I106" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J106" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K106" s="11"/>
@@ -4308,11 +4330,11 @@
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J107" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K107" s="11"/>
@@ -4330,11 +4352,11 @@
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
       <c r="I108" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J108" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K108" s="11"/>
@@ -4352,11 +4374,11 @@
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J109" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K109" s="11"/>
@@ -4374,11 +4396,11 @@
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J110" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K110" s="11"/>
@@ -4396,11 +4418,11 @@
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J111" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K111" s="11"/>
@@ -4418,11 +4440,11 @@
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J112" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K112" s="11"/>
@@ -4440,11 +4462,11 @@
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J113" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K113" s="11"/>
@@ -4462,11 +4484,11 @@
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
       <c r="I114" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J114" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K114" s="11"/>
@@ -4484,11 +4506,11 @@
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
       <c r="I115" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J115" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K115" s="11"/>
@@ -4506,11 +4528,11 @@
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
       <c r="I116" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J116" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K116" s="11"/>
@@ -4528,11 +4550,11 @@
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
       <c r="I117" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J117" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K117" s="11"/>
@@ -4550,11 +4572,11 @@
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J118" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K118" s="11"/>
@@ -4572,11 +4594,11 @@
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
       <c r="I119" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J119" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K119" s="11"/>
@@ -4594,11 +4616,11 @@
       <c r="G120" s="9"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J120" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K120" s="11"/>
@@ -4616,11 +4638,11 @@
       <c r="G121" s="9"/>
       <c r="H121" s="9"/>
       <c r="I121" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J121" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K121" s="11"/>
@@ -4638,11 +4660,11 @@
       <c r="G122" s="9"/>
       <c r="H122" s="9"/>
       <c r="I122" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J122" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K122" s="11"/>
@@ -4660,11 +4682,11 @@
       <c r="G123" s="9"/>
       <c r="H123" s="9"/>
       <c r="I123" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J123" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K123" s="11"/>
@@ -4682,11 +4704,11 @@
       <c r="G124" s="9"/>
       <c r="H124" s="9"/>
       <c r="I124" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J124" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K124" s="11"/>
@@ -4704,11 +4726,11 @@
       <c r="G125" s="9"/>
       <c r="H125" s="9"/>
       <c r="I125" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J125" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K125" s="11"/>
@@ -4726,11 +4748,11 @@
       <c r="G126" s="9"/>
       <c r="H126" s="9"/>
       <c r="I126" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J126" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K126" s="11"/>
@@ -4748,11 +4770,11 @@
       <c r="G127" s="9"/>
       <c r="H127" s="9"/>
       <c r="I127" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J127" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K127" s="11"/>
@@ -4770,11 +4792,11 @@
       <c r="G128" s="9"/>
       <c r="H128" s="9"/>
       <c r="I128" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J128" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K128" s="11"/>
@@ -4792,11 +4814,11 @@
       <c r="G129" s="9"/>
       <c r="H129" s="9"/>
       <c r="I129" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J129" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K129" s="11"/>
@@ -4814,11 +4836,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -4836,11 +4858,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -4858,11 +4880,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -4880,11 +4902,11 @@
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
       <c r="I133" s="10" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="J133" s="10" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="K133" s="11"/>
@@ -4902,11 +4924,11 @@
       <c r="G134" s="9"/>
       <c r="H134" s="9"/>
       <c r="I134" s="10" t="str">
-        <f t="shared" ref="I134:I197" si="62">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="64">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="10" t="str">
-        <f t="shared" ref="J134:J197" si="63">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="65">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="11"/>
@@ -4924,11 +4946,11 @@
       <c r="G135" s="9"/>
       <c r="H135" s="9"/>
       <c r="I135" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J135" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K135" s="11"/>
@@ -4946,11 +4968,11 @@
       <c r="G136" s="9"/>
       <c r="H136" s="9"/>
       <c r="I136" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J136" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K136" s="11"/>
@@ -4968,11 +4990,11 @@
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
       <c r="I137" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J137" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K137" s="11"/>
@@ -4990,11 +5012,11 @@
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J138" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K138" s="11"/>
@@ -5012,11 +5034,11 @@
       <c r="G139" s="9"/>
       <c r="H139" s="9"/>
       <c r="I139" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J139" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K139" s="11"/>
@@ -5034,11 +5056,11 @@
       <c r="G140" s="9"/>
       <c r="H140" s="9"/>
       <c r="I140" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J140" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K140" s="11"/>
@@ -5056,11 +5078,11 @@
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
       <c r="I141" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J141" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K141" s="11"/>
@@ -5078,11 +5100,11 @@
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J142" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K142" s="11"/>
@@ -5100,11 +5122,11 @@
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
       <c r="I143" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J143" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K143" s="11"/>
@@ -5122,11 +5144,11 @@
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
       <c r="I144" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J144" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K144" s="11"/>
@@ -5144,11 +5166,11 @@
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J145" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K145" s="11"/>
@@ -5166,11 +5188,11 @@
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J146" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K146" s="11"/>
@@ -5188,11 +5210,11 @@
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
       <c r="I147" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J147" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K147" s="11"/>
@@ -5210,11 +5232,11 @@
       <c r="G148" s="9"/>
       <c r="H148" s="9"/>
       <c r="I148" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J148" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K148" s="11"/>
@@ -5232,11 +5254,11 @@
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
       <c r="I149" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J149" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K149" s="11"/>
@@ -5254,11 +5276,11 @@
       <c r="G150" s="9"/>
       <c r="H150" s="9"/>
       <c r="I150" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J150" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K150" s="11"/>
@@ -5276,11 +5298,11 @@
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
       <c r="I151" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J151" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K151" s="11"/>
@@ -5298,11 +5320,11 @@
       <c r="G152" s="9"/>
       <c r="H152" s="9"/>
       <c r="I152" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J152" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K152" s="11"/>
@@ -5320,11 +5342,11 @@
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
       <c r="I153" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J153" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K153" s="11"/>
@@ -5342,11 +5364,11 @@
       <c r="G154" s="9"/>
       <c r="H154" s="9"/>
       <c r="I154" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J154" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K154" s="11"/>
@@ -5364,11 +5386,11 @@
       <c r="G155" s="9"/>
       <c r="H155" s="9"/>
       <c r="I155" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J155" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K155" s="11"/>
@@ -5386,11 +5408,11 @@
       <c r="G156" s="9"/>
       <c r="H156" s="9"/>
       <c r="I156" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J156" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K156" s="11"/>
@@ -5408,11 +5430,11 @@
       <c r="G157" s="9"/>
       <c r="H157" s="9"/>
       <c r="I157" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J157" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K157" s="11"/>
@@ -5430,11 +5452,11 @@
       <c r="G158" s="9"/>
       <c r="H158" s="9"/>
       <c r="I158" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J158" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K158" s="11"/>
@@ -5452,11 +5474,11 @@
       <c r="G159" s="9"/>
       <c r="H159" s="9"/>
       <c r="I159" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J159" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K159" s="11"/>
@@ -5474,11 +5496,11 @@
       <c r="G160" s="9"/>
       <c r="H160" s="9"/>
       <c r="I160" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J160" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K160" s="11"/>
@@ -5496,11 +5518,11 @@
       <c r="G161" s="9"/>
       <c r="H161" s="9"/>
       <c r="I161" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J161" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K161" s="11"/>
@@ -5518,11 +5540,11 @@
       <c r="G162" s="9"/>
       <c r="H162" s="9"/>
       <c r="I162" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J162" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K162" s="11"/>
@@ -5540,11 +5562,11 @@
       <c r="G163" s="9"/>
       <c r="H163" s="9"/>
       <c r="I163" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J163" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K163" s="11"/>
@@ -5562,11 +5584,11 @@
       <c r="G164" s="9"/>
       <c r="H164" s="9"/>
       <c r="I164" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J164" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K164" s="11"/>
@@ -5584,11 +5606,11 @@
       <c r="G165" s="9"/>
       <c r="H165" s="9"/>
       <c r="I165" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J165" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K165" s="11"/>
@@ -5606,11 +5628,11 @@
       <c r="G166" s="9"/>
       <c r="H166" s="9"/>
       <c r="I166" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J166" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K166" s="11"/>
@@ -5628,11 +5650,11 @@
       <c r="G167" s="9"/>
       <c r="H167" s="9"/>
       <c r="I167" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J167" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K167" s="11"/>
@@ -5650,11 +5672,11 @@
       <c r="G168" s="9"/>
       <c r="H168" s="9"/>
       <c r="I168" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J168" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K168" s="11"/>
@@ -5672,11 +5694,11 @@
       <c r="G169" s="9"/>
       <c r="H169" s="9"/>
       <c r="I169" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J169" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K169" s="11"/>
@@ -5694,11 +5716,11 @@
       <c r="G170" s="9"/>
       <c r="H170" s="9"/>
       <c r="I170" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J170" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K170" s="11"/>
@@ -5716,11 +5738,11 @@
       <c r="G171" s="9"/>
       <c r="H171" s="9"/>
       <c r="I171" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J171" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K171" s="11"/>
@@ -5738,11 +5760,11 @@
       <c r="G172" s="9"/>
       <c r="H172" s="9"/>
       <c r="I172" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J172" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K172" s="11"/>
@@ -5760,11 +5782,11 @@
       <c r="G173" s="9"/>
       <c r="H173" s="9"/>
       <c r="I173" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J173" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K173" s="11"/>
@@ -5782,11 +5804,11 @@
       <c r="G174" s="9"/>
       <c r="H174" s="9"/>
       <c r="I174" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J174" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K174" s="11"/>
@@ -5804,11 +5826,11 @@
       <c r="G175" s="9"/>
       <c r="H175" s="9"/>
       <c r="I175" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J175" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K175" s="11"/>
@@ -5826,11 +5848,11 @@
       <c r="G176" s="9"/>
       <c r="H176" s="9"/>
       <c r="I176" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J176" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K176" s="11"/>
@@ -5848,11 +5870,11 @@
       <c r="G177" s="9"/>
       <c r="H177" s="9"/>
       <c r="I177" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J177" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K177" s="11"/>
@@ -5870,11 +5892,11 @@
       <c r="G178" s="9"/>
       <c r="H178" s="9"/>
       <c r="I178" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J178" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K178" s="11"/>
@@ -5892,11 +5914,11 @@
       <c r="G179" s="9"/>
       <c r="H179" s="9"/>
       <c r="I179" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J179" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K179" s="11"/>
@@ -5914,11 +5936,11 @@
       <c r="G180" s="9"/>
       <c r="H180" s="9"/>
       <c r="I180" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J180" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K180" s="11"/>
@@ -5936,11 +5958,11 @@
       <c r="G181" s="9"/>
       <c r="H181" s="9"/>
       <c r="I181" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J181" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K181" s="11"/>
@@ -5958,11 +5980,11 @@
       <c r="G182" s="9"/>
       <c r="H182" s="9"/>
       <c r="I182" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J182" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K182" s="11"/>
@@ -5980,11 +6002,11 @@
       <c r="G183" s="9"/>
       <c r="H183" s="9"/>
       <c r="I183" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J183" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K183" s="11"/>
@@ -6002,11 +6024,11 @@
       <c r="G184" s="9"/>
       <c r="H184" s="9"/>
       <c r="I184" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J184" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K184" s="11"/>
@@ -6024,11 +6046,11 @@
       <c r="G185" s="9"/>
       <c r="H185" s="9"/>
       <c r="I185" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J185" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K185" s="11"/>
@@ -6046,11 +6068,11 @@
       <c r="G186" s="9"/>
       <c r="H186" s="9"/>
       <c r="I186" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J186" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K186" s="11"/>
@@ -6068,11 +6090,11 @@
       <c r="G187" s="9"/>
       <c r="H187" s="9"/>
       <c r="I187" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J187" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K187" s="11"/>
@@ -6090,11 +6112,11 @@
       <c r="G188" s="9"/>
       <c r="H188" s="9"/>
       <c r="I188" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J188" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K188" s="11"/>
@@ -6112,11 +6134,11 @@
       <c r="G189" s="9"/>
       <c r="H189" s="9"/>
       <c r="I189" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J189" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K189" s="11"/>
@@ -6134,11 +6156,11 @@
       <c r="G190" s="9"/>
       <c r="H190" s="9"/>
       <c r="I190" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J190" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K190" s="11"/>
@@ -6156,11 +6178,11 @@
       <c r="G191" s="9"/>
       <c r="H191" s="9"/>
       <c r="I191" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J191" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K191" s="11"/>
@@ -6178,11 +6200,11 @@
       <c r="G192" s="9"/>
       <c r="H192" s="9"/>
       <c r="I192" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J192" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K192" s="11"/>
@@ -6200,11 +6222,11 @@
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J193" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K193" s="11"/>
@@ -6222,11 +6244,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -6244,11 +6266,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -6266,11 +6288,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -6288,11 +6310,11 @@
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J197" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K197" s="11"/>
@@ -6310,11 +6332,11 @@
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
       <c r="I198" s="10" t="str">
-        <f t="shared" ref="I198:I261" si="64">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="66">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="10" t="str">
-        <f t="shared" ref="J198:J261" si="65">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="67">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="11"/>
@@ -6332,11 +6354,11 @@
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
       <c r="I199" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J199" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K199" s="11"/>
@@ -6354,11 +6376,11 @@
       <c r="G200" s="9"/>
       <c r="H200" s="9"/>
       <c r="I200" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J200" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K200" s="11"/>
@@ -6376,11 +6398,11 @@
       <c r="G201" s="9"/>
       <c r="H201" s="9"/>
       <c r="I201" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J201" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K201" s="11"/>
@@ -6398,11 +6420,11 @@
       <c r="G202" s="9"/>
       <c r="H202" s="9"/>
       <c r="I202" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J202" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K202" s="11"/>
@@ -6420,11 +6442,11 @@
       <c r="G203" s="9"/>
       <c r="H203" s="9"/>
       <c r="I203" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J203" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K203" s="11"/>
@@ -6442,11 +6464,11 @@
       <c r="G204" s="9"/>
       <c r="H204" s="9"/>
       <c r="I204" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J204" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K204" s="11"/>
@@ -6464,11 +6486,11 @@
       <c r="G205" s="9"/>
       <c r="H205" s="9"/>
       <c r="I205" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J205" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K205" s="11"/>
@@ -6486,11 +6508,11 @@
       <c r="G206" s="9"/>
       <c r="H206" s="9"/>
       <c r="I206" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J206" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K206" s="11"/>
@@ -6508,11 +6530,11 @@
       <c r="G207" s="9"/>
       <c r="H207" s="9"/>
       <c r="I207" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J207" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K207" s="11"/>
@@ -6530,11 +6552,11 @@
       <c r="G208" s="9"/>
       <c r="H208" s="9"/>
       <c r="I208" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J208" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K208" s="11"/>
@@ -6552,11 +6574,11 @@
       <c r="G209" s="9"/>
       <c r="H209" s="9"/>
       <c r="I209" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J209" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K209" s="11"/>
@@ -6574,11 +6596,11 @@
       <c r="G210" s="9"/>
       <c r="H210" s="9"/>
       <c r="I210" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J210" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K210" s="11"/>
@@ -6596,11 +6618,11 @@
       <c r="G211" s="9"/>
       <c r="H211" s="9"/>
       <c r="I211" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J211" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K211" s="11"/>
@@ -6618,11 +6640,11 @@
       <c r="G212" s="9"/>
       <c r="H212" s="9"/>
       <c r="I212" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J212" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K212" s="11"/>
@@ -6640,11 +6662,11 @@
       <c r="G213" s="9"/>
       <c r="H213" s="9"/>
       <c r="I213" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J213" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K213" s="11"/>
@@ -6662,11 +6684,11 @@
       <c r="G214" s="9"/>
       <c r="H214" s="9"/>
       <c r="I214" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J214" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K214" s="11"/>
@@ -6684,11 +6706,11 @@
       <c r="G215" s="9"/>
       <c r="H215" s="9"/>
       <c r="I215" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J215" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K215" s="11"/>
@@ -6706,11 +6728,11 @@
       <c r="G216" s="9"/>
       <c r="H216" s="9"/>
       <c r="I216" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J216" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K216" s="11"/>
@@ -6728,11 +6750,11 @@
       <c r="G217" s="9"/>
       <c r="H217" s="9"/>
       <c r="I217" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J217" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K217" s="11"/>
@@ -6750,11 +6772,11 @@
       <c r="G218" s="9"/>
       <c r="H218" s="9"/>
       <c r="I218" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J218" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K218" s="11"/>
@@ -6772,11 +6794,11 @@
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
       <c r="I219" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J219" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K219" s="11"/>
@@ -6794,11 +6816,11 @@
       <c r="G220" s="9"/>
       <c r="H220" s="9"/>
       <c r="I220" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J220" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K220" s="11"/>
@@ -6816,11 +6838,11 @@
       <c r="G221" s="9"/>
       <c r="H221" s="9"/>
       <c r="I221" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J221" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K221" s="11"/>
@@ -6838,11 +6860,11 @@
       <c r="G222" s="9"/>
       <c r="H222" s="9"/>
       <c r="I222" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J222" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K222" s="11"/>
@@ -6860,11 +6882,11 @@
       <c r="G223" s="9"/>
       <c r="H223" s="9"/>
       <c r="I223" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J223" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K223" s="11"/>
@@ -6882,11 +6904,11 @@
       <c r="G224" s="9"/>
       <c r="H224" s="9"/>
       <c r="I224" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J224" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K224" s="11"/>
@@ -6904,11 +6926,11 @@
       <c r="G225" s="9"/>
       <c r="H225" s="9"/>
       <c r="I225" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J225" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K225" s="11"/>
@@ -6926,11 +6948,11 @@
       <c r="G226" s="9"/>
       <c r="H226" s="9"/>
       <c r="I226" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J226" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K226" s="11"/>
@@ -6948,11 +6970,11 @@
       <c r="G227" s="9"/>
       <c r="H227" s="9"/>
       <c r="I227" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J227" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K227" s="11"/>
@@ -6970,11 +6992,11 @@
       <c r="G228" s="9"/>
       <c r="H228" s="9"/>
       <c r="I228" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J228" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K228" s="11"/>
@@ -6992,11 +7014,11 @@
       <c r="G229" s="9"/>
       <c r="H229" s="9"/>
       <c r="I229" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J229" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K229" s="11"/>
@@ -7014,11 +7036,11 @@
       <c r="G230" s="9"/>
       <c r="H230" s="9"/>
       <c r="I230" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J230" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K230" s="11"/>
@@ -7036,11 +7058,11 @@
       <c r="G231" s="9"/>
       <c r="H231" s="9"/>
       <c r="I231" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J231" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K231" s="11"/>
@@ -7058,11 +7080,11 @@
       <c r="G232" s="9"/>
       <c r="H232" s="9"/>
       <c r="I232" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J232" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K232" s="11"/>
@@ -7080,11 +7102,11 @@
       <c r="G233" s="9"/>
       <c r="H233" s="9"/>
       <c r="I233" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J233" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K233" s="11"/>
@@ -7102,11 +7124,11 @@
       <c r="G234" s="9"/>
       <c r="H234" s="9"/>
       <c r="I234" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J234" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K234" s="11"/>
@@ -7124,11 +7146,11 @@
       <c r="G235" s="9"/>
       <c r="H235" s="9"/>
       <c r="I235" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J235" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K235" s="11"/>
@@ -7146,11 +7168,11 @@
       <c r="G236" s="9"/>
       <c r="H236" s="9"/>
       <c r="I236" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J236" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K236" s="11"/>
@@ -7168,11 +7190,11 @@
       <c r="G237" s="9"/>
       <c r="H237" s="9"/>
       <c r="I237" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J237" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K237" s="11"/>
@@ -7190,11 +7212,11 @@
       <c r="G238" s="9"/>
       <c r="H238" s="9"/>
       <c r="I238" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J238" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K238" s="11"/>
@@ -7212,11 +7234,11 @@
       <c r="G239" s="9"/>
       <c r="H239" s="9"/>
       <c r="I239" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J239" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K239" s="11"/>
@@ -7234,11 +7256,11 @@
       <c r="G240" s="9"/>
       <c r="H240" s="9"/>
       <c r="I240" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J240" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K240" s="11"/>
@@ -7256,11 +7278,11 @@
       <c r="G241" s="9"/>
       <c r="H241" s="9"/>
       <c r="I241" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J241" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K241" s="11"/>
@@ -7278,11 +7300,11 @@
       <c r="G242" s="9"/>
       <c r="H242" s="9"/>
       <c r="I242" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J242" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K242" s="11"/>
@@ -7300,11 +7322,11 @@
       <c r="G243" s="9"/>
       <c r="H243" s="9"/>
       <c r="I243" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J243" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K243" s="11"/>
@@ -7322,11 +7344,11 @@
       <c r="G244" s="9"/>
       <c r="H244" s="9"/>
       <c r="I244" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J244" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K244" s="11"/>
@@ -7344,11 +7366,11 @@
       <c r="G245" s="9"/>
       <c r="H245" s="9"/>
       <c r="I245" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J245" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K245" s="11"/>
@@ -7366,11 +7388,11 @@
       <c r="G246" s="9"/>
       <c r="H246" s="9"/>
       <c r="I246" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J246" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K246" s="11"/>
@@ -7388,11 +7410,11 @@
       <c r="G247" s="9"/>
       <c r="H247" s="9"/>
       <c r="I247" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J247" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K247" s="11"/>
@@ -7410,11 +7432,11 @@
       <c r="G248" s="9"/>
       <c r="H248" s="9"/>
       <c r="I248" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J248" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K248" s="11"/>
@@ -7432,11 +7454,11 @@
       <c r="G249" s="9"/>
       <c r="H249" s="9"/>
       <c r="I249" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J249" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K249" s="11"/>
@@ -7454,11 +7476,11 @@
       <c r="G250" s="9"/>
       <c r="H250" s="9"/>
       <c r="I250" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J250" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K250" s="11"/>
@@ -7476,11 +7498,11 @@
       <c r="G251" s="9"/>
       <c r="H251" s="9"/>
       <c r="I251" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J251" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K251" s="11"/>
@@ -7498,11 +7520,11 @@
       <c r="G252" s="9"/>
       <c r="H252" s="9"/>
       <c r="I252" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J252" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K252" s="11"/>
@@ -7520,11 +7542,11 @@
       <c r="G253" s="9"/>
       <c r="H253" s="9"/>
       <c r="I253" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J253" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K253" s="11"/>
@@ -7542,11 +7564,11 @@
       <c r="G254" s="9"/>
       <c r="H254" s="9"/>
       <c r="I254" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J254" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K254" s="11"/>
@@ -7564,11 +7586,11 @@
       <c r="G255" s="9"/>
       <c r="H255" s="9"/>
       <c r="I255" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J255" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K255" s="11"/>
@@ -7586,11 +7608,11 @@
       <c r="G256" s="9"/>
       <c r="H256" s="9"/>
       <c r="I256" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J256" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K256" s="11"/>
@@ -7608,11 +7630,11 @@
       <c r="G257" s="9"/>
       <c r="H257" s="9"/>
       <c r="I257" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J257" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K257" s="11"/>
@@ -7630,11 +7652,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -7652,11 +7674,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -7674,11 +7696,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -7696,11 +7718,11 @@
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
       <c r="I261" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J261" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K261" s="11"/>
@@ -7718,11 +7740,11 @@
       <c r="G262" s="9"/>
       <c r="H262" s="9"/>
       <c r="I262" s="10" t="str">
-        <f t="shared" ref="I262:I325" si="66">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="68">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="10" t="str">
-        <f t="shared" ref="J262:J325" si="67">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="69">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="11"/>
@@ -7740,11 +7762,11 @@
       <c r="G263" s="9"/>
       <c r="H263" s="9"/>
       <c r="I263" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J263" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K263" s="11"/>
@@ -7762,11 +7784,11 @@
       <c r="G264" s="9"/>
       <c r="H264" s="9"/>
       <c r="I264" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J264" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K264" s="11"/>
@@ -7784,11 +7806,11 @@
       <c r="G265" s="9"/>
       <c r="H265" s="9"/>
       <c r="I265" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J265" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K265" s="11"/>
@@ -7806,11 +7828,11 @@
       <c r="G266" s="9"/>
       <c r="H266" s="9"/>
       <c r="I266" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J266" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K266" s="11"/>
@@ -7828,11 +7850,11 @@
       <c r="G267" s="9"/>
       <c r="H267" s="9"/>
       <c r="I267" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J267" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K267" s="11"/>
@@ -7850,11 +7872,11 @@
       <c r="G268" s="9"/>
       <c r="H268" s="9"/>
       <c r="I268" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J268" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K268" s="11"/>
@@ -7872,11 +7894,11 @@
       <c r="G269" s="9"/>
       <c r="H269" s="9"/>
       <c r="I269" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J269" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K269" s="11"/>
@@ -7894,11 +7916,11 @@
       <c r="G270" s="9"/>
       <c r="H270" s="9"/>
       <c r="I270" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J270" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K270" s="11"/>
@@ -7916,11 +7938,11 @@
       <c r="G271" s="9"/>
       <c r="H271" s="9"/>
       <c r="I271" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J271" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K271" s="11"/>
@@ -7938,11 +7960,11 @@
       <c r="G272" s="9"/>
       <c r="H272" s="9"/>
       <c r="I272" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J272" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K272" s="11"/>
@@ -7960,11 +7982,11 @@
       <c r="G273" s="9"/>
       <c r="H273" s="9"/>
       <c r="I273" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J273" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K273" s="11"/>
@@ -7982,11 +8004,11 @@
       <c r="G274" s="9"/>
       <c r="H274" s="9"/>
       <c r="I274" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J274" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K274" s="11"/>
@@ -8004,11 +8026,11 @@
       <c r="G275" s="9"/>
       <c r="H275" s="9"/>
       <c r="I275" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J275" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K275" s="11"/>
@@ -8026,11 +8048,11 @@
       <c r="G276" s="9"/>
       <c r="H276" s="9"/>
       <c r="I276" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J276" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K276" s="11"/>
@@ -8048,11 +8070,11 @@
       <c r="G277" s="9"/>
       <c r="H277" s="9"/>
       <c r="I277" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J277" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K277" s="11"/>
@@ -8070,11 +8092,11 @@
       <c r="G278" s="9"/>
       <c r="H278" s="9"/>
       <c r="I278" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J278" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K278" s="11"/>
@@ -8092,11 +8114,11 @@
       <c r="G279" s="9"/>
       <c r="H279" s="9"/>
       <c r="I279" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J279" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K279" s="11"/>
@@ -8114,11 +8136,11 @@
       <c r="G280" s="9"/>
       <c r="H280" s="9"/>
       <c r="I280" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J280" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K280" s="11"/>
@@ -8136,11 +8158,11 @@
       <c r="G281" s="9"/>
       <c r="H281" s="9"/>
       <c r="I281" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J281" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K281" s="11"/>
@@ -8158,11 +8180,11 @@
       <c r="G282" s="9"/>
       <c r="H282" s="9"/>
       <c r="I282" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J282" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K282" s="11"/>
@@ -8180,11 +8202,11 @@
       <c r="G283" s="9"/>
       <c r="H283" s="9"/>
       <c r="I283" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J283" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K283" s="11"/>
@@ -8202,11 +8224,11 @@
       <c r="G284" s="9"/>
       <c r="H284" s="9"/>
       <c r="I284" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J284" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K284" s="11"/>
@@ -8224,11 +8246,11 @@
       <c r="G285" s="9"/>
       <c r="H285" s="9"/>
       <c r="I285" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J285" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K285" s="11"/>
@@ -8246,11 +8268,11 @@
       <c r="G286" s="9"/>
       <c r="H286" s="9"/>
       <c r="I286" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J286" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K286" s="11"/>
@@ -8268,11 +8290,11 @@
       <c r="G287" s="9"/>
       <c r="H287" s="9"/>
       <c r="I287" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J287" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K287" s="11"/>
@@ -8290,11 +8312,11 @@
       <c r="G288" s="9"/>
       <c r="H288" s="9"/>
       <c r="I288" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J288" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K288" s="11"/>
@@ -8312,11 +8334,11 @@
       <c r="G289" s="9"/>
       <c r="H289" s="9"/>
       <c r="I289" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J289" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K289" s="11"/>
@@ -8334,11 +8356,11 @@
       <c r="G290" s="9"/>
       <c r="H290" s="9"/>
       <c r="I290" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J290" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K290" s="11"/>
@@ -8356,11 +8378,11 @@
       <c r="G291" s="9"/>
       <c r="H291" s="9"/>
       <c r="I291" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J291" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K291" s="11"/>
@@ -8378,11 +8400,11 @@
       <c r="G292" s="9"/>
       <c r="H292" s="9"/>
       <c r="I292" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J292" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K292" s="11"/>
@@ -8400,11 +8422,11 @@
       <c r="G293" s="9"/>
       <c r="H293" s="9"/>
       <c r="I293" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J293" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K293" s="11"/>
@@ -8422,11 +8444,11 @@
       <c r="G294" s="9"/>
       <c r="H294" s="9"/>
       <c r="I294" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J294" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K294" s="11"/>
@@ -8444,11 +8466,11 @@
       <c r="G295" s="9"/>
       <c r="H295" s="9"/>
       <c r="I295" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J295" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K295" s="11"/>
@@ -8466,11 +8488,11 @@
       <c r="G296" s="9"/>
       <c r="H296" s="9"/>
       <c r="I296" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J296" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K296" s="11"/>
@@ -8488,11 +8510,11 @@
       <c r="G297" s="9"/>
       <c r="H297" s="9"/>
       <c r="I297" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J297" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K297" s="11"/>
@@ -8510,11 +8532,11 @@
       <c r="G298" s="9"/>
       <c r="H298" s="9"/>
       <c r="I298" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J298" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K298" s="11"/>
@@ -8532,11 +8554,11 @@
       <c r="G299" s="9"/>
       <c r="H299" s="9"/>
       <c r="I299" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J299" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K299" s="11"/>
@@ -8554,11 +8576,11 @@
       <c r="G300" s="9"/>
       <c r="H300" s="9"/>
       <c r="I300" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J300" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K300" s="11"/>
@@ -8576,11 +8598,11 @@
       <c r="G301" s="9"/>
       <c r="H301" s="9"/>
       <c r="I301" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J301" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K301" s="11"/>
@@ -8598,11 +8620,11 @@
       <c r="G302" s="9"/>
       <c r="H302" s="9"/>
       <c r="I302" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J302" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K302" s="11"/>
@@ -8620,11 +8642,11 @@
       <c r="G303" s="9"/>
       <c r="H303" s="9"/>
       <c r="I303" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J303" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K303" s="11"/>
@@ -8642,11 +8664,11 @@
       <c r="G304" s="9"/>
       <c r="H304" s="9"/>
       <c r="I304" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J304" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K304" s="11"/>
@@ -8664,11 +8686,11 @@
       <c r="G305" s="9"/>
       <c r="H305" s="9"/>
       <c r="I305" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J305" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K305" s="11"/>
@@ -8686,11 +8708,11 @@
       <c r="G306" s="9"/>
       <c r="H306" s="9"/>
       <c r="I306" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J306" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K306" s="11"/>
@@ -8708,11 +8730,11 @@
       <c r="G307" s="9"/>
       <c r="H307" s="9"/>
       <c r="I307" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J307" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K307" s="11"/>
@@ -8730,11 +8752,11 @@
       <c r="G308" s="9"/>
       <c r="H308" s="9"/>
       <c r="I308" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J308" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K308" s="11"/>
@@ -8752,11 +8774,11 @@
       <c r="G309" s="9"/>
       <c r="H309" s="9"/>
       <c r="I309" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J309" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K309" s="11"/>
@@ -8774,11 +8796,11 @@
       <c r="G310" s="9"/>
       <c r="H310" s="9"/>
       <c r="I310" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J310" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K310" s="11"/>
@@ -8796,11 +8818,11 @@
       <c r="G311" s="9"/>
       <c r="H311" s="9"/>
       <c r="I311" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J311" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K311" s="11"/>
@@ -8818,11 +8840,11 @@
       <c r="G312" s="9"/>
       <c r="H312" s="9"/>
       <c r="I312" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J312" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K312" s="11"/>
@@ -8840,11 +8862,11 @@
       <c r="G313" s="9"/>
       <c r="H313" s="9"/>
       <c r="I313" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J313" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K313" s="11"/>
@@ -8862,11 +8884,11 @@
       <c r="G314" s="9"/>
       <c r="H314" s="9"/>
       <c r="I314" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J314" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K314" s="11"/>
@@ -8884,11 +8906,11 @@
       <c r="G315" s="9"/>
       <c r="H315" s="9"/>
       <c r="I315" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J315" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K315" s="11"/>
@@ -8906,11 +8928,11 @@
       <c r="G316" s="9"/>
       <c r="H316" s="9"/>
       <c r="I316" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J316" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K316" s="11"/>
@@ -8928,11 +8950,11 @@
       <c r="G317" s="9"/>
       <c r="H317" s="9"/>
       <c r="I317" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J317" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K317" s="11"/>
@@ -8950,11 +8972,11 @@
       <c r="G318" s="9"/>
       <c r="H318" s="9"/>
       <c r="I318" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J318" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K318" s="11"/>
@@ -8972,11 +8994,11 @@
       <c r="G319" s="9"/>
       <c r="H319" s="9"/>
       <c r="I319" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J319" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K319" s="11"/>
@@ -8994,11 +9016,11 @@
       <c r="G320" s="9"/>
       <c r="H320" s="9"/>
       <c r="I320" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J320" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K320" s="11"/>
@@ -9016,11 +9038,11 @@
       <c r="G321" s="9"/>
       <c r="H321" s="9"/>
       <c r="I321" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J321" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K321" s="11"/>
@@ -9038,11 +9060,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -9060,11 +9082,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -9082,11 +9104,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -9104,11 +9126,11 @@
       <c r="G325" s="9"/>
       <c r="H325" s="9"/>
       <c r="I325" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J325" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K325" s="11"/>
@@ -9126,11 +9148,11 @@
       <c r="G326" s="9"/>
       <c r="H326" s="9"/>
       <c r="I326" s="10" t="str">
-        <f t="shared" ref="I326:I389" si="68">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="70">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="10" t="str">
-        <f t="shared" ref="J326:J389" si="69">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="71">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="11"/>
@@ -9148,11 +9170,11 @@
       <c r="G327" s="9"/>
       <c r="H327" s="9"/>
       <c r="I327" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J327" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K327" s="11"/>
@@ -9170,11 +9192,11 @@
       <c r="G328" s="9"/>
       <c r="H328" s="9"/>
       <c r="I328" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J328" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K328" s="11"/>
@@ -9192,11 +9214,11 @@
       <c r="G329" s="9"/>
       <c r="H329" s="9"/>
       <c r="I329" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J329" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K329" s="11"/>
@@ -9214,11 +9236,11 @@
       <c r="G330" s="9"/>
       <c r="H330" s="9"/>
       <c r="I330" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J330" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K330" s="11"/>
@@ -9236,11 +9258,11 @@
       <c r="G331" s="9"/>
       <c r="H331" s="9"/>
       <c r="I331" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J331" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K331" s="11"/>
@@ -9258,11 +9280,11 @@
       <c r="G332" s="9"/>
       <c r="H332" s="9"/>
       <c r="I332" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J332" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K332" s="11"/>
@@ -9280,11 +9302,11 @@
       <c r="G333" s="9"/>
       <c r="H333" s="9"/>
       <c r="I333" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J333" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K333" s="11"/>
@@ -9302,11 +9324,11 @@
       <c r="G334" s="9"/>
       <c r="H334" s="9"/>
       <c r="I334" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J334" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K334" s="11"/>
@@ -9324,11 +9346,11 @@
       <c r="G335" s="9"/>
       <c r="H335" s="9"/>
       <c r="I335" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J335" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K335" s="11"/>
@@ -9346,11 +9368,11 @@
       <c r="G336" s="9"/>
       <c r="H336" s="9"/>
       <c r="I336" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J336" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K336" s="11"/>
@@ -9368,11 +9390,11 @@
       <c r="G337" s="9"/>
       <c r="H337" s="9"/>
       <c r="I337" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J337" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K337" s="11"/>
@@ -9390,11 +9412,11 @@
       <c r="G338" s="9"/>
       <c r="H338" s="9"/>
       <c r="I338" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J338" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K338" s="11"/>
@@ -9412,11 +9434,11 @@
       <c r="G339" s="9"/>
       <c r="H339" s="9"/>
       <c r="I339" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J339" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K339" s="11"/>
@@ -9434,11 +9456,11 @@
       <c r="G340" s="9"/>
       <c r="H340" s="9"/>
       <c r="I340" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J340" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K340" s="11"/>
@@ -9456,11 +9478,11 @@
       <c r="G341" s="9"/>
       <c r="H341" s="9"/>
       <c r="I341" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J341" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K341" s="11"/>
@@ -9478,11 +9500,11 @@
       <c r="G342" s="9"/>
       <c r="H342" s="9"/>
       <c r="I342" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J342" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K342" s="11"/>
@@ -9500,11 +9522,11 @@
       <c r="G343" s="9"/>
       <c r="H343" s="9"/>
       <c r="I343" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J343" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K343" s="11"/>
@@ -9522,11 +9544,11 @@
       <c r="G344" s="9"/>
       <c r="H344" s="9"/>
       <c r="I344" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J344" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K344" s="11"/>
@@ -9544,11 +9566,11 @@
       <c r="G345" s="9"/>
       <c r="H345" s="9"/>
       <c r="I345" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J345" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K345" s="11"/>
@@ -9566,11 +9588,11 @@
       <c r="G346" s="9"/>
       <c r="H346" s="9"/>
       <c r="I346" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J346" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K346" s="11"/>
@@ -9588,11 +9610,11 @@
       <c r="G347" s="9"/>
       <c r="H347" s="9"/>
       <c r="I347" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J347" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K347" s="11"/>
@@ -9610,11 +9632,11 @@
       <c r="G348" s="9"/>
       <c r="H348" s="9"/>
       <c r="I348" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J348" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K348" s="11"/>
@@ -9632,11 +9654,11 @@
       <c r="G349" s="9"/>
       <c r="H349" s="9"/>
       <c r="I349" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J349" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K349" s="11"/>
@@ -9654,11 +9676,11 @@
       <c r="G350" s="9"/>
       <c r="H350" s="9"/>
       <c r="I350" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J350" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K350" s="11"/>
@@ -9676,11 +9698,11 @@
       <c r="G351" s="9"/>
       <c r="H351" s="9"/>
       <c r="I351" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J351" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K351" s="11"/>
@@ -9698,11 +9720,11 @@
       <c r="G352" s="9"/>
       <c r="H352" s="9"/>
       <c r="I352" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J352" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K352" s="11"/>
@@ -9720,11 +9742,11 @@
       <c r="G353" s="9"/>
       <c r="H353" s="9"/>
       <c r="I353" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J353" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K353" s="11"/>
@@ -9742,11 +9764,11 @@
       <c r="G354" s="9"/>
       <c r="H354" s="9"/>
       <c r="I354" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J354" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K354" s="11"/>
@@ -9764,11 +9786,11 @@
       <c r="G355" s="9"/>
       <c r="H355" s="9"/>
       <c r="I355" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J355" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K355" s="11"/>
@@ -9786,11 +9808,11 @@
       <c r="G356" s="9"/>
       <c r="H356" s="9"/>
       <c r="I356" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J356" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K356" s="11"/>
@@ -9808,11 +9830,11 @@
       <c r="G357" s="9"/>
       <c r="H357" s="9"/>
       <c r="I357" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J357" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K357" s="11"/>
@@ -9830,11 +9852,11 @@
       <c r="G358" s="9"/>
       <c r="H358" s="9"/>
       <c r="I358" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J358" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K358" s="11"/>
@@ -9852,11 +9874,11 @@
       <c r="G359" s="9"/>
       <c r="H359" s="9"/>
       <c r="I359" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J359" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K359" s="11"/>
@@ -9874,11 +9896,11 @@
       <c r="G360" s="9"/>
       <c r="H360" s="9"/>
       <c r="I360" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J360" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K360" s="11"/>
@@ -9896,11 +9918,11 @@
       <c r="G361" s="9"/>
       <c r="H361" s="9"/>
       <c r="I361" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J361" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K361" s="11"/>
@@ -9918,11 +9940,11 @@
       <c r="G362" s="9"/>
       <c r="H362" s="9"/>
       <c r="I362" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J362" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K362" s="11"/>
@@ -9940,11 +9962,11 @@
       <c r="G363" s="9"/>
       <c r="H363" s="9"/>
       <c r="I363" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J363" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K363" s="11"/>
@@ -9962,11 +9984,11 @@
       <c r="G364" s="9"/>
       <c r="H364" s="9"/>
       <c r="I364" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J364" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K364" s="11"/>
@@ -9984,11 +10006,11 @@
       <c r="G365" s="9"/>
       <c r="H365" s="9"/>
       <c r="I365" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J365" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K365" s="11"/>
@@ -10006,11 +10028,11 @@
       <c r="G366" s="9"/>
       <c r="H366" s="9"/>
       <c r="I366" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J366" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K366" s="11"/>
@@ -10028,11 +10050,11 @@
       <c r="G367" s="9"/>
       <c r="H367" s="9"/>
       <c r="I367" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J367" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K367" s="11"/>
@@ -10050,11 +10072,11 @@
       <c r="G368" s="9"/>
       <c r="H368" s="9"/>
       <c r="I368" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J368" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K368" s="11"/>
@@ -10072,11 +10094,11 @@
       <c r="G369" s="9"/>
       <c r="H369" s="9"/>
       <c r="I369" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J369" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K369" s="11"/>
@@ -10094,11 +10116,11 @@
       <c r="G370" s="9"/>
       <c r="H370" s="9"/>
       <c r="I370" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J370" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K370" s="11"/>
@@ -10116,11 +10138,11 @@
       <c r="G371" s="9"/>
       <c r="H371" s="9"/>
       <c r="I371" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J371" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K371" s="11"/>
@@ -10138,11 +10160,11 @@
       <c r="G372" s="9"/>
       <c r="H372" s="9"/>
       <c r="I372" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J372" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K372" s="11"/>
@@ -10160,11 +10182,11 @@
       <c r="G373" s="9"/>
       <c r="H373" s="9"/>
       <c r="I373" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J373" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K373" s="11"/>
@@ -10182,11 +10204,11 @@
       <c r="G374" s="9"/>
       <c r="H374" s="9"/>
       <c r="I374" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J374" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K374" s="11"/>
@@ -10204,11 +10226,11 @@
       <c r="G375" s="9"/>
       <c r="H375" s="9"/>
       <c r="I375" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J375" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K375" s="11"/>
@@ -10226,11 +10248,11 @@
       <c r="G376" s="9"/>
       <c r="H376" s="9"/>
       <c r="I376" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J376" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K376" s="11"/>
@@ -10248,11 +10270,11 @@
       <c r="G377" s="9"/>
       <c r="H377" s="9"/>
       <c r="I377" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J377" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K377" s="11"/>
@@ -10270,11 +10292,11 @@
       <c r="G378" s="9"/>
       <c r="H378" s="9"/>
       <c r="I378" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J378" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K378" s="11"/>
@@ -10292,11 +10314,11 @@
       <c r="G379" s="9"/>
       <c r="H379" s="9"/>
       <c r="I379" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J379" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K379" s="11"/>
@@ -10314,11 +10336,11 @@
       <c r="G380" s="9"/>
       <c r="H380" s="9"/>
       <c r="I380" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J380" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K380" s="11"/>
@@ -10336,11 +10358,11 @@
       <c r="G381" s="9"/>
       <c r="H381" s="9"/>
       <c r="I381" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J381" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K381" s="11"/>
@@ -10358,11 +10380,11 @@
       <c r="G382" s="9"/>
       <c r="H382" s="9"/>
       <c r="I382" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J382" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K382" s="11"/>
@@ -10380,11 +10402,11 @@
       <c r="G383" s="9"/>
       <c r="H383" s="9"/>
       <c r="I383" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J383" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K383" s="11"/>
@@ -10402,11 +10424,11 @@
       <c r="G384" s="9"/>
       <c r="H384" s="9"/>
       <c r="I384" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J384" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K384" s="11"/>
@@ -10424,11 +10446,11 @@
       <c r="G385" s="9"/>
       <c r="H385" s="9"/>
       <c r="I385" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J385" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K385" s="11"/>
@@ -10446,11 +10468,11 @@
       <c r="G386" s="9"/>
       <c r="H386" s="9"/>
       <c r="I386" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J386" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K386" s="11"/>
@@ -10468,11 +10490,11 @@
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J387" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K387" s="11"/>
@@ -10490,11 +10512,11 @@
       <c r="G388" s="9"/>
       <c r="H388" s="9"/>
       <c r="I388" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J388" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K388" s="11"/>
@@ -10512,11 +10534,11 @@
       <c r="G389" s="9"/>
       <c r="H389" s="9"/>
       <c r="I389" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J389" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K389" s="11"/>
@@ -10534,11 +10556,11 @@
       <c r="G390" s="9"/>
       <c r="H390" s="9"/>
       <c r="I390" s="10" t="str">
-        <f t="shared" ref="I390:I401" si="70">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="72">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="10" t="str">
-        <f t="shared" ref="J390:J401" si="71">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="73">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="11"/>
@@ -10556,11 +10578,11 @@
       <c r="G391" s="9"/>
       <c r="H391" s="9"/>
       <c r="I391" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J391" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K391" s="11"/>
@@ -10578,11 +10600,11 @@
       <c r="G392" s="9"/>
       <c r="H392" s="9"/>
       <c r="I392" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J392" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K392" s="11"/>
@@ -10600,11 +10622,11 @@
       <c r="G393" s="9"/>
       <c r="H393" s="9"/>
       <c r="I393" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J393" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K393" s="11"/>
@@ -10622,11 +10644,11 @@
       <c r="G394" s="9"/>
       <c r="H394" s="9"/>
       <c r="I394" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J394" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K394" s="11"/>
@@ -10644,11 +10666,11 @@
       <c r="G395" s="9"/>
       <c r="H395" s="9"/>
       <c r="I395" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J395" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K395" s="11"/>
@@ -10666,11 +10688,11 @@
       <c r="G396" s="9"/>
       <c r="H396" s="9"/>
       <c r="I396" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J396" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K396" s="11"/>
@@ -10688,11 +10710,11 @@
       <c r="G397" s="9"/>
       <c r="H397" s="9"/>
       <c r="I397" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J397" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K397" s="11"/>
@@ -10710,11 +10732,11 @@
       <c r="G398" s="9"/>
       <c r="H398" s="9"/>
       <c r="I398" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J398" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K398" s="11"/>
@@ -10732,11 +10754,11 @@
       <c r="G399" s="9"/>
       <c r="H399" s="9"/>
       <c r="I399" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J399" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K399" s="11"/>
@@ -10754,11 +10776,11 @@
       <c r="G400" s="9"/>
       <c r="H400" s="9"/>
       <c r="I400" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J400" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K400" s="11"/>
@@ -10776,11 +10798,11 @@
       <c r="G401" s="9"/>
       <c r="H401" s="9"/>
       <c r="I401" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J401" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K401" s="11"/>

--- a/12626731.xlsx
+++ b/12626731.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHIVEN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED23621A-C2E5-40CA-93FA-EA2621AA1B8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{866B1C7F-26BA-4572-A8A1-582C840E2087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3067,25 +3067,47 @@
       <c r="N49" s="12"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="8"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="9"/>
-      <c r="H50" s="9"/>
-      <c r="I50" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="11"/>
-      <c r="L50" s="11"/>
-      <c r="M50" s="11"/>
+      <c r="A50" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B50" s="14">
+        <v>400</v>
+      </c>
+      <c r="C50" s="14">
+        <v>0</v>
+      </c>
+      <c r="D50" s="14">
+        <v>120</v>
+      </c>
+      <c r="E50" s="14">
+        <v>70</v>
+      </c>
+      <c r="F50" s="14">
+        <v>200</v>
+      </c>
+      <c r="G50" s="14">
+        <v>4</v>
+      </c>
+      <c r="H50" s="14">
+        <v>270</v>
+      </c>
+      <c r="I50" s="15">
+        <f t="shared" ref="I50" si="62">IF(SUM(B50:F50,H50)=0,"",SUM(B50:F50,H50))</f>
+        <v>1060</v>
+      </c>
+      <c r="J50" s="15">
+        <f t="shared" ref="J50" si="63">IF(I50="","",1440-I50)</f>
+        <v>380</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N50" s="12"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
@@ -3516,11 +3538,11 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
       <c r="I70" s="10" t="str">
-        <f t="shared" ref="I70:I133" si="62">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="64">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="10" t="str">
-        <f t="shared" ref="J70:J133" si="63">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="65">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="11"/>
@@ -3538,11 +3560,11 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
       <c r="I71" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J71" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K71" s="11"/>
@@ -3560,11 +3582,11 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
       <c r="I72" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J72" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K72" s="11"/>
@@ -3582,11 +3604,11 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
       <c r="I73" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J73" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K73" s="11"/>
@@ -3604,11 +3626,11 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
       <c r="I74" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J74" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K74" s="11"/>
@@ -3626,11 +3648,11 @@
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="I75" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J75" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K75" s="11"/>
@@ -3648,11 +3670,11 @@
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="I76" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J76" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K76" s="11"/>
@@ -3670,11 +3692,11 @@
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J77" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K77" s="11"/>
@@ -3692,11 +3714,11 @@
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J78" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K78" s="11"/>
@@ -3714,11 +3736,11 @@
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J79" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K79" s="11"/>
@@ -3736,11 +3758,11 @@
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J80" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K80" s="11"/>
@@ -3758,11 +3780,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J81" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -3780,11 +3802,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J82" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -3802,11 +3824,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J83" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -3824,11 +3846,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J84" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -3846,11 +3868,11 @@
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
       <c r="I85" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J85" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K85" s="11"/>
@@ -3868,11 +3890,11 @@
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J86" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K86" s="11"/>
@@ -3890,11 +3912,11 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
       <c r="I87" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J87" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K87" s="11"/>
@@ -3912,11 +3934,11 @@
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
       <c r="I88" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J88" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K88" s="11"/>
@@ -3934,11 +3956,11 @@
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
       <c r="I89" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J89" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K89" s="11"/>
@@ -3956,11 +3978,11 @@
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
       <c r="I90" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J90" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K90" s="11"/>
@@ -3978,11 +4000,11 @@
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
       <c r="I91" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J91" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K91" s="11"/>
@@ -4000,11 +4022,11 @@
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
       <c r="I92" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J92" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K92" s="11"/>
@@ -4022,11 +4044,11 @@
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
       <c r="I93" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J93" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K93" s="11"/>
@@ -4044,11 +4066,11 @@
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
       <c r="I94" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J94" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K94" s="11"/>
@@ -4066,11 +4088,11 @@
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
       <c r="I95" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J95" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K95" s="11"/>
@@ -4088,11 +4110,11 @@
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
       <c r="I96" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J96" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K96" s="11"/>
@@ -4110,11 +4132,11 @@
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J97" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K97" s="11"/>
@@ -4132,11 +4154,11 @@
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
       <c r="I98" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J98" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K98" s="11"/>
@@ -4154,11 +4176,11 @@
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
       <c r="I99" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J99" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K99" s="11"/>
@@ -4176,11 +4198,11 @@
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
       <c r="I100" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J100" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K100" s="11"/>
@@ -4198,11 +4220,11 @@
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
       <c r="I101" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J101" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K101" s="11"/>
@@ -4220,11 +4242,11 @@
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
       <c r="I102" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J102" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K102" s="11"/>
@@ -4242,11 +4264,11 @@
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J103" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K103" s="11"/>
@@ -4264,11 +4286,11 @@
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
       <c r="I104" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J104" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K104" s="11"/>
@@ -4286,11 +4308,11 @@
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
       <c r="I105" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J105" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K105" s="11"/>
@@ -4308,11 +4330,11 @@
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
       <c r="I106" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J106" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K106" s="11"/>
@@ -4330,11 +4352,11 @@
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J107" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K107" s="11"/>
@@ -4352,11 +4374,11 @@
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
       <c r="I108" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J108" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K108" s="11"/>
@@ -4374,11 +4396,11 @@
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J109" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K109" s="11"/>
@@ -4396,11 +4418,11 @@
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J110" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K110" s="11"/>
@@ -4418,11 +4440,11 @@
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J111" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K111" s="11"/>
@@ -4440,11 +4462,11 @@
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J112" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K112" s="11"/>
@@ -4462,11 +4484,11 @@
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J113" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K113" s="11"/>
@@ -4484,11 +4506,11 @@
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
       <c r="I114" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J114" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K114" s="11"/>
@@ -4506,11 +4528,11 @@
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
       <c r="I115" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J115" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K115" s="11"/>
@@ -4528,11 +4550,11 @@
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
       <c r="I116" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J116" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K116" s="11"/>
@@ -4550,11 +4572,11 @@
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
       <c r="I117" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J117" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K117" s="11"/>
@@ -4572,11 +4594,11 @@
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J118" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K118" s="11"/>
@@ -4594,11 +4616,11 @@
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
       <c r="I119" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J119" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K119" s="11"/>
@@ -4616,11 +4638,11 @@
       <c r="G120" s="9"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J120" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K120" s="11"/>
@@ -4638,11 +4660,11 @@
       <c r="G121" s="9"/>
       <c r="H121" s="9"/>
       <c r="I121" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J121" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K121" s="11"/>
@@ -4660,11 +4682,11 @@
       <c r="G122" s="9"/>
       <c r="H122" s="9"/>
       <c r="I122" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J122" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K122" s="11"/>
@@ -4682,11 +4704,11 @@
       <c r="G123" s="9"/>
       <c r="H123" s="9"/>
       <c r="I123" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J123" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K123" s="11"/>
@@ -4704,11 +4726,11 @@
       <c r="G124" s="9"/>
       <c r="H124" s="9"/>
       <c r="I124" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J124" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K124" s="11"/>
@@ -4726,11 +4748,11 @@
       <c r="G125" s="9"/>
       <c r="H125" s="9"/>
       <c r="I125" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J125" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K125" s="11"/>
@@ -4748,11 +4770,11 @@
       <c r="G126" s="9"/>
       <c r="H126" s="9"/>
       <c r="I126" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J126" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K126" s="11"/>
@@ -4770,11 +4792,11 @@
       <c r="G127" s="9"/>
       <c r="H127" s="9"/>
       <c r="I127" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J127" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K127" s="11"/>
@@ -4792,11 +4814,11 @@
       <c r="G128" s="9"/>
       <c r="H128" s="9"/>
       <c r="I128" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J128" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K128" s="11"/>
@@ -4814,11 +4836,11 @@
       <c r="G129" s="9"/>
       <c r="H129" s="9"/>
       <c r="I129" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J129" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K129" s="11"/>
@@ -4836,11 +4858,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -4858,11 +4880,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -4880,11 +4902,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -4902,11 +4924,11 @@
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
       <c r="I133" s="10" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="J133" s="10" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="K133" s="11"/>
@@ -4924,11 +4946,11 @@
       <c r="G134" s="9"/>
       <c r="H134" s="9"/>
       <c r="I134" s="10" t="str">
-        <f t="shared" ref="I134:I197" si="64">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="66">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="10" t="str">
-        <f t="shared" ref="J134:J197" si="65">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="67">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="11"/>
@@ -4946,11 +4968,11 @@
       <c r="G135" s="9"/>
       <c r="H135" s="9"/>
       <c r="I135" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J135" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K135" s="11"/>
@@ -4968,11 +4990,11 @@
       <c r="G136" s="9"/>
       <c r="H136" s="9"/>
       <c r="I136" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J136" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K136" s="11"/>
@@ -4990,11 +5012,11 @@
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
       <c r="I137" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J137" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K137" s="11"/>
@@ -5012,11 +5034,11 @@
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J138" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K138" s="11"/>
@@ -5034,11 +5056,11 @@
       <c r="G139" s="9"/>
       <c r="H139" s="9"/>
       <c r="I139" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J139" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K139" s="11"/>
@@ -5056,11 +5078,11 @@
       <c r="G140" s="9"/>
       <c r="H140" s="9"/>
       <c r="I140" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J140" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K140" s="11"/>
@@ -5078,11 +5100,11 @@
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
       <c r="I141" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J141" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K141" s="11"/>
@@ -5100,11 +5122,11 @@
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J142" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K142" s="11"/>
@@ -5122,11 +5144,11 @@
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
       <c r="I143" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J143" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K143" s="11"/>
@@ -5144,11 +5166,11 @@
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
       <c r="I144" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J144" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K144" s="11"/>
@@ -5166,11 +5188,11 @@
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J145" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K145" s="11"/>
@@ -5188,11 +5210,11 @@
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J146" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K146" s="11"/>
@@ -5210,11 +5232,11 @@
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
       <c r="I147" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J147" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K147" s="11"/>
@@ -5232,11 +5254,11 @@
       <c r="G148" s="9"/>
       <c r="H148" s="9"/>
       <c r="I148" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J148" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K148" s="11"/>
@@ -5254,11 +5276,11 @@
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
       <c r="I149" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J149" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K149" s="11"/>
@@ -5276,11 +5298,11 @@
       <c r="G150" s="9"/>
       <c r="H150" s="9"/>
       <c r="I150" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J150" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K150" s="11"/>
@@ -5298,11 +5320,11 @@
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
       <c r="I151" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J151" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K151" s="11"/>
@@ -5320,11 +5342,11 @@
       <c r="G152" s="9"/>
       <c r="H152" s="9"/>
       <c r="I152" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J152" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K152" s="11"/>
@@ -5342,11 +5364,11 @@
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
       <c r="I153" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J153" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K153" s="11"/>
@@ -5364,11 +5386,11 @@
       <c r="G154" s="9"/>
       <c r="H154" s="9"/>
       <c r="I154" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J154" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K154" s="11"/>
@@ -5386,11 +5408,11 @@
       <c r="G155" s="9"/>
       <c r="H155" s="9"/>
       <c r="I155" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J155" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K155" s="11"/>
@@ -5408,11 +5430,11 @@
       <c r="G156" s="9"/>
       <c r="H156" s="9"/>
       <c r="I156" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J156" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K156" s="11"/>
@@ -5430,11 +5452,11 @@
       <c r="G157" s="9"/>
       <c r="H157" s="9"/>
       <c r="I157" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J157" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K157" s="11"/>
@@ -5452,11 +5474,11 @@
       <c r="G158" s="9"/>
       <c r="H158" s="9"/>
       <c r="I158" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J158" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K158" s="11"/>
@@ -5474,11 +5496,11 @@
       <c r="G159" s="9"/>
       <c r="H159" s="9"/>
       <c r="I159" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J159" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K159" s="11"/>
@@ -5496,11 +5518,11 @@
       <c r="G160" s="9"/>
       <c r="H160" s="9"/>
       <c r="I160" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J160" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K160" s="11"/>
@@ -5518,11 +5540,11 @@
       <c r="G161" s="9"/>
       <c r="H161" s="9"/>
       <c r="I161" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J161" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K161" s="11"/>
@@ -5540,11 +5562,11 @@
       <c r="G162" s="9"/>
       <c r="H162" s="9"/>
       <c r="I162" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J162" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K162" s="11"/>
@@ -5562,11 +5584,11 @@
       <c r="G163" s="9"/>
       <c r="H163" s="9"/>
       <c r="I163" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J163" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K163" s="11"/>
@@ -5584,11 +5606,11 @@
       <c r="G164" s="9"/>
       <c r="H164" s="9"/>
       <c r="I164" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J164" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K164" s="11"/>
@@ -5606,11 +5628,11 @@
       <c r="G165" s="9"/>
       <c r="H165" s="9"/>
       <c r="I165" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J165" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K165" s="11"/>
@@ -5628,11 +5650,11 @@
       <c r="G166" s="9"/>
       <c r="H166" s="9"/>
       <c r="I166" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J166" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K166" s="11"/>
@@ -5650,11 +5672,11 @@
       <c r="G167" s="9"/>
       <c r="H167" s="9"/>
       <c r="I167" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J167" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K167" s="11"/>
@@ -5672,11 +5694,11 @@
       <c r="G168" s="9"/>
       <c r="H168" s="9"/>
       <c r="I168" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J168" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K168" s="11"/>
@@ -5694,11 +5716,11 @@
       <c r="G169" s="9"/>
       <c r="H169" s="9"/>
       <c r="I169" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J169" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K169" s="11"/>
@@ -5716,11 +5738,11 @@
       <c r="G170" s="9"/>
       <c r="H170" s="9"/>
       <c r="I170" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J170" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K170" s="11"/>
@@ -5738,11 +5760,11 @@
       <c r="G171" s="9"/>
       <c r="H171" s="9"/>
       <c r="I171" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J171" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K171" s="11"/>
@@ -5760,11 +5782,11 @@
       <c r="G172" s="9"/>
       <c r="H172" s="9"/>
       <c r="I172" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J172" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K172" s="11"/>
@@ -5782,11 +5804,11 @@
       <c r="G173" s="9"/>
       <c r="H173" s="9"/>
       <c r="I173" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J173" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K173" s="11"/>
@@ -5804,11 +5826,11 @@
       <c r="G174" s="9"/>
       <c r="H174" s="9"/>
       <c r="I174" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J174" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K174" s="11"/>
@@ -5826,11 +5848,11 @@
       <c r="G175" s="9"/>
       <c r="H175" s="9"/>
       <c r="I175" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J175" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K175" s="11"/>
@@ -5848,11 +5870,11 @@
       <c r="G176" s="9"/>
       <c r="H176" s="9"/>
       <c r="I176" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J176" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K176" s="11"/>
@@ -5870,11 +5892,11 @@
       <c r="G177" s="9"/>
       <c r="H177" s="9"/>
       <c r="I177" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J177" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K177" s="11"/>
@@ -5892,11 +5914,11 @@
       <c r="G178" s="9"/>
       <c r="H178" s="9"/>
       <c r="I178" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J178" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K178" s="11"/>
@@ -5914,11 +5936,11 @@
       <c r="G179" s="9"/>
       <c r="H179" s="9"/>
       <c r="I179" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J179" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K179" s="11"/>
@@ -5936,11 +5958,11 @@
       <c r="G180" s="9"/>
       <c r="H180" s="9"/>
       <c r="I180" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J180" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K180" s="11"/>
@@ -5958,11 +5980,11 @@
       <c r="G181" s="9"/>
       <c r="H181" s="9"/>
       <c r="I181" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J181" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K181" s="11"/>
@@ -5980,11 +6002,11 @@
       <c r="G182" s="9"/>
       <c r="H182" s="9"/>
       <c r="I182" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J182" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K182" s="11"/>
@@ -6002,11 +6024,11 @@
       <c r="G183" s="9"/>
       <c r="H183" s="9"/>
       <c r="I183" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J183" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K183" s="11"/>
@@ -6024,11 +6046,11 @@
       <c r="G184" s="9"/>
       <c r="H184" s="9"/>
       <c r="I184" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J184" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K184" s="11"/>
@@ -6046,11 +6068,11 @@
       <c r="G185" s="9"/>
       <c r="H185" s="9"/>
       <c r="I185" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J185" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K185" s="11"/>
@@ -6068,11 +6090,11 @@
       <c r="G186" s="9"/>
       <c r="H186" s="9"/>
       <c r="I186" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J186" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K186" s="11"/>
@@ -6090,11 +6112,11 @@
       <c r="G187" s="9"/>
       <c r="H187" s="9"/>
       <c r="I187" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J187" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K187" s="11"/>
@@ -6112,11 +6134,11 @@
       <c r="G188" s="9"/>
       <c r="H188" s="9"/>
       <c r="I188" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J188" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K188" s="11"/>
@@ -6134,11 +6156,11 @@
       <c r="G189" s="9"/>
       <c r="H189" s="9"/>
       <c r="I189" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J189" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K189" s="11"/>
@@ -6156,11 +6178,11 @@
       <c r="G190" s="9"/>
       <c r="H190" s="9"/>
       <c r="I190" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J190" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K190" s="11"/>
@@ -6178,11 +6200,11 @@
       <c r="G191" s="9"/>
       <c r="H191" s="9"/>
       <c r="I191" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J191" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K191" s="11"/>
@@ -6200,11 +6222,11 @@
       <c r="G192" s="9"/>
       <c r="H192" s="9"/>
       <c r="I192" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J192" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K192" s="11"/>
@@ -6222,11 +6244,11 @@
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J193" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K193" s="11"/>
@@ -6244,11 +6266,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -6266,11 +6288,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -6288,11 +6310,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -6310,11 +6332,11 @@
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="10" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="J197" s="10" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="K197" s="11"/>
@@ -6332,11 +6354,11 @@
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
       <c r="I198" s="10" t="str">
-        <f t="shared" ref="I198:I261" si="66">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="68">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="10" t="str">
-        <f t="shared" ref="J198:J261" si="67">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="69">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="11"/>
@@ -6354,11 +6376,11 @@
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
       <c r="I199" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J199" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K199" s="11"/>
@@ -6376,11 +6398,11 @@
       <c r="G200" s="9"/>
       <c r="H200" s="9"/>
       <c r="I200" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J200" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K200" s="11"/>
@@ -6398,11 +6420,11 @@
       <c r="G201" s="9"/>
       <c r="H201" s="9"/>
       <c r="I201" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J201" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K201" s="11"/>
@@ -6420,11 +6442,11 @@
       <c r="G202" s="9"/>
       <c r="H202" s="9"/>
       <c r="I202" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J202" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K202" s="11"/>
@@ -6442,11 +6464,11 @@
       <c r="G203" s="9"/>
       <c r="H203" s="9"/>
       <c r="I203" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J203" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K203" s="11"/>
@@ -6464,11 +6486,11 @@
       <c r="G204" s="9"/>
       <c r="H204" s="9"/>
       <c r="I204" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J204" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K204" s="11"/>
@@ -6486,11 +6508,11 @@
       <c r="G205" s="9"/>
       <c r="H205" s="9"/>
       <c r="I205" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J205" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K205" s="11"/>
@@ -6508,11 +6530,11 @@
       <c r="G206" s="9"/>
       <c r="H206" s="9"/>
       <c r="I206" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J206" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K206" s="11"/>
@@ -6530,11 +6552,11 @@
       <c r="G207" s="9"/>
       <c r="H207" s="9"/>
       <c r="I207" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J207" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K207" s="11"/>
@@ -6552,11 +6574,11 @@
       <c r="G208" s="9"/>
       <c r="H208" s="9"/>
       <c r="I208" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J208" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K208" s="11"/>
@@ -6574,11 +6596,11 @@
       <c r="G209" s="9"/>
       <c r="H209" s="9"/>
       <c r="I209" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J209" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K209" s="11"/>
@@ -6596,11 +6618,11 @@
       <c r="G210" s="9"/>
       <c r="H210" s="9"/>
       <c r="I210" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J210" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K210" s="11"/>
@@ -6618,11 +6640,11 @@
       <c r="G211" s="9"/>
       <c r="H211" s="9"/>
       <c r="I211" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J211" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K211" s="11"/>
@@ -6640,11 +6662,11 @@
       <c r="G212" s="9"/>
       <c r="H212" s="9"/>
       <c r="I212" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J212" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K212" s="11"/>
@@ -6662,11 +6684,11 @@
       <c r="G213" s="9"/>
       <c r="H213" s="9"/>
       <c r="I213" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J213" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K213" s="11"/>
@@ -6684,11 +6706,11 @@
       <c r="G214" s="9"/>
       <c r="H214" s="9"/>
       <c r="I214" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J214" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K214" s="11"/>
@@ -6706,11 +6728,11 @@
       <c r="G215" s="9"/>
       <c r="H215" s="9"/>
       <c r="I215" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J215" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K215" s="11"/>
@@ -6728,11 +6750,11 @@
       <c r="G216" s="9"/>
       <c r="H216" s="9"/>
       <c r="I216" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J216" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K216" s="11"/>
@@ -6750,11 +6772,11 @@
       <c r="G217" s="9"/>
       <c r="H217" s="9"/>
       <c r="I217" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J217" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K217" s="11"/>
@@ -6772,11 +6794,11 @@
       <c r="G218" s="9"/>
       <c r="H218" s="9"/>
       <c r="I218" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J218" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K218" s="11"/>
@@ -6794,11 +6816,11 @@
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
       <c r="I219" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J219" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K219" s="11"/>
@@ -6816,11 +6838,11 @@
       <c r="G220" s="9"/>
       <c r="H220" s="9"/>
       <c r="I220" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J220" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K220" s="11"/>
@@ -6838,11 +6860,11 @@
       <c r="G221" s="9"/>
       <c r="H221" s="9"/>
       <c r="I221" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J221" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K221" s="11"/>
@@ -6860,11 +6882,11 @@
       <c r="G222" s="9"/>
       <c r="H222" s="9"/>
       <c r="I222" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J222" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K222" s="11"/>
@@ -6882,11 +6904,11 @@
       <c r="G223" s="9"/>
       <c r="H223" s="9"/>
       <c r="I223" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J223" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K223" s="11"/>
@@ -6904,11 +6926,11 @@
       <c r="G224" s="9"/>
       <c r="H224" s="9"/>
       <c r="I224" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J224" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K224" s="11"/>
@@ -6926,11 +6948,11 @@
       <c r="G225" s="9"/>
       <c r="H225" s="9"/>
       <c r="I225" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J225" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K225" s="11"/>
@@ -6948,11 +6970,11 @@
       <c r="G226" s="9"/>
       <c r="H226" s="9"/>
       <c r="I226" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J226" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K226" s="11"/>
@@ -6970,11 +6992,11 @@
       <c r="G227" s="9"/>
       <c r="H227" s="9"/>
       <c r="I227" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J227" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K227" s="11"/>
@@ -6992,11 +7014,11 @@
       <c r="G228" s="9"/>
       <c r="H228" s="9"/>
       <c r="I228" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J228" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K228" s="11"/>
@@ -7014,11 +7036,11 @@
       <c r="G229" s="9"/>
       <c r="H229" s="9"/>
       <c r="I229" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J229" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K229" s="11"/>
@@ -7036,11 +7058,11 @@
       <c r="G230" s="9"/>
       <c r="H230" s="9"/>
       <c r="I230" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J230" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K230" s="11"/>
@@ -7058,11 +7080,11 @@
       <c r="G231" s="9"/>
       <c r="H231" s="9"/>
       <c r="I231" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J231" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K231" s="11"/>
@@ -7080,11 +7102,11 @@
       <c r="G232" s="9"/>
       <c r="H232" s="9"/>
       <c r="I232" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J232" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K232" s="11"/>
@@ -7102,11 +7124,11 @@
       <c r="G233" s="9"/>
       <c r="H233" s="9"/>
       <c r="I233" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J233" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K233" s="11"/>
@@ -7124,11 +7146,11 @@
       <c r="G234" s="9"/>
       <c r="H234" s="9"/>
       <c r="I234" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J234" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K234" s="11"/>
@@ -7146,11 +7168,11 @@
       <c r="G235" s="9"/>
       <c r="H235" s="9"/>
       <c r="I235" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J235" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K235" s="11"/>
@@ -7168,11 +7190,11 @@
       <c r="G236" s="9"/>
       <c r="H236" s="9"/>
       <c r="I236" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J236" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K236" s="11"/>
@@ -7190,11 +7212,11 @@
       <c r="G237" s="9"/>
       <c r="H237" s="9"/>
       <c r="I237" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J237" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K237" s="11"/>
@@ -7212,11 +7234,11 @@
       <c r="G238" s="9"/>
       <c r="H238" s="9"/>
       <c r="I238" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J238" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K238" s="11"/>
@@ -7234,11 +7256,11 @@
       <c r="G239" s="9"/>
       <c r="H239" s="9"/>
       <c r="I239" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J239" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K239" s="11"/>
@@ -7256,11 +7278,11 @@
       <c r="G240" s="9"/>
       <c r="H240" s="9"/>
       <c r="I240" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J240" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K240" s="11"/>
@@ -7278,11 +7300,11 @@
       <c r="G241" s="9"/>
       <c r="H241" s="9"/>
       <c r="I241" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J241" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K241" s="11"/>
@@ -7300,11 +7322,11 @@
       <c r="G242" s="9"/>
       <c r="H242" s="9"/>
       <c r="I242" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J242" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K242" s="11"/>
@@ -7322,11 +7344,11 @@
       <c r="G243" s="9"/>
       <c r="H243" s="9"/>
       <c r="I243" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J243" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K243" s="11"/>
@@ -7344,11 +7366,11 @@
       <c r="G244" s="9"/>
       <c r="H244" s="9"/>
       <c r="I244" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J244" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K244" s="11"/>
@@ -7366,11 +7388,11 @@
       <c r="G245" s="9"/>
       <c r="H245" s="9"/>
       <c r="I245" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J245" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K245" s="11"/>
@@ -7388,11 +7410,11 @@
       <c r="G246" s="9"/>
       <c r="H246" s="9"/>
       <c r="I246" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J246" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K246" s="11"/>
@@ -7410,11 +7432,11 @@
       <c r="G247" s="9"/>
       <c r="H247" s="9"/>
       <c r="I247" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J247" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K247" s="11"/>
@@ -7432,11 +7454,11 @@
       <c r="G248" s="9"/>
       <c r="H248" s="9"/>
       <c r="I248" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J248" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K248" s="11"/>
@@ -7454,11 +7476,11 @@
       <c r="G249" s="9"/>
       <c r="H249" s="9"/>
       <c r="I249" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J249" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K249" s="11"/>
@@ -7476,11 +7498,11 @@
       <c r="G250" s="9"/>
       <c r="H250" s="9"/>
       <c r="I250" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J250" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K250" s="11"/>
@@ -7498,11 +7520,11 @@
       <c r="G251" s="9"/>
       <c r="H251" s="9"/>
       <c r="I251" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J251" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K251" s="11"/>
@@ -7520,11 +7542,11 @@
       <c r="G252" s="9"/>
       <c r="H252" s="9"/>
       <c r="I252" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J252" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K252" s="11"/>
@@ -7542,11 +7564,11 @@
       <c r="G253" s="9"/>
       <c r="H253" s="9"/>
       <c r="I253" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J253" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K253" s="11"/>
@@ -7564,11 +7586,11 @@
       <c r="G254" s="9"/>
       <c r="H254" s="9"/>
       <c r="I254" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J254" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K254" s="11"/>
@@ -7586,11 +7608,11 @@
       <c r="G255" s="9"/>
       <c r="H255" s="9"/>
       <c r="I255" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J255" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K255" s="11"/>
@@ -7608,11 +7630,11 @@
       <c r="G256" s="9"/>
       <c r="H256" s="9"/>
       <c r="I256" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J256" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K256" s="11"/>
@@ -7630,11 +7652,11 @@
       <c r="G257" s="9"/>
       <c r="H257" s="9"/>
       <c r="I257" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J257" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K257" s="11"/>
@@ -7652,11 +7674,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -7674,11 +7696,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -7696,11 +7718,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -7718,11 +7740,11 @@
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
       <c r="I261" s="10" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="J261" s="10" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="K261" s="11"/>
@@ -7740,11 +7762,11 @@
       <c r="G262" s="9"/>
       <c r="H262" s="9"/>
       <c r="I262" s="10" t="str">
-        <f t="shared" ref="I262:I325" si="68">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="70">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="10" t="str">
-        <f t="shared" ref="J262:J325" si="69">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="71">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="11"/>
@@ -7762,11 +7784,11 @@
       <c r="G263" s="9"/>
       <c r="H263" s="9"/>
       <c r="I263" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J263" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K263" s="11"/>
@@ -7784,11 +7806,11 @@
       <c r="G264" s="9"/>
       <c r="H264" s="9"/>
       <c r="I264" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J264" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K264" s="11"/>
@@ -7806,11 +7828,11 @@
       <c r="G265" s="9"/>
       <c r="H265" s="9"/>
       <c r="I265" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J265" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K265" s="11"/>
@@ -7828,11 +7850,11 @@
       <c r="G266" s="9"/>
       <c r="H266" s="9"/>
       <c r="I266" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J266" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K266" s="11"/>
@@ -7850,11 +7872,11 @@
       <c r="G267" s="9"/>
       <c r="H267" s="9"/>
       <c r="I267" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J267" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K267" s="11"/>
@@ -7872,11 +7894,11 @@
       <c r="G268" s="9"/>
       <c r="H268" s="9"/>
       <c r="I268" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J268" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K268" s="11"/>
@@ -7894,11 +7916,11 @@
       <c r="G269" s="9"/>
       <c r="H269" s="9"/>
       <c r="I269" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J269" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K269" s="11"/>
@@ -7916,11 +7938,11 @@
       <c r="G270" s="9"/>
       <c r="H270" s="9"/>
       <c r="I270" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J270" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K270" s="11"/>
@@ -7938,11 +7960,11 @@
       <c r="G271" s="9"/>
       <c r="H271" s="9"/>
       <c r="I271" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J271" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K271" s="11"/>
@@ -7960,11 +7982,11 @@
       <c r="G272" s="9"/>
       <c r="H272" s="9"/>
       <c r="I272" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J272" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K272" s="11"/>
@@ -7982,11 +8004,11 @@
       <c r="G273" s="9"/>
       <c r="H273" s="9"/>
       <c r="I273" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J273" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K273" s="11"/>
@@ -8004,11 +8026,11 @@
       <c r="G274" s="9"/>
       <c r="H274" s="9"/>
       <c r="I274" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J274" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K274" s="11"/>
@@ -8026,11 +8048,11 @@
       <c r="G275" s="9"/>
       <c r="H275" s="9"/>
       <c r="I275" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J275" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K275" s="11"/>
@@ -8048,11 +8070,11 @@
       <c r="G276" s="9"/>
       <c r="H276" s="9"/>
       <c r="I276" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J276" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K276" s="11"/>
@@ -8070,11 +8092,11 @@
       <c r="G277" s="9"/>
       <c r="H277" s="9"/>
       <c r="I277" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J277" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K277" s="11"/>
@@ -8092,11 +8114,11 @@
       <c r="G278" s="9"/>
       <c r="H278" s="9"/>
       <c r="I278" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J278" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K278" s="11"/>
@@ -8114,11 +8136,11 @@
       <c r="G279" s="9"/>
       <c r="H279" s="9"/>
       <c r="I279" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J279" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K279" s="11"/>
@@ -8136,11 +8158,11 @@
       <c r="G280" s="9"/>
       <c r="H280" s="9"/>
       <c r="I280" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J280" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K280" s="11"/>
@@ -8158,11 +8180,11 @@
       <c r="G281" s="9"/>
       <c r="H281" s="9"/>
       <c r="I281" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J281" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K281" s="11"/>
@@ -8180,11 +8202,11 @@
       <c r="G282" s="9"/>
       <c r="H282" s="9"/>
       <c r="I282" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J282" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K282" s="11"/>
@@ -8202,11 +8224,11 @@
       <c r="G283" s="9"/>
       <c r="H283" s="9"/>
       <c r="I283" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J283" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K283" s="11"/>
@@ -8224,11 +8246,11 @@
       <c r="G284" s="9"/>
       <c r="H284" s="9"/>
       <c r="I284" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J284" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K284" s="11"/>
@@ -8246,11 +8268,11 @@
       <c r="G285" s="9"/>
       <c r="H285" s="9"/>
       <c r="I285" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J285" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K285" s="11"/>
@@ -8268,11 +8290,11 @@
       <c r="G286" s="9"/>
       <c r="H286" s="9"/>
       <c r="I286" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J286" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K286" s="11"/>
@@ -8290,11 +8312,11 @@
       <c r="G287" s="9"/>
       <c r="H287" s="9"/>
       <c r="I287" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J287" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K287" s="11"/>
@@ -8312,11 +8334,11 @@
       <c r="G288" s="9"/>
       <c r="H288" s="9"/>
       <c r="I288" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J288" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K288" s="11"/>
@@ -8334,11 +8356,11 @@
       <c r="G289" s="9"/>
       <c r="H289" s="9"/>
       <c r="I289" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J289" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K289" s="11"/>
@@ -8356,11 +8378,11 @@
       <c r="G290" s="9"/>
       <c r="H290" s="9"/>
       <c r="I290" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J290" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K290" s="11"/>
@@ -8378,11 +8400,11 @@
       <c r="G291" s="9"/>
       <c r="H291" s="9"/>
       <c r="I291" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J291" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K291" s="11"/>
@@ -8400,11 +8422,11 @@
       <c r="G292" s="9"/>
       <c r="H292" s="9"/>
       <c r="I292" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J292" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K292" s="11"/>
@@ -8422,11 +8444,11 @@
       <c r="G293" s="9"/>
       <c r="H293" s="9"/>
       <c r="I293" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J293" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K293" s="11"/>
@@ -8444,11 +8466,11 @@
       <c r="G294" s="9"/>
       <c r="H294" s="9"/>
       <c r="I294" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J294" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K294" s="11"/>
@@ -8466,11 +8488,11 @@
       <c r="G295" s="9"/>
       <c r="H295" s="9"/>
       <c r="I295" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J295" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K295" s="11"/>
@@ -8488,11 +8510,11 @@
       <c r="G296" s="9"/>
       <c r="H296" s="9"/>
       <c r="I296" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J296" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K296" s="11"/>
@@ -8510,11 +8532,11 @@
       <c r="G297" s="9"/>
       <c r="H297" s="9"/>
       <c r="I297" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J297" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K297" s="11"/>
@@ -8532,11 +8554,11 @@
       <c r="G298" s="9"/>
       <c r="H298" s="9"/>
       <c r="I298" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J298" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K298" s="11"/>
@@ -8554,11 +8576,11 @@
       <c r="G299" s="9"/>
       <c r="H299" s="9"/>
       <c r="I299" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J299" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K299" s="11"/>
@@ -8576,11 +8598,11 @@
       <c r="G300" s="9"/>
       <c r="H300" s="9"/>
       <c r="I300" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J300" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K300" s="11"/>
@@ -8598,11 +8620,11 @@
       <c r="G301" s="9"/>
       <c r="H301" s="9"/>
       <c r="I301" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J301" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K301" s="11"/>
@@ -8620,11 +8642,11 @@
       <c r="G302" s="9"/>
       <c r="H302" s="9"/>
       <c r="I302" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J302" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K302" s="11"/>
@@ -8642,11 +8664,11 @@
       <c r="G303" s="9"/>
       <c r="H303" s="9"/>
       <c r="I303" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J303" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K303" s="11"/>
@@ -8664,11 +8686,11 @@
       <c r="G304" s="9"/>
       <c r="H304" s="9"/>
       <c r="I304" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J304" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K304" s="11"/>
@@ -8686,11 +8708,11 @@
       <c r="G305" s="9"/>
       <c r="H305" s="9"/>
       <c r="I305" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J305" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K305" s="11"/>
@@ -8708,11 +8730,11 @@
       <c r="G306" s="9"/>
       <c r="H306" s="9"/>
       <c r="I306" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J306" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K306" s="11"/>
@@ -8730,11 +8752,11 @@
       <c r="G307" s="9"/>
       <c r="H307" s="9"/>
       <c r="I307" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J307" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K307" s="11"/>
@@ -8752,11 +8774,11 @@
       <c r="G308" s="9"/>
       <c r="H308" s="9"/>
       <c r="I308" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J308" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K308" s="11"/>
@@ -8774,11 +8796,11 @@
       <c r="G309" s="9"/>
       <c r="H309" s="9"/>
       <c r="I309" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J309" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K309" s="11"/>
@@ -8796,11 +8818,11 @@
       <c r="G310" s="9"/>
       <c r="H310" s="9"/>
       <c r="I310" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J310" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K310" s="11"/>
@@ -8818,11 +8840,11 @@
       <c r="G311" s="9"/>
       <c r="H311" s="9"/>
       <c r="I311" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J311" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K311" s="11"/>
@@ -8840,11 +8862,11 @@
       <c r="G312" s="9"/>
       <c r="H312" s="9"/>
       <c r="I312" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J312" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K312" s="11"/>
@@ -8862,11 +8884,11 @@
       <c r="G313" s="9"/>
       <c r="H313" s="9"/>
       <c r="I313" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J313" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K313" s="11"/>
@@ -8884,11 +8906,11 @@
       <c r="G314" s="9"/>
       <c r="H314" s="9"/>
       <c r="I314" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J314" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K314" s="11"/>
@@ -8906,11 +8928,11 @@
       <c r="G315" s="9"/>
       <c r="H315" s="9"/>
       <c r="I315" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J315" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K315" s="11"/>
@@ -8928,11 +8950,11 @@
       <c r="G316" s="9"/>
       <c r="H316" s="9"/>
       <c r="I316" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J316" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K316" s="11"/>
@@ -8950,11 +8972,11 @@
       <c r="G317" s="9"/>
       <c r="H317" s="9"/>
       <c r="I317" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J317" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K317" s="11"/>
@@ -8972,11 +8994,11 @@
       <c r="G318" s="9"/>
       <c r="H318" s="9"/>
       <c r="I318" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J318" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K318" s="11"/>
@@ -8994,11 +9016,11 @@
       <c r="G319" s="9"/>
       <c r="H319" s="9"/>
       <c r="I319" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J319" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K319" s="11"/>
@@ -9016,11 +9038,11 @@
       <c r="G320" s="9"/>
       <c r="H320" s="9"/>
       <c r="I320" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J320" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K320" s="11"/>
@@ -9038,11 +9060,11 @@
       <c r="G321" s="9"/>
       <c r="H321" s="9"/>
       <c r="I321" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J321" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K321" s="11"/>
@@ -9060,11 +9082,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -9082,11 +9104,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -9104,11 +9126,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -9126,11 +9148,11 @@
       <c r="G325" s="9"/>
       <c r="H325" s="9"/>
       <c r="I325" s="10" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="J325" s="10" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="K325" s="11"/>
@@ -9148,11 +9170,11 @@
       <c r="G326" s="9"/>
       <c r="H326" s="9"/>
       <c r="I326" s="10" t="str">
-        <f t="shared" ref="I326:I389" si="70">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="72">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="10" t="str">
-        <f t="shared" ref="J326:J389" si="71">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="73">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="11"/>
@@ -9170,11 +9192,11 @@
       <c r="G327" s="9"/>
       <c r="H327" s="9"/>
       <c r="I327" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J327" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K327" s="11"/>
@@ -9192,11 +9214,11 @@
       <c r="G328" s="9"/>
       <c r="H328" s="9"/>
       <c r="I328" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J328" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K328" s="11"/>
@@ -9214,11 +9236,11 @@
       <c r="G329" s="9"/>
       <c r="H329" s="9"/>
       <c r="I329" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J329" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K329" s="11"/>
@@ -9236,11 +9258,11 @@
       <c r="G330" s="9"/>
       <c r="H330" s="9"/>
       <c r="I330" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J330" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K330" s="11"/>
@@ -9258,11 +9280,11 @@
       <c r="G331" s="9"/>
       <c r="H331" s="9"/>
       <c r="I331" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J331" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K331" s="11"/>
@@ -9280,11 +9302,11 @@
       <c r="G332" s="9"/>
       <c r="H332" s="9"/>
       <c r="I332" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J332" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K332" s="11"/>
@@ -9302,11 +9324,11 @@
       <c r="G333" s="9"/>
       <c r="H333" s="9"/>
       <c r="I333" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J333" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K333" s="11"/>
@@ -9324,11 +9346,11 @@
       <c r="G334" s="9"/>
       <c r="H334" s="9"/>
       <c r="I334" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J334" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K334" s="11"/>
@@ -9346,11 +9368,11 @@
       <c r="G335" s="9"/>
       <c r="H335" s="9"/>
       <c r="I335" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J335" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K335" s="11"/>
@@ -9368,11 +9390,11 @@
       <c r="G336" s="9"/>
       <c r="H336" s="9"/>
       <c r="I336" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J336" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K336" s="11"/>
@@ -9390,11 +9412,11 @@
       <c r="G337" s="9"/>
       <c r="H337" s="9"/>
       <c r="I337" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J337" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K337" s="11"/>
@@ -9412,11 +9434,11 @@
       <c r="G338" s="9"/>
       <c r="H338" s="9"/>
       <c r="I338" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J338" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K338" s="11"/>
@@ -9434,11 +9456,11 @@
       <c r="G339" s="9"/>
       <c r="H339" s="9"/>
       <c r="I339" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J339" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K339" s="11"/>
@@ -9456,11 +9478,11 @@
       <c r="G340" s="9"/>
       <c r="H340" s="9"/>
       <c r="I340" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J340" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K340" s="11"/>
@@ -9478,11 +9500,11 @@
       <c r="G341" s="9"/>
       <c r="H341" s="9"/>
       <c r="I341" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J341" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K341" s="11"/>
@@ -9500,11 +9522,11 @@
       <c r="G342" s="9"/>
       <c r="H342" s="9"/>
       <c r="I342" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J342" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K342" s="11"/>
@@ -9522,11 +9544,11 @@
       <c r="G343" s="9"/>
       <c r="H343" s="9"/>
       <c r="I343" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J343" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K343" s="11"/>
@@ -9544,11 +9566,11 @@
       <c r="G344" s="9"/>
       <c r="H344" s="9"/>
       <c r="I344" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J344" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K344" s="11"/>
@@ -9566,11 +9588,11 @@
       <c r="G345" s="9"/>
       <c r="H345" s="9"/>
       <c r="I345" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J345" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K345" s="11"/>
@@ -9588,11 +9610,11 @@
       <c r="G346" s="9"/>
       <c r="H346" s="9"/>
       <c r="I346" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J346" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K346" s="11"/>
@@ -9610,11 +9632,11 @@
       <c r="G347" s="9"/>
       <c r="H347" s="9"/>
       <c r="I347" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J347" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K347" s="11"/>
@@ -9632,11 +9654,11 @@
       <c r="G348" s="9"/>
       <c r="H348" s="9"/>
       <c r="I348" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J348" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K348" s="11"/>
@@ -9654,11 +9676,11 @@
       <c r="G349" s="9"/>
       <c r="H349" s="9"/>
       <c r="I349" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J349" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K349" s="11"/>
@@ -9676,11 +9698,11 @@
       <c r="G350" s="9"/>
       <c r="H350" s="9"/>
       <c r="I350" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J350" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K350" s="11"/>
@@ -9698,11 +9720,11 @@
       <c r="G351" s="9"/>
       <c r="H351" s="9"/>
       <c r="I351" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J351" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K351" s="11"/>
@@ -9720,11 +9742,11 @@
       <c r="G352" s="9"/>
       <c r="H352" s="9"/>
       <c r="I352" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J352" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K352" s="11"/>
@@ -9742,11 +9764,11 @@
       <c r="G353" s="9"/>
       <c r="H353" s="9"/>
       <c r="I353" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J353" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K353" s="11"/>
@@ -9764,11 +9786,11 @@
       <c r="G354" s="9"/>
       <c r="H354" s="9"/>
       <c r="I354" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J354" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K354" s="11"/>
@@ -9786,11 +9808,11 @@
       <c r="G355" s="9"/>
       <c r="H355" s="9"/>
       <c r="I355" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J355" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K355" s="11"/>
@@ -9808,11 +9830,11 @@
       <c r="G356" s="9"/>
       <c r="H356" s="9"/>
       <c r="I356" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J356" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K356" s="11"/>
@@ -9830,11 +9852,11 @@
       <c r="G357" s="9"/>
       <c r="H357" s="9"/>
       <c r="I357" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J357" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K357" s="11"/>
@@ -9852,11 +9874,11 @@
       <c r="G358" s="9"/>
       <c r="H358" s="9"/>
       <c r="I358" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J358" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K358" s="11"/>
@@ -9874,11 +9896,11 @@
       <c r="G359" s="9"/>
       <c r="H359" s="9"/>
       <c r="I359" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J359" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K359" s="11"/>
@@ -9896,11 +9918,11 @@
       <c r="G360" s="9"/>
       <c r="H360" s="9"/>
       <c r="I360" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J360" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K360" s="11"/>
@@ -9918,11 +9940,11 @@
       <c r="G361" s="9"/>
       <c r="H361" s="9"/>
       <c r="I361" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J361" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K361" s="11"/>
@@ -9940,11 +9962,11 @@
       <c r="G362" s="9"/>
       <c r="H362" s="9"/>
       <c r="I362" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J362" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K362" s="11"/>
@@ -9962,11 +9984,11 @@
       <c r="G363" s="9"/>
       <c r="H363" s="9"/>
       <c r="I363" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J363" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K363" s="11"/>
@@ -9984,11 +10006,11 @@
       <c r="G364" s="9"/>
       <c r="H364" s="9"/>
       <c r="I364" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J364" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K364" s="11"/>
@@ -10006,11 +10028,11 @@
       <c r="G365" s="9"/>
       <c r="H365" s="9"/>
       <c r="I365" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J365" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K365" s="11"/>
@@ -10028,11 +10050,11 @@
       <c r="G366" s="9"/>
       <c r="H366" s="9"/>
       <c r="I366" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J366" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K366" s="11"/>
@@ -10050,11 +10072,11 @@
       <c r="G367" s="9"/>
       <c r="H367" s="9"/>
       <c r="I367" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J367" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K367" s="11"/>
@@ -10072,11 +10094,11 @@
       <c r="G368" s="9"/>
       <c r="H368" s="9"/>
       <c r="I368" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J368" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K368" s="11"/>
@@ -10094,11 +10116,11 @@
       <c r="G369" s="9"/>
       <c r="H369" s="9"/>
       <c r="I369" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J369" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K369" s="11"/>
@@ -10116,11 +10138,11 @@
       <c r="G370" s="9"/>
       <c r="H370" s="9"/>
       <c r="I370" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J370" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K370" s="11"/>
@@ -10138,11 +10160,11 @@
       <c r="G371" s="9"/>
       <c r="H371" s="9"/>
       <c r="I371" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J371" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K371" s="11"/>
@@ -10160,11 +10182,11 @@
       <c r="G372" s="9"/>
       <c r="H372" s="9"/>
       <c r="I372" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J372" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K372" s="11"/>
@@ -10182,11 +10204,11 @@
       <c r="G373" s="9"/>
       <c r="H373" s="9"/>
       <c r="I373" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J373" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K373" s="11"/>
@@ -10204,11 +10226,11 @@
       <c r="G374" s="9"/>
       <c r="H374" s="9"/>
       <c r="I374" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J374" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K374" s="11"/>
@@ -10226,11 +10248,11 @@
       <c r="G375" s="9"/>
       <c r="H375" s="9"/>
       <c r="I375" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J375" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K375" s="11"/>
@@ -10248,11 +10270,11 @@
       <c r="G376" s="9"/>
       <c r="H376" s="9"/>
       <c r="I376" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J376" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K376" s="11"/>
@@ -10270,11 +10292,11 @@
       <c r="G377" s="9"/>
       <c r="H377" s="9"/>
       <c r="I377" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J377" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K377" s="11"/>
@@ -10292,11 +10314,11 @@
       <c r="G378" s="9"/>
       <c r="H378" s="9"/>
       <c r="I378" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J378" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K378" s="11"/>
@@ -10314,11 +10336,11 @@
       <c r="G379" s="9"/>
       <c r="H379" s="9"/>
       <c r="I379" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J379" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K379" s="11"/>
@@ -10336,11 +10358,11 @@
       <c r="G380" s="9"/>
       <c r="H380" s="9"/>
       <c r="I380" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J380" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K380" s="11"/>
@@ -10358,11 +10380,11 @@
       <c r="G381" s="9"/>
       <c r="H381" s="9"/>
       <c r="I381" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J381" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K381" s="11"/>
@@ -10380,11 +10402,11 @@
       <c r="G382" s="9"/>
       <c r="H382" s="9"/>
       <c r="I382" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J382" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K382" s="11"/>
@@ -10402,11 +10424,11 @@
       <c r="G383" s="9"/>
       <c r="H383" s="9"/>
       <c r="I383" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J383" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K383" s="11"/>
@@ -10424,11 +10446,11 @@
       <c r="G384" s="9"/>
       <c r="H384" s="9"/>
       <c r="I384" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J384" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K384" s="11"/>
@@ -10446,11 +10468,11 @@
       <c r="G385" s="9"/>
       <c r="H385" s="9"/>
       <c r="I385" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J385" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K385" s="11"/>
@@ -10468,11 +10490,11 @@
       <c r="G386" s="9"/>
       <c r="H386" s="9"/>
       <c r="I386" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J386" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K386" s="11"/>
@@ -10490,11 +10512,11 @@
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J387" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K387" s="11"/>
@@ -10512,11 +10534,11 @@
       <c r="G388" s="9"/>
       <c r="H388" s="9"/>
       <c r="I388" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J388" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K388" s="11"/>
@@ -10534,11 +10556,11 @@
       <c r="G389" s="9"/>
       <c r="H389" s="9"/>
       <c r="I389" s="10" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="J389" s="10" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="K389" s="11"/>
@@ -10556,11 +10578,11 @@
       <c r="G390" s="9"/>
       <c r="H390" s="9"/>
       <c r="I390" s="10" t="str">
-        <f t="shared" ref="I390:I401" si="72">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="74">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="10" t="str">
-        <f t="shared" ref="J390:J401" si="73">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="75">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="11"/>
@@ -10578,11 +10600,11 @@
       <c r="G391" s="9"/>
       <c r="H391" s="9"/>
       <c r="I391" s="10" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="J391" s="10" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
       <c r="K391" s="11"/>
@@ -10600,11 +10622,11 @@
       <c r="G392" s="9"/>
       <c r="H392" s="9"/>
       <c r="I392" s="10" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="J392" s="10" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
       <c r="K392" s="11"/>
@@ -10622,11 +10644,11 @@
       <c r="G393" s="9"/>
       <c r="H393" s="9"/>
       <c r="I393" s="10" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="J393" s="10" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
       <c r="K393" s="11"/>
@@ -10644,11 +10666,11 @@
       <c r="G394" s="9"/>
       <c r="H394" s="9"/>
       <c r="I394" s="10" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="J394" s="10" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
       <c r="K394" s="11"/>
@@ -10666,11 +10688,11 @@
       <c r="G395" s="9"/>
       <c r="H395" s="9"/>
       <c r="I395" s="10" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="J395" s="10" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
       <c r="K395" s="11"/>
@@ -10688,11 +10710,11 @@
       <c r="G396" s="9"/>
       <c r="H396" s="9"/>
       <c r="I396" s="10" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="J396" s="10" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
       <c r="K396" s="11"/>
@@ -10710,11 +10732,11 @@
       <c r="G397" s="9"/>
       <c r="H397" s="9"/>
       <c r="I397" s="10" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="J397" s="10" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
       <c r="K397" s="11"/>
@@ -10732,11 +10754,11 @@
       <c r="G398" s="9"/>
       <c r="H398" s="9"/>
       <c r="I398" s="10" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="J398" s="10" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
       <c r="K398" s="11"/>
@@ -10754,11 +10776,11 @@
       <c r="G399" s="9"/>
       <c r="H399" s="9"/>
       <c r="I399" s="10" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="J399" s="10" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
       <c r="K399" s="11"/>
@@ -10776,11 +10798,11 @@
       <c r="G400" s="9"/>
       <c r="H400" s="9"/>
       <c r="I400" s="10" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="J400" s="10" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
       <c r="K400" s="11"/>
@@ -10798,11 +10820,11 @@
       <c r="G401" s="9"/>
       <c r="H401" s="9"/>
       <c r="I401" s="10" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="J401" s="10" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
       <c r="K401" s="11"/>
